--- a/Compute-Link-Attenuations/TenPatches/batch_analyze_output_multi/stats_multi.xlsx
+++ b/Compute-Link-Attenuations/TenPatches/batch_analyze_output_multi/stats_multi.xlsx
@@ -44206,31 +44206,31 @@
         <v>368399</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2315114221287305</v>
+        <v>0.1306465108982027</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2320506058873874</v>
+        <v>0.12792904215186</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2580783529231732</v>
+        <v>0.1394721173012631</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1823365953653378</v>
+        <v>0.09582361944231463</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2426177681144301</v>
+        <v>0.129355724100973</v>
       </c>
       <c r="J2" t="n">
-        <v>0.5142744917965882</v>
+        <v>0.2707024108001605</v>
       </c>
       <c r="K2" t="n">
-        <v>0.632730412221257</v>
+        <v>0.3925329844473531</v>
       </c>
       <c r="L2" t="n">
-        <v>1.47597273269042</v>
+        <v>0.468392863571744</v>
       </c>
       <c r="M2" t="n">
-        <v>95075.80713854407</v>
+        <v>51381.38854166802</v>
       </c>
     </row>
     <row r="3">
@@ -44253,31 +44253,31 @@
         <v>3408</v>
       </c>
       <c r="E3" t="n">
-        <v>0.05278952407365911</v>
+        <v>0.02559801040489932</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01809562814910352</v>
+        <v>0.01550976594984039</v>
       </c>
       <c r="G3" t="n">
-        <v>0.103546415711893</v>
+        <v>0.04588995994179944</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1310365274410735</v>
+        <v>0.04670960969082329</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04742712115004813</v>
+        <v>0.0337126593292108</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2958991207707208</v>
+        <v>0.102561466209444</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5259991219724853</v>
+        <v>0.2456330002588006</v>
       </c>
       <c r="L3" t="n">
-        <v>0.9893017792064838</v>
+        <v>0.2906470832378574</v>
       </c>
       <c r="M3" t="n">
-        <v>352.8861847461312</v>
+        <v>156.3929834816525</v>
       </c>
     </row>
     <row r="4">
@@ -44300,31 +44300,31 @@
         <v>17085</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03270602911908007</v>
+        <v>0.01618190740633295</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01106590541031261</v>
+        <v>0.006827556132228856</v>
       </c>
       <c r="G4" t="n">
-        <v>0.09465327873197954</v>
+        <v>0.04325333577149761</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1164499512988472</v>
+        <v>0.04588735171121246</v>
       </c>
       <c r="I4" t="n">
-        <v>0.04636052426940765</v>
+        <v>0.02719120233410667</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2657812620768717</v>
+        <v>0.1059651795321242</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4767931860343891</v>
+        <v>0.201989478626428</v>
       </c>
       <c r="L4" t="n">
-        <v>1.448069794590415</v>
+        <v>0.3191721766971276</v>
       </c>
       <c r="M4" t="n">
-        <v>1617.151267135871</v>
+        <v>738.9832416560366</v>
       </c>
     </row>
     <row r="5">
@@ -44347,31 +44347,31 @@
         <v>459</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.01892275172369011</v>
+        <v>-0.005362769644545725</v>
       </c>
       <c r="F5" t="n">
-        <v>6.288612078159902e-05</v>
+        <v>-0.00245145122546445</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05527616860236949</v>
+        <v>0.02590582764273513</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1208302339000693</v>
+        <v>0.03218416283112141</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01954565552743952</v>
+        <v>0.01334669054619636</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1054015941470283</v>
+        <v>0.06779512290418115</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6942565413228055</v>
+        <v>0.1453802897182536</v>
       </c>
       <c r="L5" t="n">
-        <v>1.119262616575068</v>
+        <v>0.2113194773703913</v>
       </c>
       <c r="M5" t="n">
-        <v>25.3717613884876</v>
+        <v>11.89077488801542</v>
       </c>
     </row>
     <row r="6">
@@ -44394,31 +44394,31 @@
         <v>1788</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.00488729403749405</v>
+        <v>-0.001372117636772029</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0003389491549308412</v>
+        <v>-0.001244823451211751</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05478252244659238</v>
+        <v>0.02741191986491195</v>
       </c>
       <c r="H6" t="n">
-        <v>0.08671126808447102</v>
+        <v>0.032679086690002</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02544976790423401</v>
+        <v>0.01601470817620974</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1328122097129649</v>
+        <v>0.06719802667207589</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3980348911490675</v>
+        <v>0.1579847984830567</v>
       </c>
       <c r="L6" t="n">
-        <v>1.246573796986787</v>
+        <v>0.2400782710136644</v>
       </c>
       <c r="M6" t="n">
-        <v>97.95115013450717</v>
+        <v>49.01251271846257</v>
       </c>
     </row>
     <row r="7">
@@ -44441,31 +44441,31 @@
         <v>541</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.03570210379374206</v>
+        <v>-0.01344816746604435</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.009578344731837609</v>
+        <v>-0.006741872537707046</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05076978909331795</v>
+        <v>0.02398268161668471</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1127972109639531</v>
+        <v>0.02831065997320244</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02053408090624034</v>
+        <v>0.01476087745077484</v>
       </c>
       <c r="J7" t="n">
-        <v>0.09571639037395559</v>
+        <v>0.05659054830586437</v>
       </c>
       <c r="K7" t="n">
-        <v>0.63781498738913</v>
+        <v>0.1435394026783839</v>
       </c>
       <c r="L7" t="n">
-        <v>1.049982134022978</v>
+        <v>0.2008946367202745</v>
       </c>
       <c r="M7" t="n">
-        <v>27.46645589948501</v>
+        <v>12.97463075462642</v>
       </c>
     </row>
     <row r="8">
@@ -44770,31 +44770,31 @@
         <v>346972</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2351708550246405</v>
+        <v>0.1400904022476426</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2441425107964239</v>
+        <v>0.1524200754787934</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2723359196537569</v>
+        <v>0.1750834671216907</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1945568341411266</v>
+        <v>0.1368594374918886</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2555727973443383</v>
+        <v>0.162945694476917</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5360804218992045</v>
+        <v>0.3261291677549812</v>
       </c>
       <c r="K14" t="n">
-        <v>0.6741757549278367</v>
+        <v>0.4437521006114755</v>
       </c>
       <c r="L14" t="n">
-        <v>2.122354221362843</v>
+        <v>2.380097723252358</v>
       </c>
       <c r="M14" t="n">
-        <v>94492.93871410332</v>
+        <v>60749.06075414727</v>
       </c>
     </row>
     <row r="15">
@@ -44817,31 +44817,31 @@
         <v>3333</v>
       </c>
       <c r="E15" t="n">
-        <v>0.03263878598058267</v>
+        <v>0.02796099376427814</v>
       </c>
       <c r="F15" t="n">
-        <v>0.007961901001747422</v>
+        <v>0.013856875464497</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1069900888508562</v>
+        <v>0.05631450116022816</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1419134623101533</v>
+        <v>0.0618005428234778</v>
       </c>
       <c r="I15" t="n">
-        <v>0.05369330673371371</v>
+        <v>0.03571730232768618</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2890445335726665</v>
+        <v>0.1356729579619117</v>
       </c>
       <c r="K15" t="n">
-        <v>0.5596809767943337</v>
+        <v>0.3097114811515815</v>
       </c>
       <c r="L15" t="n">
-        <v>2.344705610186359</v>
+        <v>0.3515730277244986</v>
       </c>
       <c r="M15" t="n">
-        <v>356.5979661399036</v>
+        <v>187.6962323670405</v>
       </c>
     </row>
     <row r="16">
@@ -44864,31 +44864,31 @@
         <v>16771</v>
       </c>
       <c r="E16" t="n">
-        <v>0.02339856217706737</v>
+        <v>0.01878936114897764</v>
       </c>
       <c r="F16" t="n">
-        <v>0.007901293648275395</v>
+        <v>0.01013350643156344</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1035908912320711</v>
+        <v>0.05476949520815459</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1329418433785486</v>
+        <v>0.05570444867779689</v>
       </c>
       <c r="I16" t="n">
-        <v>0.05490770508670897</v>
+        <v>0.03595577457861038</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2696940864309134</v>
+        <v>0.1306094132465415</v>
       </c>
       <c r="K16" t="n">
-        <v>0.544678472730702</v>
+        <v>0.2399236598219245</v>
       </c>
       <c r="L16" t="n">
-        <v>2.28111877347812</v>
+        <v>0.4154748860649209</v>
       </c>
       <c r="M16" t="n">
-        <v>1737.322836853065</v>
+        <v>918.5392041359606</v>
       </c>
     </row>
     <row r="17">
@@ -44911,31 +44911,31 @@
         <v>454</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0344949536232747</v>
+        <v>-0.008482184598650458</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0002022954272336645</v>
+        <v>-0.001455654420912329</v>
       </c>
       <c r="G17" t="n">
-        <v>0.06996574101258422</v>
+        <v>0.03608602292237014</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1808382673586941</v>
+        <v>0.04374369137390754</v>
       </c>
       <c r="I17" t="n">
-        <v>0.02842124020718543</v>
+        <v>0.02127957895919236</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1194260279457285</v>
+        <v>0.0863357653309916</v>
       </c>
       <c r="K17" t="n">
-        <v>0.77836853971799</v>
+        <v>0.22353780550267</v>
       </c>
       <c r="L17" t="n">
-        <v>1.981587652469111</v>
+        <v>0.2940428163528467</v>
       </c>
       <c r="M17" t="n">
-        <v>31.76444641971324</v>
+        <v>16.38305440675605</v>
       </c>
     </row>
     <row r="18">
@@ -44958,31 +44958,31 @@
         <v>1876</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.009066705436654943</v>
+        <v>-0.001059449525574773</v>
       </c>
       <c r="F18" t="n">
-        <v>0.001878950186793679</v>
+        <v>0.0001727654747728064</v>
       </c>
       <c r="G18" t="n">
-        <v>0.07033087403231043</v>
+        <v>0.03710782644970869</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1277283224754122</v>
+        <v>0.04265395180266668</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0334395496011429</v>
+        <v>0.02323884880104567</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1521140402122789</v>
+        <v>0.09007012071642295</v>
       </c>
       <c r="K18" t="n">
-        <v>0.56241624251412</v>
+        <v>0.1975441030943769</v>
       </c>
       <c r="L18" t="n">
-        <v>1.924592586744562</v>
+        <v>0.3245696106076874</v>
       </c>
       <c r="M18" t="n">
-        <v>131.9407196846144</v>
+        <v>69.61428241965351</v>
       </c>
     </row>
     <row r="19">
@@ -45005,31 +45005,31 @@
         <v>569</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.04843525681325966</v>
+        <v>-0.02444373806683799</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.004061765503677471</v>
+        <v>-0.006548193726544356</v>
       </c>
       <c r="G19" t="n">
-        <v>0.07391719172983642</v>
+        <v>0.03704383722599656</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1972340556710573</v>
+        <v>0.05635752080928232</v>
       </c>
       <c r="I19" t="n">
-        <v>0.01984262026713628</v>
+        <v>0.0172339065451951</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1265841919168354</v>
+        <v>0.08732507992279548</v>
       </c>
       <c r="K19" t="n">
-        <v>1.090832072709611</v>
+        <v>0.3008630819940407</v>
       </c>
       <c r="L19" t="n">
-        <v>2.017284702529142</v>
+        <v>0.3302370243441404</v>
       </c>
       <c r="M19" t="n">
-        <v>42.05888209427692</v>
+        <v>21.07794338159204</v>
       </c>
     </row>
     <row r="20">
@@ -45052,31 +45052,31 @@
         <v>1737</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7592377525367193</v>
+        <v>1.454564381822911</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7395111322402954</v>
+        <v>1.442709505558014</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7592377525367193</v>
+        <v>1.454564381822911</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2289338451543399</v>
+        <v>0.2672687695774184</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7395111322402954</v>
+        <v>1.442709505558014</v>
       </c>
       <c r="J20" t="n">
-        <v>1.129810102874762</v>
+        <v>1.977086053974926</v>
       </c>
       <c r="K20" t="n">
-        <v>1.184394913823344</v>
+        <v>2.024245034107007</v>
       </c>
       <c r="L20" t="n">
-        <v>1.197588013252243</v>
+        <v>2.028131218081398</v>
       </c>
       <c r="M20" t="n">
-        <v>1318.795976156282</v>
+        <v>2526.578331226396</v>
       </c>
     </row>
     <row r="21">
@@ -45334,31 +45334,31 @@
         <v>197977</v>
       </c>
       <c r="E26" t="n">
-        <v>0.3300132906016237</v>
+        <v>-0.1025288550433069</v>
       </c>
       <c r="F26" t="n">
-        <v>0.3639516363483244</v>
+        <v>0.01273951103924355</v>
       </c>
       <c r="G26" t="n">
-        <v>0.4257957420298717</v>
+        <v>0.3473446815841759</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2856658847967697</v>
+        <v>0.4892479216278954</v>
       </c>
       <c r="I26" t="n">
-        <v>0.4075183907710034</v>
+        <v>0.2174311320345012</v>
       </c>
       <c r="J26" t="n">
-        <v>0.8013237480888782</v>
+        <v>0.6665011236012062</v>
       </c>
       <c r="K26" t="n">
-        <v>0.9035681452067685</v>
+        <v>2.67186636108186</v>
       </c>
       <c r="L26" t="n">
-        <v>2.962936608432782</v>
+        <v>4.795767843901819</v>
       </c>
       <c r="M26" t="n">
-        <v>84297.76361984792</v>
+        <v>68766.25802599039</v>
       </c>
     </row>
     <row r="27">
@@ -45381,31 +45381,31 @@
         <v>1919</v>
       </c>
       <c r="E27" t="n">
-        <v>0.002192961103810443</v>
+        <v>-0.05005387169851656</v>
       </c>
       <c r="F27" t="n">
-        <v>0.01065775233057826</v>
+        <v>-0.00155345133528837</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1695932526475049</v>
+        <v>0.130931558642799</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2247779560645375</v>
+        <v>0.2682113415449406</v>
       </c>
       <c r="I27" t="n">
-        <v>0.08642152069349854</v>
+        <v>0.05668883601911247</v>
       </c>
       <c r="J27" t="n">
-        <v>0.4382524360993228</v>
+        <v>0.2618372597082222</v>
       </c>
       <c r="K27" t="n">
-        <v>0.9930342913378274</v>
+        <v>1.575869874451109</v>
       </c>
       <c r="L27" t="n">
-        <v>2.8505879284775</v>
+        <v>2.274607107202379</v>
       </c>
       <c r="M27" t="n">
-        <v>325.4494518305619</v>
+        <v>251.2576610355313</v>
       </c>
     </row>
     <row r="28">
@@ -45428,31 +45428,31 @@
         <v>10369</v>
       </c>
       <c r="E28" t="n">
-        <v>0.03462501361763472</v>
+        <v>-0.03242114056221768</v>
       </c>
       <c r="F28" t="n">
-        <v>0.01984479696661006</v>
+        <v>-0.002692705517654829</v>
       </c>
       <c r="G28" t="n">
-        <v>0.2175325455420302</v>
+        <v>0.1271337085924385</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2796270616965709</v>
+        <v>0.232805368764773</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1215041738734115</v>
+        <v>0.06310508346332834</v>
       </c>
       <c r="J28" t="n">
-        <v>0.5391978051629871</v>
+        <v>0.2867062060097905</v>
       </c>
       <c r="K28" t="n">
-        <v>1.37955476541568</v>
+        <v>1.054752653907361</v>
       </c>
       <c r="L28" t="n">
-        <v>4.185497927662548</v>
+        <v>3.60216399716297</v>
       </c>
       <c r="M28" t="n">
-        <v>2255.594964725311</v>
+        <v>1318.249424394995</v>
       </c>
     </row>
     <row r="29">
@@ -45475,31 +45475,31 @@
         <v>323</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.02724081804771799</v>
+        <v>-0.004123633344517573</v>
       </c>
       <c r="F29" t="n">
-        <v>0.006370912189455884</v>
+        <v>-0.000199726565069437</v>
       </c>
       <c r="G29" t="n">
-        <v>0.134700999229628</v>
+        <v>0.05231585897457004</v>
       </c>
       <c r="H29" t="n">
-        <v>0.3329809433170208</v>
+        <v>0.07468700717370316</v>
       </c>
       <c r="I29" t="n">
-        <v>0.04948590669168453</v>
+        <v>0.02621428087315743</v>
       </c>
       <c r="J29" t="n">
-        <v>0.2875447240696021</v>
+        <v>0.1328115611395674</v>
       </c>
       <c r="K29" t="n">
-        <v>2.199345481699155</v>
+        <v>0.4063790128687248</v>
       </c>
       <c r="L29" t="n">
-        <v>3.021229512165444</v>
+        <v>0.4728057232445267</v>
       </c>
       <c r="M29" t="n">
-        <v>43.50842275116983</v>
+        <v>16.89802244878612</v>
       </c>
     </row>
     <row r="30">
@@ -45522,31 +45522,31 @@
         <v>1433</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.01065570570894843</v>
+        <v>-0.005928903972668582</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.003844029638095874</v>
+        <v>0.001460654084984518</v>
       </c>
       <c r="G30" t="n">
-        <v>0.1598139788865898</v>
+        <v>0.07615635354346882</v>
       </c>
       <c r="H30" t="n">
-        <v>0.2426816905184648</v>
+        <v>0.09330111220838375</v>
       </c>
       <c r="I30" t="n">
-        <v>0.08694515590571179</v>
+        <v>0.04460519004464247</v>
       </c>
       <c r="J30" t="n">
-        <v>0.3909495988417658</v>
+        <v>0.1889877600459465</v>
       </c>
       <c r="K30" t="n">
-        <v>0.9365432059965649</v>
+        <v>0.5390750501819386</v>
       </c>
       <c r="L30" t="n">
-        <v>2.960382089919563</v>
+        <v>0.6364683278834913</v>
       </c>
       <c r="M30" t="n">
-        <v>229.0134317444832</v>
+        <v>109.1320546277908</v>
       </c>
     </row>
     <row r="31">
@@ -45569,31 +45569,31 @@
         <v>423</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.1776805950891638</v>
+        <v>-0.01550655412647561</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.01422139278347853</v>
+        <v>-0.00908935592769323</v>
       </c>
       <c r="G31" t="n">
-        <v>0.2362248257740948</v>
+        <v>0.04880685446443005</v>
       </c>
       <c r="H31" t="n">
-        <v>0.6202227981596025</v>
+        <v>0.06293249419556525</v>
       </c>
       <c r="I31" t="n">
-        <v>0.06840632883960844</v>
+        <v>0.02971845711256415</v>
       </c>
       <c r="J31" t="n">
-        <v>0.5202169524452153</v>
+        <v>0.101775652839237</v>
       </c>
       <c r="K31" t="n">
-        <v>2.717184736267176</v>
+        <v>0.3341897339064025</v>
       </c>
       <c r="L31" t="n">
-        <v>7.631818100156119</v>
+        <v>0.5913407123674147</v>
       </c>
       <c r="M31" t="n">
-        <v>99.92310130244212</v>
+        <v>20.64529943845391</v>
       </c>
     </row>
     <row r="32">
@@ -45616,31 +45616,31 @@
         <v>25301</v>
       </c>
       <c r="E32" t="n">
-        <v>0.3436993660952916</v>
+        <v>0.3369704729039495</v>
       </c>
       <c r="F32" t="n">
-        <v>0.2058539390563965</v>
+        <v>0.09019902348518372</v>
       </c>
       <c r="G32" t="n">
-        <v>0.3467991709690598</v>
+        <v>0.3596068774011873</v>
       </c>
       <c r="H32" t="n">
-        <v>0.5261471309117034</v>
+        <v>0.6321219884259661</v>
       </c>
       <c r="I32" t="n">
-        <v>0.2058539390563965</v>
+        <v>0.09828877449035645</v>
       </c>
       <c r="J32" t="n">
-        <v>0.7776806205511093</v>
+        <v>1.224606603384018</v>
       </c>
       <c r="K32" t="n">
-        <v>2.975685179233551</v>
+        <v>2.687528848648071</v>
       </c>
       <c r="L32" t="n">
-        <v>6.475658938288689</v>
+        <v>3.710021734237671</v>
       </c>
       <c r="M32" t="n">
-        <v>8774.365824688182</v>
+        <v>9098.41360512744</v>
       </c>
     </row>
     <row r="33">
@@ -45663,31 +45663,31 @@
         <v>202</v>
       </c>
       <c r="E33" t="n">
-        <v>0.142835863893575</v>
+        <v>0.08963130207935183</v>
       </c>
       <c r="F33" t="n">
-        <v>0.1371677964925766</v>
+        <v>0.05621816217899323</v>
       </c>
       <c r="G33" t="n">
-        <v>0.1453127602834513</v>
+        <v>0.09757998777498113</v>
       </c>
       <c r="H33" t="n">
-        <v>0.1204153562125368</v>
+        <v>0.1843516236501554</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1371677964925766</v>
+        <v>0.0580422580242157</v>
       </c>
       <c r="J33" t="n">
-        <v>0.2850338757038117</v>
+        <v>0.1621373310685158</v>
       </c>
       <c r="K33" t="n">
-        <v>0.3826437181234361</v>
+        <v>0.4487184607982639</v>
       </c>
       <c r="L33" t="n">
-        <v>0.8754383325576782</v>
+        <v>1.893389523029327</v>
       </c>
       <c r="M33" t="n">
-        <v>29.35317757725716</v>
+        <v>19.71115753054619</v>
       </c>
     </row>
     <row r="34">
@@ -45710,31 +45710,31 @@
         <v>1416</v>
       </c>
       <c r="E34" t="n">
-        <v>0.06572601349634977</v>
+        <v>0.03966768121736198</v>
       </c>
       <c r="F34" t="n">
-        <v>0.05669566988945007</v>
+        <v>0.0307600349187851</v>
       </c>
       <c r="G34" t="n">
-        <v>0.08531553250879555</v>
+        <v>0.07703102361095154</v>
       </c>
       <c r="H34" t="n">
-        <v>0.09363891816751831</v>
+        <v>0.1349428702462608</v>
       </c>
       <c r="I34" t="n">
-        <v>0.06457166373729706</v>
+        <v>0.05174455046653748</v>
       </c>
       <c r="J34" t="n">
-        <v>0.1813376396894455</v>
+        <v>0.1568603813648224</v>
       </c>
       <c r="K34" t="n">
-        <v>0.3460698992013904</v>
+        <v>0.3000841230154035</v>
       </c>
       <c r="L34" t="n">
-        <v>1.120536506175995</v>
+        <v>2.008134484291077</v>
       </c>
       <c r="M34" t="n">
-        <v>120.8067940324545</v>
+        <v>109.0759294331074</v>
       </c>
     </row>
     <row r="35">
@@ -45757,31 +45757,31 @@
         <v>13</v>
       </c>
       <c r="E35" t="n">
-        <v>0.02158082907016461</v>
+        <v>-0.001210430493721595</v>
       </c>
       <c r="F35" t="n">
-        <v>0.02172142267227173</v>
+        <v>0.02467793226242065</v>
       </c>
       <c r="G35" t="n">
-        <v>0.05740968539164616</v>
+        <v>0.04033122383631193</v>
       </c>
       <c r="H35" t="n">
-        <v>0.03497088736735924</v>
+        <v>0.02464375393459498</v>
       </c>
       <c r="I35" t="n">
-        <v>0.04853528738021851</v>
+        <v>0.03408312797546387</v>
       </c>
       <c r="J35" t="n">
-        <v>0.1012775003910065</v>
+        <v>0.05235785841941834</v>
       </c>
       <c r="K35" t="n">
-        <v>0.1060339295864105</v>
+        <v>0.1079750728607177</v>
       </c>
       <c r="L35" t="n">
-        <v>0.1066820621490479</v>
+        <v>0.1154310703277588</v>
       </c>
       <c r="M35" t="n">
-        <v>0.7463259100914001</v>
+        <v>0.5243059098720551</v>
       </c>
     </row>
     <row r="36">
@@ -45804,31 +45804,31 @@
         <v>190</v>
       </c>
       <c r="E36" t="n">
-        <v>0.09994457591521112</v>
+        <v>0.07153466806599969</v>
       </c>
       <c r="F36" t="n">
-        <v>0.0529053658246994</v>
+        <v>0.03781722486019135</v>
       </c>
       <c r="G36" t="n">
-        <v>0.1195493435389117</v>
+        <v>0.1033292728819345</v>
       </c>
       <c r="H36" t="n">
-        <v>0.172057129449829</v>
+        <v>0.1620957305248619</v>
       </c>
       <c r="I36" t="n">
-        <v>0.05729100108146667</v>
+        <v>0.04852157831192017</v>
       </c>
       <c r="J36" t="n">
-        <v>0.3829489946365345</v>
+        <v>0.3133840620517716</v>
       </c>
       <c r="K36" t="n">
-        <v>0.6346048480272293</v>
+        <v>0.5948374950885772</v>
       </c>
       <c r="L36" t="n">
-        <v>0.6372301578521729</v>
+        <v>0.607225775718689</v>
       </c>
       <c r="M36" t="n">
-        <v>22.71437527239323</v>
+        <v>19.63256184756756</v>
       </c>
     </row>
     <row r="37">
@@ -45851,31 +45851,31 @@
         <v>50</v>
       </c>
       <c r="E37" t="n">
-        <v>0.07522142946720123</v>
+        <v>0.02908824294805527</v>
       </c>
       <c r="F37" t="n">
-        <v>0.06970894336700439</v>
+        <v>0.0358244776725769</v>
       </c>
       <c r="G37" t="n">
-        <v>0.08381552636623382</v>
+        <v>0.03921179622411728</v>
       </c>
       <c r="H37" t="n">
-        <v>0.0602441036186709</v>
+        <v>0.01711685167130665</v>
       </c>
       <c r="I37" t="n">
-        <v>0.06970894336700439</v>
+        <v>0.03793139755725861</v>
       </c>
       <c r="J37" t="n">
-        <v>0.1674325466156006</v>
+        <v>0.06333740502595901</v>
       </c>
       <c r="K37" t="n">
-        <v>0.2515519177913665</v>
+        <v>0.07224838748574255</v>
       </c>
       <c r="L37" t="n">
-        <v>0.2652631253004074</v>
+        <v>0.0746438205242157</v>
       </c>
       <c r="M37" t="n">
-        <v>4.190776318311691</v>
+        <v>1.960589811205864</v>
       </c>
     </row>
     <row r="38">
@@ -45898,31 +45898,31 @@
         <v>340377</v>
       </c>
       <c r="E38" t="n">
-        <v>0.2087803401453636</v>
+        <v>0.06750152429861719</v>
       </c>
       <c r="F38" t="n">
-        <v>0.2254729656374217</v>
+        <v>0.07790179237562479</v>
       </c>
       <c r="G38" t="n">
-        <v>0.2899299049023725</v>
+        <v>0.1681356383647618</v>
       </c>
       <c r="H38" t="n">
-        <v>0.1992465092592122</v>
+        <v>0.1341299010385572</v>
       </c>
       <c r="I38" t="n">
-        <v>0.2680836020143337</v>
+        <v>0.1388492433667274</v>
       </c>
       <c r="J38" t="n">
-        <v>0.5660282437352957</v>
+        <v>0.3521756718852462</v>
       </c>
       <c r="K38" t="n">
-        <v>0.7168340564467286</v>
+        <v>0.5619801090732415</v>
       </c>
       <c r="L38" t="n">
-        <v>2.370167712620956</v>
+        <v>1.243206545081916</v>
       </c>
       <c r="M38" t="n">
-        <v>98685.47124095485</v>
+        <v>57229.50417968252</v>
       </c>
     </row>
     <row r="39">
@@ -45945,31 +45945,31 @@
         <v>3160</v>
       </c>
       <c r="E39" t="n">
-        <v>0.02501100375234956</v>
+        <v>-0.002617067917720821</v>
       </c>
       <c r="F39" t="n">
-        <v>0.008590757750693252</v>
+        <v>0.004789336549200498</v>
       </c>
       <c r="G39" t="n">
-        <v>0.1359826269623131</v>
+        <v>0.0757205225346258</v>
       </c>
       <c r="H39" t="n">
-        <v>0.1577365853003367</v>
+        <v>0.07819196423888602</v>
       </c>
       <c r="I39" t="n">
-        <v>0.08235399658258896</v>
+        <v>0.05208346715473258</v>
       </c>
       <c r="J39" t="n">
-        <v>0.3561085427255518</v>
+        <v>0.1744407889465234</v>
       </c>
       <c r="K39" t="n">
-        <v>0.5627638092580555</v>
+        <v>0.4253738038602972</v>
       </c>
       <c r="L39" t="n">
-        <v>3.01306533930345</v>
+        <v>0.5022244985016228</v>
       </c>
       <c r="M39" t="n">
-        <v>429.7051012009096</v>
+        <v>239.2768512094175</v>
       </c>
     </row>
     <row r="40">
@@ -45992,31 +45992,31 @@
         <v>16905</v>
       </c>
       <c r="E40" t="n">
-        <v>0.01843437748512012</v>
+        <v>0.002126393423344052</v>
       </c>
       <c r="F40" t="n">
-        <v>0.006457346622051574</v>
+        <v>0.002826342244986424</v>
       </c>
       <c r="G40" t="n">
-        <v>0.1307229611640382</v>
+        <v>0.07999657369835311</v>
       </c>
       <c r="H40" t="n">
-        <v>0.1522834664533081</v>
+        <v>0.08678425843952796</v>
       </c>
       <c r="I40" t="n">
-        <v>0.07559123362629537</v>
+        <v>0.05220799706155965</v>
       </c>
       <c r="J40" t="n">
-        <v>0.343667952455727</v>
+        <v>0.1890449848018919</v>
       </c>
       <c r="K40" t="n">
-        <v>0.6160759835963544</v>
+        <v>0.3999297583267815</v>
       </c>
       <c r="L40" t="n">
-        <v>2.860958586294112</v>
+        <v>0.9523287604814238</v>
       </c>
       <c r="M40" t="n">
-        <v>2209.871658478066</v>
+        <v>1352.342078370659</v>
       </c>
     </row>
     <row r="41">
@@ -46039,31 +46039,31 @@
         <v>457</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.03345435336146242</v>
+        <v>-0.009307860275668352</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.003759733503716568</v>
+        <v>-0.0006048437772747326</v>
       </c>
       <c r="G41" t="n">
-        <v>0.09061702619953807</v>
+        <v>0.05353812971606711</v>
       </c>
       <c r="H41" t="n">
-        <v>0.2176582541900966</v>
+        <v>0.06249270967696656</v>
       </c>
       <c r="I41" t="n">
-        <v>0.04066871748659012</v>
+        <v>0.03247931625325961</v>
       </c>
       <c r="J41" t="n">
-        <v>0.179962578680031</v>
+        <v>0.1350015031879026</v>
       </c>
       <c r="K41" t="n">
-        <v>0.8976159314652842</v>
+        <v>0.2745435325037368</v>
       </c>
       <c r="L41" t="n">
-        <v>3.288448620275771</v>
+        <v>0.35282361697064</v>
       </c>
       <c r="M41" t="n">
-        <v>41.4119809731889</v>
+        <v>24.46692528024267</v>
       </c>
     </row>
     <row r="42">
@@ -46086,31 +46086,31 @@
         <v>1911</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.02076325194746498</v>
+        <v>-0.01380107135981629</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.006410387098841121</v>
+        <v>-0.003614736010584871</v>
       </c>
       <c r="G42" t="n">
-        <v>0.09461797996947377</v>
+        <v>0.06911654275632527</v>
       </c>
       <c r="H42" t="n">
-        <v>0.1480735130317681</v>
+        <v>0.07984768681900051</v>
       </c>
       <c r="I42" t="n">
-        <v>0.0512499773949165</v>
+        <v>0.04344044812514878</v>
       </c>
       <c r="J42" t="n">
-        <v>0.2255496251630499</v>
+        <v>0.1648632131222678</v>
       </c>
       <c r="K42" t="n">
-        <v>0.56310396313971</v>
+        <v>0.2948869043977795</v>
       </c>
       <c r="L42" t="n">
-        <v>2.552944062259586</v>
+        <v>0.6755232576604295</v>
       </c>
       <c r="M42" t="n">
-        <v>180.8149597216644</v>
+        <v>132.0817132073376</v>
       </c>
     </row>
     <row r="43">
@@ -46133,31 +46133,31 @@
         <v>591</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.05279065715775268</v>
+        <v>-0.01560293098890007</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.001094343598584554</v>
+        <v>-0.001064841467587399</v>
       </c>
       <c r="G43" t="n">
-        <v>0.0881945858945444</v>
+        <v>0.04557179954858525</v>
       </c>
       <c r="H43" t="n">
-        <v>0.2965667931704377</v>
+        <v>0.06525226289563438</v>
       </c>
       <c r="I43" t="n">
-        <v>0.02899607217392089</v>
+        <v>0.02185209030964589</v>
       </c>
       <c r="J43" t="n">
-        <v>0.1686148898047338</v>
+        <v>0.1240681692342768</v>
       </c>
       <c r="K43" t="n">
-        <v>1.097380018808432</v>
+        <v>0.2816487033486674</v>
       </c>
       <c r="L43" t="n">
-        <v>4.914401962793144</v>
+        <v>0.5259418453368288</v>
       </c>
       <c r="M43" t="n">
-        <v>52.12300026367574</v>
+        <v>26.93293353321388</v>
       </c>
     </row>
     <row r="44">
@@ -46180,31 +46180,31 @@
         <v>3889</v>
       </c>
       <c r="E44" t="n">
-        <v>0.4927603899163363</v>
+        <v>0.5291665651648471</v>
       </c>
       <c r="F44" t="n">
-        <v>0.5007083415985107</v>
+        <v>0.5431781113147736</v>
       </c>
       <c r="G44" t="n">
-        <v>0.4927603899163363</v>
+        <v>0.5291665651648471</v>
       </c>
       <c r="H44" t="n">
-        <v>0.2459967348923677</v>
+        <v>0.26595378553673</v>
       </c>
       <c r="I44" t="n">
-        <v>0.5007083415985107</v>
+        <v>0.5431781113147736</v>
       </c>
       <c r="J44" t="n">
-        <v>0.8805274147540332</v>
+        <v>0.9051740787923336</v>
       </c>
       <c r="K44" t="n">
-        <v>0.9481720766425132</v>
+        <v>0.9432313042879105</v>
       </c>
       <c r="L44" t="n">
-        <v>0.9573894962668419</v>
+        <v>0.961571216583252</v>
       </c>
       <c r="M44" t="n">
-        <v>1916.345156384632</v>
+        <v>2057.92877192609</v>
       </c>
     </row>
     <row r="45">
@@ -46227,31 +46227,31 @@
         <v>18</v>
       </c>
       <c r="E45" t="n">
-        <v>0.1836401853296492</v>
+        <v>0.1763911015457577</v>
       </c>
       <c r="F45" t="n">
-        <v>0.1861548721790314</v>
+        <v>0.1787703335285187</v>
       </c>
       <c r="G45" t="n">
-        <v>0.1836401853296492</v>
+        <v>0.1763911015457577</v>
       </c>
       <c r="H45" t="n">
-        <v>0.01610406870536586</v>
+        <v>0.01600183890996617</v>
       </c>
       <c r="I45" t="n">
-        <v>0.1861548721790314</v>
+        <v>0.1787703335285187</v>
       </c>
       <c r="J45" t="n">
-        <v>0.1971501648426056</v>
+        <v>0.1915277063846588</v>
       </c>
       <c r="K45" t="n">
-        <v>0.2041641968488693</v>
+        <v>0.1983730274438858</v>
       </c>
       <c r="L45" t="n">
-        <v>0.2047427892684937</v>
+        <v>0.1989456415176392</v>
       </c>
       <c r="M45" t="n">
-        <v>3.305523335933685</v>
+        <v>3.175039827823639</v>
       </c>
     </row>
     <row r="46">
@@ -46274,31 +46274,31 @@
         <v>51</v>
       </c>
       <c r="E46" t="n">
-        <v>0.2780011156026055</v>
+        <v>0.2683267745317197</v>
       </c>
       <c r="F46" t="n">
-        <v>0.2797446846961975</v>
+        <v>0.2754653692245483</v>
       </c>
       <c r="G46" t="n">
-        <v>0.2780011156026055</v>
+        <v>0.2683267745317197</v>
       </c>
       <c r="H46" t="n">
-        <v>0.1597718157234893</v>
+        <v>0.1520516874866244</v>
       </c>
       <c r="I46" t="n">
-        <v>0.2797446846961975</v>
+        <v>0.2754653692245483</v>
       </c>
       <c r="J46" t="n">
-        <v>0.5308985412120819</v>
+        <v>0.4941602051258087</v>
       </c>
       <c r="K46" t="n">
-        <v>0.5583748072385788</v>
+        <v>0.5154527872800827</v>
       </c>
       <c r="L46" t="n">
-        <v>0.5612224638462067</v>
+        <v>0.5191526710987091</v>
       </c>
       <c r="M46" t="n">
-        <v>14.17805689573288</v>
+        <v>13.68466550111771</v>
       </c>
     </row>
     <row r="47">
@@ -46368,31 +46368,31 @@
         <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>0.309478223323822</v>
+        <v>0.3090832829475403</v>
       </c>
       <c r="F48" t="n">
-        <v>0.309478223323822</v>
+        <v>0.3090832829475403</v>
       </c>
       <c r="G48" t="n">
-        <v>0.309478223323822</v>
+        <v>0.3090832829475403</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>0.309478223323822</v>
+        <v>0.3090832829475403</v>
       </c>
       <c r="J48" t="n">
-        <v>0.309478223323822</v>
+        <v>0.3090832829475403</v>
       </c>
       <c r="K48" t="n">
-        <v>0.309478223323822</v>
+        <v>0.3090832829475403</v>
       </c>
       <c r="L48" t="n">
-        <v>0.309478223323822</v>
+        <v>0.3090832829475403</v>
       </c>
       <c r="M48" t="n">
-        <v>0.309478223323822</v>
+        <v>0.3090832829475403</v>
       </c>
     </row>
     <row r="49">
@@ -46462,31 +46462,31 @@
         <v>180696</v>
       </c>
       <c r="E50" t="n">
-        <v>0.2866633494386643</v>
+        <v>-0.2675773907586363</v>
       </c>
       <c r="F50" t="n">
-        <v>0.3485833390835306</v>
+        <v>-0.04967221859713973</v>
       </c>
       <c r="G50" t="n">
-        <v>0.4210839684395128</v>
+        <v>0.4788837136401596</v>
       </c>
       <c r="H50" t="n">
-        <v>0.2707361861790287</v>
+        <v>0.7573022549365174</v>
       </c>
       <c r="I50" t="n">
-        <v>0.4112767759354076</v>
+        <v>0.2714378684193863</v>
       </c>
       <c r="J50" t="n">
-        <v>0.7620085665377729</v>
+        <v>1.055641529431928</v>
       </c>
       <c r="K50" t="n">
-        <v>0.9509949216514376</v>
+        <v>3.391962834965914</v>
       </c>
       <c r="L50" t="n">
-        <v>8.038418351576947</v>
+        <v>10.53718535982954</v>
       </c>
       <c r="M50" t="n">
-        <v>76088.18876114622</v>
+        <v>86532.37151992228</v>
       </c>
     </row>
     <row r="51">
@@ -46509,31 +46509,31 @@
         <v>1678</v>
       </c>
       <c r="E51" t="n">
-        <v>0.02043474106513129</v>
+        <v>-0.02920752840642597</v>
       </c>
       <c r="F51" t="n">
-        <v>0.0249290223711796</v>
+        <v>-0.009587623836217167</v>
       </c>
       <c r="G51" t="n">
-        <v>0.2381039683562096</v>
+        <v>0.1459761980759492</v>
       </c>
       <c r="H51" t="n">
-        <v>0.269769130901068</v>
+        <v>0.1759282211015154</v>
       </c>
       <c r="I51" t="n">
-        <v>0.1666232869511975</v>
+        <v>0.1007430476916822</v>
       </c>
       <c r="J51" t="n">
-        <v>0.5146146864791314</v>
+        <v>0.322577904559168</v>
       </c>
       <c r="K51" t="n">
-        <v>1.284214786912785</v>
+        <v>0.6763250344902976</v>
       </c>
       <c r="L51" t="n">
-        <v>3.472723458172496</v>
+        <v>2.873684503316725</v>
       </c>
       <c r="M51" t="n">
-        <v>399.5384589017197</v>
+        <v>244.9480603714428</v>
       </c>
     </row>
     <row r="52">
@@ -46556,31 +46556,31 @@
         <v>10224</v>
       </c>
       <c r="E52" t="n">
-        <v>0.003945936379961812</v>
+        <v>-0.0761019031405608</v>
       </c>
       <c r="F52" t="n">
-        <v>0.04135446484574174</v>
+        <v>-0.003450795946907542</v>
       </c>
       <c r="G52" t="n">
-        <v>0.2654329396257305</v>
+        <v>0.2054041763991233</v>
       </c>
       <c r="H52" t="n">
-        <v>0.3382236605870074</v>
+        <v>0.3247038336081276</v>
       </c>
       <c r="I52" t="n">
-        <v>0.1748451992855659</v>
+        <v>0.1149669134666673</v>
       </c>
       <c r="J52" t="n">
-        <v>0.58148390037493</v>
+        <v>0.4488837577270557</v>
       </c>
       <c r="K52" t="n">
-        <v>1.616789889165183</v>
+        <v>1.372714436861085</v>
       </c>
       <c r="L52" t="n">
-        <v>5.488741228574937</v>
+        <v>5.351552971659662</v>
       </c>
       <c r="M52" t="n">
-        <v>2713.786374733469</v>
+        <v>2100.052299504636</v>
       </c>
     </row>
     <row r="53">
@@ -46603,31 +46603,31 @@
         <v>304</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.1095019700828449</v>
+        <v>-0.04085920170169659</v>
       </c>
       <c r="F53" t="n">
-        <v>0.001338429959073949</v>
+        <v>-0.0003816682330028241</v>
       </c>
       <c r="G53" t="n">
-        <v>0.2338917627412098</v>
+        <v>0.1313905193425613</v>
       </c>
       <c r="H53" t="n">
-        <v>0.5192109939462279</v>
+        <v>0.2760487266726181</v>
       </c>
       <c r="I53" t="n">
-        <v>0.09169067235069772</v>
+        <v>0.06910010007152746</v>
       </c>
       <c r="J53" t="n">
-        <v>0.4035356780158841</v>
+        <v>0.2794689672120517</v>
       </c>
       <c r="K53" t="n">
-        <v>3.043742816583829</v>
+        <v>1.29329749308633</v>
       </c>
       <c r="L53" t="n">
-        <v>4.47443834468796</v>
+        <v>3.747774881709601</v>
       </c>
       <c r="M53" t="n">
-        <v>71.10309587332777</v>
+        <v>39.94271788013863</v>
       </c>
     </row>
     <row r="54">
@@ -46650,31 +46650,31 @@
         <v>1058</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.09819134528618952</v>
+        <v>-0.07497445671064411</v>
       </c>
       <c r="F54" t="n">
-        <v>0.004053009463313573</v>
+        <v>0.001712979239062139</v>
       </c>
       <c r="G54" t="n">
-        <v>0.2524704751081728</v>
+        <v>0.1803844122234867</v>
       </c>
       <c r="H54" t="n">
-        <v>0.5153019588334113</v>
+        <v>0.330729650331324</v>
       </c>
       <c r="I54" t="n">
-        <v>0.1192505207849813</v>
+        <v>0.07719530559406124</v>
       </c>
       <c r="J54" t="n">
-        <v>0.5041805461353737</v>
+        <v>0.3945799848759154</v>
       </c>
       <c r="K54" t="n">
-        <v>2.992769532898627</v>
+        <v>1.95632569668552</v>
       </c>
       <c r="L54" t="n">
-        <v>5.610500794780256</v>
+        <v>3.26483548737223</v>
       </c>
       <c r="M54" t="n">
-        <v>267.1137626644469</v>
+        <v>190.8467081324489</v>
       </c>
     </row>
     <row r="55">
@@ -46697,31 +46697,31 @@
         <v>365</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.2055657983245755</v>
+        <v>-0.06638932501668435</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.01152123654028746</v>
+        <v>-0.003360471669885585</v>
       </c>
       <c r="G55" t="n">
-        <v>0.2886584258597932</v>
+        <v>0.1370014844698617</v>
       </c>
       <c r="H55" t="n">
-        <v>0.5812331931399614</v>
+        <v>0.2882057291716387</v>
       </c>
       <c r="I55" t="n">
-        <v>0.09307225249254235</v>
+        <v>0.06007295450398255</v>
       </c>
       <c r="J55" t="n">
-        <v>0.7399087426014991</v>
+        <v>0.2797275596777179</v>
       </c>
       <c r="K55" t="n">
-        <v>3.116899433790118</v>
+        <v>1.379855800895055</v>
       </c>
       <c r="L55" t="n">
-        <v>4.46217825514371</v>
+        <v>3.165657868476943</v>
       </c>
       <c r="M55" t="n">
-        <v>105.3603254388245</v>
+        <v>50.0055418314995</v>
       </c>
     </row>
     <row r="56">
@@ -46744,31 +46744,31 @@
         <v>94695</v>
       </c>
       <c r="E56" t="n">
-        <v>0.2287775148959814</v>
+        <v>0.3310316394236164</v>
       </c>
       <c r="F56" t="n">
-        <v>0.1499916017055511</v>
+        <v>0.121021568775177</v>
       </c>
       <c r="G56" t="n">
-        <v>0.2317698325069382</v>
+        <v>0.3394075079687028</v>
       </c>
       <c r="H56" t="n">
-        <v>0.2542471724630556</v>
+        <v>0.5123455505870012</v>
       </c>
       <c r="I56" t="n">
-        <v>0.1500143706798553</v>
+        <v>0.122213751077652</v>
       </c>
       <c r="J56" t="n">
-        <v>0.5265523254871369</v>
+        <v>0.8996961116790776</v>
       </c>
       <c r="K56" t="n">
-        <v>1.192759272456168</v>
+        <v>2.126689580082894</v>
       </c>
       <c r="L56" t="n">
-        <v>3.417383909225464</v>
+        <v>6.218338310718536</v>
       </c>
       <c r="M56" t="n">
-        <v>21947.44428924451</v>
+        <v>32140.19396709631</v>
       </c>
     </row>
     <row r="57">
@@ -46791,31 +46791,31 @@
         <v>968</v>
       </c>
       <c r="E57" t="n">
-        <v>0.1360108630668315</v>
+        <v>0.1733401611029891</v>
       </c>
       <c r="F57" t="n">
-        <v>0.0513283982872963</v>
+        <v>0.03726153075695038</v>
       </c>
       <c r="G57" t="n">
-        <v>0.1435496592153485</v>
+        <v>0.1852510232461175</v>
       </c>
       <c r="H57" t="n">
-        <v>0.2152479336520908</v>
+        <v>0.4176777828908609</v>
       </c>
       <c r="I57" t="n">
-        <v>0.05403780937194824</v>
+        <v>0.04836559295654297</v>
       </c>
       <c r="J57" t="n">
-        <v>0.3847504764795305</v>
+        <v>0.4141416013240818</v>
       </c>
       <c r="K57" t="n">
-        <v>1.234176758229732</v>
+        <v>2.707526684999466</v>
       </c>
       <c r="L57" t="n">
-        <v>1.282383978366852</v>
+        <v>2.719185292720795</v>
       </c>
       <c r="M57" t="n">
-        <v>138.9560701204573</v>
+        <v>179.3229905022417</v>
       </c>
     </row>
     <row r="58">
@@ -46838,31 +46838,31 @@
         <v>4097</v>
       </c>
       <c r="E58" t="n">
-        <v>0.09248109748225647</v>
+        <v>0.09731508128841547</v>
       </c>
       <c r="F58" t="n">
-        <v>0.0348844975233078</v>
+        <v>0.02631294727325439</v>
       </c>
       <c r="G58" t="n">
-        <v>0.1002280355590951</v>
+        <v>0.1088688135379876</v>
       </c>
       <c r="H58" t="n">
-        <v>0.1708445825016242</v>
+        <v>0.2196879722658995</v>
       </c>
       <c r="I58" t="n">
-        <v>0.03870053589344025</v>
+        <v>0.03249561786651611</v>
       </c>
       <c r="J58" t="n">
-        <v>0.26255943775177</v>
+        <v>0.289583569765091</v>
       </c>
       <c r="K58" t="n">
-        <v>0.8388070726394652</v>
+        <v>0.8729657077789306</v>
       </c>
       <c r="L58" t="n">
-        <v>1.706420049071312</v>
+        <v>2.249202996492386</v>
       </c>
       <c r="M58" t="n">
-        <v>410.6342616856127</v>
+        <v>446.0355290651351</v>
       </c>
     </row>
     <row r="59">
@@ -46885,31 +46885,31 @@
         <v>120</v>
       </c>
       <c r="E59" t="n">
-        <v>0.04516854286193848</v>
+        <v>0.04885264796515306</v>
       </c>
       <c r="F59" t="n">
-        <v>0.0104326456785202</v>
+        <v>0.008722379803657532</v>
       </c>
       <c r="G59" t="n">
-        <v>0.0534253180027008</v>
+        <v>0.05665881248811881</v>
       </c>
       <c r="H59" t="n">
-        <v>0.1059828981820506</v>
+        <v>0.1072368659465469</v>
       </c>
       <c r="I59" t="n">
-        <v>0.0164656937122345</v>
+        <v>0.01645179837942123</v>
       </c>
       <c r="J59" t="n">
-        <v>0.1554957807064057</v>
+        <v>0.1692752957344056</v>
       </c>
       <c r="K59" t="n">
-        <v>0.6254631826281557</v>
+        <v>0.6129956454038623</v>
       </c>
       <c r="L59" t="n">
-        <v>0.7244633138179779</v>
+        <v>0.6494264304637909</v>
       </c>
       <c r="M59" t="n">
-        <v>6.411038160324097</v>
+        <v>6.799057498574257</v>
       </c>
     </row>
     <row r="60">
@@ -46932,31 +46932,31 @@
         <v>566</v>
       </c>
       <c r="E60" t="n">
-        <v>0.0283594826242949</v>
+        <v>0.0260724493634785</v>
       </c>
       <c r="F60" t="n">
-        <v>0.01107749342918396</v>
+        <v>0.006965205073356628</v>
       </c>
       <c r="G60" t="n">
-        <v>0.03791594797541312</v>
+        <v>0.03643484665047996</v>
       </c>
       <c r="H60" t="n">
-        <v>0.07392203204279665</v>
+        <v>0.0742877439239928</v>
       </c>
       <c r="I60" t="n">
-        <v>0.0191509872674942</v>
+        <v>0.01857702434062958</v>
       </c>
       <c r="J60" t="n">
-        <v>0.06560666114091873</v>
+        <v>0.07026175409555435</v>
       </c>
       <c r="K60" t="n">
-        <v>0.3665137782692912</v>
+        <v>0.3669515490531928</v>
       </c>
       <c r="L60" t="n">
-        <v>1.066572368144989</v>
+        <v>1.104517877101898</v>
       </c>
       <c r="M60" t="n">
-        <v>21.46042655408382</v>
+        <v>20.62212320417166</v>
       </c>
     </row>
     <row r="61">
@@ -46979,31 +46979,31 @@
         <v>141</v>
       </c>
       <c r="E61" t="n">
-        <v>0.02938163037418474</v>
+        <v>0.02827548124688737</v>
       </c>
       <c r="F61" t="n">
-        <v>0.008752286434173584</v>
+        <v>0.005088865756988525</v>
       </c>
       <c r="G61" t="n">
-        <v>0.03644419931773598</v>
+        <v>0.03632430626568219</v>
       </c>
       <c r="H61" t="n">
-        <v>0.1248138729462022</v>
+        <v>0.1372425310067043</v>
       </c>
       <c r="I61" t="n">
-        <v>0.01214638352394104</v>
+        <v>0.006486117839813232</v>
       </c>
       <c r="J61" t="n">
-        <v>0.06411299109458923</v>
+        <v>0.05252447724342346</v>
       </c>
       <c r="K61" t="n">
-        <v>0.2603423058986661</v>
+        <v>0.3278809249401082</v>
       </c>
       <c r="L61" t="n">
-        <v>1.410838663578033</v>
+        <v>1.540058195590973</v>
       </c>
       <c r="M61" t="n">
-        <v>5.138632103800774</v>
+        <v>5.121727183461189</v>
       </c>
     </row>
     <row r="62">
@@ -47026,31 +47026,31 @@
         <v>210182</v>
       </c>
       <c r="E62" t="n">
-        <v>0.2612934252913322</v>
+        <v>0.04540137277930993</v>
       </c>
       <c r="F62" t="n">
-        <v>0.288807940673567</v>
+        <v>0.06641819806323385</v>
       </c>
       <c r="G62" t="n">
-        <v>0.3263939188683266</v>
+        <v>0.1740209764575232</v>
       </c>
       <c r="H62" t="n">
-        <v>0.2167927223287798</v>
+        <v>0.1817827409117444</v>
       </c>
       <c r="I62" t="n">
-        <v>0.3185590080480414</v>
+        <v>0.1266833461283577</v>
       </c>
       <c r="J62" t="n">
-        <v>0.6230446601369503</v>
+        <v>0.3652304542739755</v>
       </c>
       <c r="K62" t="n">
-        <v>0.7559341525079968</v>
+        <v>0.9451973053962803</v>
       </c>
       <c r="L62" t="n">
-        <v>2.423109636502585</v>
+        <v>2.029819488179555</v>
       </c>
       <c r="M62" t="n">
-        <v>68602.12665558262</v>
+        <v>36576.07687379513</v>
       </c>
     </row>
     <row r="63">
@@ -47073,31 +47073,31 @@
         <v>2176</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.001540859546904615</v>
+        <v>-0.006637841902163578</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.001101925184874804</v>
+        <v>-0.0007209493486718806</v>
       </c>
       <c r="G63" t="n">
-        <v>0.1235529877837644</v>
+        <v>0.06707207278666555</v>
       </c>
       <c r="H63" t="n">
-        <v>0.1505250398398535</v>
+        <v>0.074064749524809</v>
       </c>
       <c r="I63" t="n">
-        <v>0.07308143762417579</v>
+        <v>0.04463837035257599</v>
       </c>
       <c r="J63" t="n">
-        <v>0.3128553092455115</v>
+        <v>0.1574327287817732</v>
       </c>
       <c r="K63" t="n">
-        <v>0.5764565913914892</v>
+        <v>0.3875183433487668</v>
       </c>
       <c r="L63" t="n">
-        <v>2.093828389764664</v>
+        <v>0.6482339049964988</v>
       </c>
       <c r="M63" t="n">
-        <v>268.8513014174714</v>
+        <v>145.9488303837842</v>
       </c>
     </row>
     <row r="64">
@@ -47120,31 +47120,31 @@
         <v>11289</v>
       </c>
       <c r="E64" t="n">
-        <v>0.02405290643721329</v>
+        <v>0.004040705472867773</v>
       </c>
       <c r="F64" t="n">
-        <v>0.01583094791467801</v>
+        <v>0.004254143012500805</v>
       </c>
       <c r="G64" t="n">
-        <v>0.1400057111896069</v>
+        <v>0.07693144175090638</v>
       </c>
       <c r="H64" t="n">
-        <v>0.1657630816034085</v>
+        <v>0.09282568573637713</v>
       </c>
       <c r="I64" t="n">
-        <v>0.08645498196970355</v>
+        <v>0.04762712324651028</v>
       </c>
       <c r="J64" t="n">
-        <v>0.3473786269116547</v>
+        <v>0.1783490542700928</v>
       </c>
       <c r="K64" t="n">
-        <v>0.6459214164005533</v>
+        <v>0.4448677192269481</v>
       </c>
       <c r="L64" t="n">
-        <v>3.458052617535779</v>
+        <v>1.058509131849696</v>
       </c>
       <c r="M64" t="n">
-        <v>1580.524473619473</v>
+        <v>868.4790459259822</v>
       </c>
     </row>
     <row r="65">
@@ -47167,31 +47167,31 @@
         <v>367</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.02645779534579221</v>
+        <v>-0.009263290626887914</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.0007072137260669395</v>
+        <v>-0.002552502706296817</v>
       </c>
       <c r="G65" t="n">
-        <v>0.09558601278707254</v>
+        <v>0.06105678359191161</v>
       </c>
       <c r="H65" t="n">
-        <v>0.1810621693839419</v>
+        <v>0.08136134660227611</v>
       </c>
       <c r="I65" t="n">
-        <v>0.0409291883828643</v>
+        <v>0.02854005353460827</v>
       </c>
       <c r="J65" t="n">
-        <v>0.2149747162619783</v>
+        <v>0.152842716082035</v>
       </c>
       <c r="K65" t="n">
-        <v>0.6380490009165655</v>
+        <v>0.3932931670380414</v>
       </c>
       <c r="L65" t="n">
-        <v>2.19496425726989</v>
+        <v>0.4907498735396403</v>
       </c>
       <c r="M65" t="n">
-        <v>35.08006669285562</v>
+        <v>22.40783957823156</v>
       </c>
     </row>
     <row r="66">
@@ -47214,31 +47214,31 @@
         <v>1145</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.02219060027962171</v>
+        <v>-0.0133562454868614</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.0003535397181340855</v>
+        <v>-0.00249335583649989</v>
       </c>
       <c r="G66" t="n">
-        <v>0.1131965584529326</v>
+        <v>0.06643410689538345</v>
       </c>
       <c r="H66" t="n">
-        <v>0.180570652293489</v>
+        <v>0.07592581103276441</v>
       </c>
       <c r="I66" t="n">
-        <v>0.0561347177305355</v>
+        <v>0.04192794115720443</v>
       </c>
       <c r="J66" t="n">
-        <v>0.2759184745421427</v>
+        <v>0.1663220385803832</v>
       </c>
       <c r="K66" t="n">
-        <v>0.6391216221490539</v>
+        <v>0.3370143743513105</v>
       </c>
       <c r="L66" t="n">
-        <v>3.891849661572965</v>
+        <v>0.719481495682224</v>
       </c>
       <c r="M66" t="n">
-        <v>129.6100594286078</v>
+        <v>76.06705239521406</v>
       </c>
     </row>
     <row r="67">
@@ -47261,31 +47261,31 @@
         <v>397</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.06284055366821713</v>
+        <v>-0.02443163221049829</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.01593697941674309</v>
+        <v>-0.01207937675367613</v>
       </c>
       <c r="G67" t="n">
-        <v>0.09189509036778511</v>
+        <v>0.05069202812132911</v>
       </c>
       <c r="H67" t="n">
-        <v>0.1591335710630983</v>
+        <v>0.05937664045969387</v>
       </c>
       <c r="I67" t="n">
-        <v>0.04004959641868754</v>
+        <v>0.02852483452930319</v>
       </c>
       <c r="J67" t="n">
-        <v>0.2339496805883127</v>
+        <v>0.1216640890355809</v>
       </c>
       <c r="K67" t="n">
-        <v>0.601400039348396</v>
+        <v>0.229021274226581</v>
       </c>
       <c r="L67" t="n">
-        <v>1.916582946102194</v>
+        <v>0.5122263705701994</v>
       </c>
       <c r="M67" t="n">
-        <v>36.48235087601068</v>
+        <v>20.12473516416766</v>
       </c>
     </row>
     <row r="68">
@@ -47308,31 +47308,31 @@
         <v>4659</v>
       </c>
       <c r="E68" t="n">
-        <v>0.7810153493880375</v>
+        <v>1.124038901231521</v>
       </c>
       <c r="F68" t="n">
-        <v>0.8335390985012054</v>
+        <v>1.063153326511383</v>
       </c>
       <c r="G68" t="n">
-        <v>0.7810153493880375</v>
+        <v>1.124038901231521</v>
       </c>
       <c r="H68" t="n">
-        <v>0.2942653263545393</v>
+        <v>0.6512036282808839</v>
       </c>
       <c r="I68" t="n">
-        <v>0.8335390985012054</v>
+        <v>1.063153326511383</v>
       </c>
       <c r="J68" t="n">
-        <v>1.17815486676991</v>
+        <v>1.932712411880493</v>
       </c>
       <c r="K68" t="n">
-        <v>1.262100846767426</v>
+        <v>2.205600972771645</v>
       </c>
       <c r="L68" t="n">
-        <v>1.293378174304962</v>
+        <v>2.224749810993671</v>
       </c>
       <c r="M68" t="n">
-        <v>3638.750512798867</v>
+        <v>5236.897240837655</v>
       </c>
     </row>
     <row r="69">
@@ -47355,31 +47355,31 @@
         <v>28</v>
       </c>
       <c r="E69" t="n">
-        <v>0.4149132094212941</v>
+        <v>0.3556861004659108</v>
       </c>
       <c r="F69" t="n">
-        <v>0.4158017039299011</v>
+        <v>0.3634275496006012</v>
       </c>
       <c r="G69" t="n">
-        <v>0.4149132094212941</v>
+        <v>0.3556861004659108</v>
       </c>
       <c r="H69" t="n">
-        <v>0.06334605605917146</v>
+        <v>0.08729682846625586</v>
       </c>
       <c r="I69" t="n">
-        <v>0.4158017039299011</v>
+        <v>0.3634275496006012</v>
       </c>
       <c r="J69" t="n">
-        <v>0.4345915287733078</v>
+        <v>0.3964599102735519</v>
       </c>
       <c r="K69" t="n">
-        <v>0.6335657453536988</v>
+        <v>0.6173547968268396</v>
       </c>
       <c r="L69" t="n">
-        <v>0.7049559354782104</v>
+        <v>0.6974101662635803</v>
       </c>
       <c r="M69" t="n">
-        <v>11.61756986379623</v>
+        <v>9.959210813045502</v>
       </c>
     </row>
     <row r="70">
@@ -47402,31 +47402,31 @@
         <v>144</v>
       </c>
       <c r="E70" t="n">
-        <v>0.6040005412392525</v>
+        <v>0.6101833347670941</v>
       </c>
       <c r="F70" t="n">
-        <v>0.6241320054978132</v>
+        <v>0.6318279132246971</v>
       </c>
       <c r="G70" t="n">
-        <v>0.6047497236092264</v>
+        <v>0.6109585916856304</v>
       </c>
       <c r="H70" t="n">
-        <v>0.2767300677194764</v>
+        <v>0.2979886921220815</v>
       </c>
       <c r="I70" t="n">
-        <v>0.6241320054978132</v>
+        <v>0.6318279132246971</v>
       </c>
       <c r="J70" t="n">
-        <v>0.9755508661270145</v>
+        <v>0.9939690470695497</v>
       </c>
       <c r="K70" t="n">
-        <v>1.165277987420559</v>
+        <v>1.207027626335621</v>
       </c>
       <c r="L70" t="n">
-        <v>1.198980242013931</v>
+        <v>1.254670172929764</v>
       </c>
       <c r="M70" t="n">
-        <v>87.08396019972861</v>
+        <v>87.97803720273077</v>
       </c>
     </row>
     <row r="71">
@@ -47496,31 +47496,31 @@
         <v>10</v>
       </c>
       <c r="E72" t="n">
-        <v>0.3739948265429121</v>
+        <v>0.3594844572420698</v>
       </c>
       <c r="F72" t="n">
-        <v>0.3721111416816711</v>
+        <v>0.3550328097335296</v>
       </c>
       <c r="G72" t="n">
-        <v>0.3739948265429121</v>
+        <v>0.3594844572420698</v>
       </c>
       <c r="H72" t="n">
-        <v>0.06669348728454229</v>
+        <v>0.06027665719011654</v>
       </c>
       <c r="I72" t="n">
-        <v>0.3721111416816711</v>
+        <v>0.3550328097335296</v>
       </c>
       <c r="J72" t="n">
-        <v>0.4424056013463996</v>
+        <v>0.420036121213343</v>
       </c>
       <c r="K72" t="n">
-        <v>0.4985915770486463</v>
+        <v>0.4800518407777418</v>
       </c>
       <c r="L72" t="n">
-        <v>0.5048344632377848</v>
+        <v>0.4867202540626749</v>
       </c>
       <c r="M72" t="n">
-        <v>3.739948265429121</v>
+        <v>3.594844572420698</v>
       </c>
     </row>
     <row r="73">
@@ -47543,31 +47543,31 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>0.3318519537958006</v>
+        <v>0.3174147750250995</v>
       </c>
       <c r="F73" t="n">
-        <v>0.3340818122960627</v>
+        <v>0.3214139775373042</v>
       </c>
       <c r="G73" t="n">
-        <v>0.3318519537958006</v>
+        <v>0.3174147750250995</v>
       </c>
       <c r="H73" t="n">
-        <v>0.2455258110582875</v>
+        <v>0.2417207761971144</v>
       </c>
       <c r="I73" t="n">
-        <v>0.3340818122960627</v>
+        <v>0.3214139775373042</v>
       </c>
       <c r="J73" t="n">
-        <v>0.5719662037678063</v>
+        <v>0.5534357515163719</v>
       </c>
       <c r="K73" t="n">
-        <v>0.6254901918489486</v>
+        <v>0.6056406506616622</v>
       </c>
       <c r="L73" t="n">
-        <v>0.6314373016357422</v>
+        <v>0.6114411950111389</v>
       </c>
       <c r="M73" t="n">
-        <v>0.9955558613874018</v>
+        <v>0.9522443250752985</v>
       </c>
     </row>
     <row r="74">
@@ -47590,31 +47590,31 @@
         <v>157433</v>
       </c>
       <c r="E74" t="n">
-        <v>0.2210011548500336</v>
+        <v>-0.06231717926887322</v>
       </c>
       <c r="F74" t="n">
-        <v>0.217827611578167</v>
+        <v>-0.003527725108509939</v>
       </c>
       <c r="G74" t="n">
-        <v>0.295044612603662</v>
+        <v>0.2191679971565552</v>
       </c>
       <c r="H74" t="n">
-        <v>0.2200735233047125</v>
+        <v>0.2460590785919051</v>
       </c>
       <c r="I74" t="n">
-        <v>0.2533066595241715</v>
+        <v>0.1489083517872617</v>
       </c>
       <c r="J74" t="n">
-        <v>0.6058398907059479</v>
+        <v>0.4619938154099488</v>
       </c>
       <c r="K74" t="n">
-        <v>0.7894127918378073</v>
+        <v>1.300625661551914</v>
       </c>
       <c r="L74" t="n">
-        <v>2.499162222240659</v>
+        <v>1.996368164816265</v>
       </c>
       <c r="M74" t="n">
-        <v>46449.75849603233</v>
+        <v>34504.27529634796</v>
       </c>
     </row>
     <row r="75">
@@ -47637,31 +47637,31 @@
         <v>1576</v>
       </c>
       <c r="E75" t="n">
-        <v>0.00609077018930603</v>
+        <v>-0.005210590087933324</v>
       </c>
       <c r="F75" t="n">
-        <v>0.007244354211393094</v>
+        <v>0.004556298833417663</v>
       </c>
       <c r="G75" t="n">
-        <v>0.1215185704505562</v>
+        <v>0.08396986168618147</v>
       </c>
       <c r="H75" t="n">
-        <v>0.1468033782501536</v>
+        <v>0.09854928975402828</v>
       </c>
       <c r="I75" t="n">
-        <v>0.07005638910101719</v>
+        <v>0.05379580019370091</v>
       </c>
       <c r="J75" t="n">
-        <v>0.289877558471293</v>
+        <v>0.1858073635937184</v>
       </c>
       <c r="K75" t="n">
-        <v>0.7833576608533352</v>
+        <v>0.4400152925005313</v>
       </c>
       <c r="L75" t="n">
-        <v>1.204655886741155</v>
+        <v>0.922916796249491</v>
       </c>
       <c r="M75" t="n">
-        <v>191.5132670300765</v>
+        <v>132.336502017422</v>
       </c>
     </row>
     <row r="76">
@@ -47684,31 +47684,31 @@
         <v>8727</v>
       </c>
       <c r="E76" t="n">
-        <v>0.02321905027250675</v>
+        <v>-0.005398169668509943</v>
       </c>
       <c r="F76" t="n">
-        <v>0.01570268207133939</v>
+        <v>0.001535297310935935</v>
       </c>
       <c r="G76" t="n">
-        <v>0.1234537493116434</v>
+        <v>0.08185524779080994</v>
       </c>
       <c r="H76" t="n">
-        <v>0.1291029928613309</v>
+        <v>0.08313206969756207</v>
       </c>
       <c r="I76" t="n">
-        <v>0.08103853655422344</v>
+        <v>0.05873209422764723</v>
       </c>
       <c r="J76" t="n">
-        <v>0.2924487269068834</v>
+        <v>0.1798309138966468</v>
       </c>
       <c r="K76" t="n">
-        <v>0.5701718529600532</v>
+        <v>0.3774681434569089</v>
       </c>
       <c r="L76" t="n">
-        <v>1.200053153926703</v>
+        <v>1.126154809240042</v>
       </c>
       <c r="M76" t="n">
-        <v>1077.380870242712</v>
+        <v>714.3507474703983</v>
       </c>
     </row>
     <row r="77">
@@ -47731,31 +47731,31 @@
         <v>284</v>
       </c>
       <c r="E77" t="n">
-        <v>-0.02300556631296964</v>
+        <v>-0.01135897632915325</v>
       </c>
       <c r="F77" t="n">
-        <v>0.001256155054388803</v>
+        <v>0.0004070654817605349</v>
       </c>
       <c r="G77" t="n">
-        <v>0.08632552647586568</v>
+        <v>0.06583971450114696</v>
       </c>
       <c r="H77" t="n">
-        <v>0.1297308322383657</v>
+        <v>0.07538389331021275</v>
       </c>
       <c r="I77" t="n">
-        <v>0.04627027972460131</v>
+        <v>0.03919812605643383</v>
       </c>
       <c r="J77" t="n">
-        <v>0.2117910359592839</v>
+        <v>0.1570526021203657</v>
       </c>
       <c r="K77" t="n">
-        <v>0.4902492257334843</v>
+        <v>0.3517500765213514</v>
       </c>
       <c r="L77" t="n">
-        <v>1.29145465115188</v>
+        <v>0.408705585434239</v>
       </c>
       <c r="M77" t="n">
-        <v>24.51644951914585</v>
+        <v>18.69847891832574</v>
       </c>
     </row>
     <row r="78">
@@ -47778,31 +47778,31 @@
         <v>1043</v>
       </c>
       <c r="E78" t="n">
-        <v>-0.005613645056829367</v>
+        <v>-0.006896338988076313</v>
       </c>
       <c r="F78" t="n">
-        <v>0.001137904107481029</v>
+        <v>-0.0006449514983122869</v>
       </c>
       <c r="G78" t="n">
-        <v>0.09855873682689224</v>
+        <v>0.06114420426311755</v>
       </c>
       <c r="H78" t="n">
-        <v>0.111651886807848</v>
+        <v>0.06508595804935127</v>
       </c>
       <c r="I78" t="n">
-        <v>0.057080183047309</v>
+        <v>0.03771074952648591</v>
       </c>
       <c r="J78" t="n">
-        <v>0.2383205602426909</v>
+        <v>0.1509950964155938</v>
       </c>
       <c r="K78" t="n">
-        <v>0.5267904938747353</v>
+        <v>0.2931434372242224</v>
       </c>
       <c r="L78" t="n">
-        <v>0.7416042999508997</v>
+        <v>0.4729126947189212</v>
       </c>
       <c r="M78" t="n">
-        <v>102.7967625104486</v>
+        <v>63.77340504643161</v>
       </c>
     </row>
     <row r="79">
@@ -47825,31 +47825,31 @@
         <v>354</v>
       </c>
       <c r="E79" t="n">
-        <v>-0.03012958307724081</v>
+        <v>-0.006384515428949435</v>
       </c>
       <c r="F79" t="n">
-        <v>-0.002555047218623952</v>
+        <v>-0.001639729776653122</v>
       </c>
       <c r="G79" t="n">
-        <v>0.08107724002530653</v>
+        <v>0.04893560072117154</v>
       </c>
       <c r="H79" t="n">
-        <v>0.1217100654532781</v>
+        <v>0.05518588510813115</v>
       </c>
       <c r="I79" t="n">
-        <v>0.04412346861969188</v>
+        <v>0.03075927520649516</v>
       </c>
       <c r="J79" t="n">
-        <v>0.1919125316815146</v>
+        <v>0.1170530214992664</v>
       </c>
       <c r="K79" t="n">
-        <v>0.5136490462157519</v>
+        <v>0.2662593865250411</v>
       </c>
       <c r="L79" t="n">
-        <v>1.046917655395041</v>
+        <v>0.3360880478152226</v>
       </c>
       <c r="M79" t="n">
-        <v>28.70134296895851</v>
+        <v>17.32320265529473</v>
       </c>
     </row>
     <row r="80">
@@ -47872,31 +47872,31 @@
         <v>3211</v>
       </c>
       <c r="E80" t="n">
-        <v>0.2744689203615465</v>
+        <v>0.2199676464982064</v>
       </c>
       <c r="F80" t="n">
-        <v>0.2487210929393768</v>
+        <v>0.1798008978366852</v>
       </c>
       <c r="G80" t="n">
-        <v>0.278363505318617</v>
+        <v>0.2236986826398743</v>
       </c>
       <c r="H80" t="n">
-        <v>0.1818890195124295</v>
+        <v>0.1893593340810526</v>
       </c>
       <c r="I80" t="n">
-        <v>0.2487210929393768</v>
+        <v>0.1798008978366852</v>
       </c>
       <c r="J80" t="n">
-        <v>0.5368506908416748</v>
+        <v>0.4849430918693542</v>
       </c>
       <c r="K80" t="n">
-        <v>0.6129107594490052</v>
+        <v>0.843031930923462</v>
       </c>
       <c r="L80" t="n">
-        <v>0.6203942894935608</v>
+        <v>0.8981576561927795</v>
       </c>
       <c r="M80" t="n">
-        <v>893.8252155780792</v>
+        <v>718.2964699566364</v>
       </c>
     </row>
     <row r="81">
@@ -47919,31 +47919,31 @@
         <v>44</v>
       </c>
       <c r="E81" t="n">
-        <v>0.1510029455477541</v>
+        <v>0.1027405383912</v>
       </c>
       <c r="F81" t="n">
-        <v>0.1290188878774643</v>
+        <v>0.108754962682724</v>
       </c>
       <c r="G81" t="n">
-        <v>0.1510029455477541</v>
+        <v>0.1027405383912</v>
       </c>
       <c r="H81" t="n">
-        <v>0.09030725667071891</v>
+        <v>0.0396631362500005</v>
       </c>
       <c r="I81" t="n">
-        <v>0.1290188878774643</v>
+        <v>0.108754962682724</v>
       </c>
       <c r="J81" t="n">
-        <v>0.2853158295154572</v>
+        <v>0.1556171208620071</v>
       </c>
       <c r="K81" t="n">
-        <v>0.3427921319007873</v>
+        <v>0.1623862093687058</v>
       </c>
       <c r="L81" t="n">
-        <v>0.3505465388298035</v>
+        <v>0.1636508703231812</v>
       </c>
       <c r="M81" t="n">
-        <v>6.644129604101181</v>
+        <v>4.520583689212799</v>
       </c>
     </row>
     <row r="82">
@@ -47966,31 +47966,31 @@
         <v>317</v>
       </c>
       <c r="E82" t="n">
-        <v>0.05420153722025994</v>
+        <v>0.04845347652675978</v>
       </c>
       <c r="F82" t="n">
-        <v>0.05959427356719971</v>
+        <v>0.0435962975025177</v>
       </c>
       <c r="G82" t="n">
-        <v>0.07877172459187191</v>
+        <v>0.0713409638555268</v>
       </c>
       <c r="H82" t="n">
-        <v>0.06225110977029907</v>
+        <v>0.06125132105333593</v>
       </c>
       <c r="I82" t="n">
-        <v>0.06751313805580139</v>
+        <v>0.0574568510055542</v>
       </c>
       <c r="J82" t="n">
-        <v>0.1276228547096253</v>
+        <v>0.1288140237331391</v>
       </c>
       <c r="K82" t="n">
-        <v>0.3158857035636898</v>
+        <v>0.3078087067604053</v>
       </c>
       <c r="L82" t="n">
-        <v>0.4319264590740204</v>
+        <v>0.4240322411060333</v>
       </c>
       <c r="M82" t="n">
-        <v>24.9706366956234</v>
+        <v>22.615085542202</v>
       </c>
     </row>
     <row r="83">
@@ -48013,31 +48013,31 @@
         <v>2</v>
       </c>
       <c r="E83" t="n">
-        <v>0.05480575561523438</v>
+        <v>0.05716539919376373</v>
       </c>
       <c r="F83" t="n">
-        <v>0.05480575561523438</v>
+        <v>0.05716539919376373</v>
       </c>
       <c r="G83" t="n">
-        <v>0.05480575561523438</v>
+        <v>0.05716539919376373</v>
       </c>
       <c r="H83" t="n">
-        <v>0.0002753138542175293</v>
+        <v>0.002127960324287415</v>
       </c>
       <c r="I83" t="n">
-        <v>0.05480575561523438</v>
+        <v>0.05716539919376373</v>
       </c>
       <c r="J83" t="n">
-        <v>0.0550260066986084</v>
+        <v>0.05886776745319366</v>
       </c>
       <c r="K83" t="n">
-        <v>0.05507556319236755</v>
+        <v>0.0592508003115654</v>
       </c>
       <c r="L83" t="n">
-        <v>0.0550810694694519</v>
+        <v>0.05929335951805115</v>
       </c>
       <c r="M83" t="n">
-        <v>0.1096115112304688</v>
+        <v>0.1143307983875275</v>
       </c>
     </row>
     <row r="84">
@@ -48060,31 +48060,31 @@
         <v>48</v>
       </c>
       <c r="E84" t="n">
-        <v>0.05266152136027813</v>
+        <v>0.04334461813171705</v>
       </c>
       <c r="F84" t="n">
-        <v>0.05485044419765472</v>
+        <v>0.04444931447505951</v>
       </c>
       <c r="G84" t="n">
-        <v>0.05789720950027307</v>
+        <v>0.04885452364881834</v>
       </c>
       <c r="H84" t="n">
-        <v>0.0317042961355543</v>
+        <v>0.03123732126056294</v>
       </c>
       <c r="I84" t="n">
-        <v>0.05749957263469696</v>
+        <v>0.04444931447505951</v>
       </c>
       <c r="J84" t="n">
-        <v>0.08551006019115448</v>
+        <v>0.07953106462955475</v>
       </c>
       <c r="K84" t="n">
-        <v>0.157141864001751</v>
+        <v>0.1567121064662934</v>
       </c>
       <c r="L84" t="n">
-        <v>0.1868128478527069</v>
+        <v>0.1867576539516449</v>
       </c>
       <c r="M84" t="n">
-        <v>2.779066056013107</v>
+        <v>2.34501713514328</v>
       </c>
     </row>
     <row r="85">
@@ -48107,31 +48107,31 @@
         <v>17</v>
       </c>
       <c r="E85" t="n">
-        <v>0.04416930324891034</v>
+        <v>0.02756306178429548</v>
       </c>
       <c r="F85" t="n">
-        <v>0.04568237066268921</v>
+        <v>0.02222010493278503</v>
       </c>
       <c r="G85" t="n">
-        <v>0.05028162283055922</v>
+        <v>0.03429683341699488</v>
       </c>
       <c r="H85" t="n">
-        <v>0.01602277702351795</v>
+        <v>0.02261579702787745</v>
       </c>
       <c r="I85" t="n">
-        <v>0.04568237066268921</v>
+        <v>0.02688592672348022</v>
       </c>
       <c r="J85" t="n">
-        <v>0.06960551738739014</v>
+        <v>0.0717552661895752</v>
       </c>
       <c r="K85" t="n">
-        <v>0.08501960039138794</v>
+        <v>0.08886822819709778</v>
       </c>
       <c r="L85" t="n">
-        <v>0.08665972948074341</v>
+        <v>0.09193900227546692</v>
       </c>
       <c r="M85" t="n">
-        <v>0.8547875881195068</v>
+        <v>0.583046168088913</v>
       </c>
     </row>
     <row r="86">
@@ -48154,31 +48154,31 @@
         <v>198207</v>
       </c>
       <c r="E86" t="n">
-        <v>0.3695083483777208</v>
+        <v>-0.1084297543146057</v>
       </c>
       <c r="F86" t="n">
-        <v>0.4156857800754254</v>
+        <v>-0.01448944417315789</v>
       </c>
       <c r="G86" t="n">
-        <v>0.4200226678237394</v>
+        <v>0.2553675742668539</v>
       </c>
       <c r="H86" t="n">
-        <v>0.2574842357190434</v>
+        <v>0.3301279413145364</v>
       </c>
       <c r="I86" t="n">
-        <v>0.4281275431703737</v>
+        <v>0.1572649138260204</v>
       </c>
       <c r="J86" t="n">
-        <v>0.7610618057992645</v>
+        <v>0.5460276580127109</v>
       </c>
       <c r="K86" t="n">
-        <v>0.8488041631547207</v>
+        <v>1.779621973473567</v>
       </c>
       <c r="L86" t="n">
-        <v>2.720978463010328</v>
+        <v>4.054564235607326</v>
       </c>
       <c r="M86" t="n">
-        <v>83251.43292133992</v>
+        <v>50615.64079271031</v>
       </c>
     </row>
     <row r="87">
@@ -48201,31 +48201,31 @@
         <v>1955</v>
       </c>
       <c r="E87" t="n">
-        <v>0.06753283487932767</v>
+        <v>-0.03601850711285888</v>
       </c>
       <c r="F87" t="n">
-        <v>0.03264851487231343</v>
+        <v>-0.007935661768548773</v>
       </c>
       <c r="G87" t="n">
-        <v>0.1783022389885569</v>
+        <v>0.09002356080312951</v>
       </c>
       <c r="H87" t="n">
-        <v>0.1669997365512211</v>
+        <v>0.1093858577791425</v>
       </c>
       <c r="I87" t="n">
-        <v>0.1268764315707564</v>
+        <v>0.04933922996671627</v>
       </c>
       <c r="J87" t="n">
-        <v>0.4134178375235049</v>
+        <v>0.239331837204229</v>
       </c>
       <c r="K87" t="n">
-        <v>0.6912282162503398</v>
+        <v>0.4512574285031442</v>
       </c>
       <c r="L87" t="n">
-        <v>1.193544599017712</v>
+        <v>1.105587229714984</v>
       </c>
       <c r="M87" t="n">
-        <v>348.5808772226288</v>
+        <v>175.9960613701182</v>
       </c>
     </row>
     <row r="88">
@@ -48248,31 +48248,31 @@
         <v>10948</v>
       </c>
       <c r="E88" t="n">
-        <v>0.05623884038713232</v>
+        <v>-0.02362573393897654</v>
       </c>
       <c r="F88" t="n">
-        <v>0.04632362016262796</v>
+        <v>0.0007917814652098935</v>
       </c>
       <c r="G88" t="n">
-        <v>0.2002190240515587</v>
+        <v>0.1049702954422519</v>
       </c>
       <c r="H88" t="n">
-        <v>0.2087685583020739</v>
+        <v>0.143628752723844</v>
       </c>
       <c r="I88" t="n">
-        <v>0.1319563069701588</v>
+        <v>0.0616844515102456</v>
       </c>
       <c r="J88" t="n">
-        <v>0.4726891719460233</v>
+        <v>0.237065520643701</v>
       </c>
       <c r="K88" t="n">
-        <v>0.8989997539014571</v>
+        <v>0.7285050905825844</v>
       </c>
       <c r="L88" t="n">
-        <v>3.243426331299041</v>
+        <v>1.441243921558894</v>
       </c>
       <c r="M88" t="n">
-        <v>2191.997875316465</v>
+        <v>1149.214794501773</v>
       </c>
     </row>
     <row r="89">
@@ -48295,31 +48295,31 @@
         <v>324</v>
       </c>
       <c r="E89" t="n">
-        <v>-0.05431485296104344</v>
+        <v>-0.003514527914631406</v>
       </c>
       <c r="F89" t="n">
-        <v>0.0004771860791829624</v>
+        <v>0.001381548069964108</v>
       </c>
       <c r="G89" t="n">
-        <v>0.1682531891398856</v>
+        <v>0.05466833828863601</v>
       </c>
       <c r="H89" t="n">
-        <v>0.2618107577830485</v>
+        <v>0.05743562986065493</v>
       </c>
       <c r="I89" t="n">
-        <v>0.09035896975572853</v>
+        <v>0.03687842693291149</v>
       </c>
       <c r="J89" t="n">
-        <v>0.3441247148880345</v>
+        <v>0.127058335609484</v>
       </c>
       <c r="K89" t="n">
-        <v>1.146382320692295</v>
+        <v>0.2472117138986989</v>
       </c>
       <c r="L89" t="n">
-        <v>2.745071648392072</v>
+        <v>0.2699191445499834</v>
       </c>
       <c r="M89" t="n">
-        <v>54.51403328132294</v>
+        <v>17.71254160551807</v>
       </c>
     </row>
     <row r="90">
@@ -48342,31 +48342,31 @@
         <v>1110</v>
       </c>
       <c r="E90" t="n">
-        <v>-0.009688299251352948</v>
+        <v>-0.009186314840467967</v>
       </c>
       <c r="F90" t="n">
-        <v>0.00912607481008551</v>
+        <v>-0.0005401152624855397</v>
       </c>
       <c r="G90" t="n">
-        <v>0.1526248615055347</v>
+        <v>0.08425790283433586</v>
       </c>
       <c r="H90" t="n">
-        <v>0.2235929259511862</v>
+        <v>0.1136294845710175</v>
       </c>
       <c r="I90" t="n">
-        <v>0.08859646769453342</v>
+        <v>0.0412720689008599</v>
       </c>
       <c r="J90" t="n">
-        <v>0.358065812949434</v>
+        <v>0.2100872245150167</v>
       </c>
       <c r="K90" t="n">
-        <v>1.053144845409641</v>
+        <v>0.5508150497590539</v>
       </c>
       <c r="L90" t="n">
-        <v>4.129177664231745</v>
+        <v>0.9424822995202957</v>
       </c>
       <c r="M90" t="n">
-        <v>169.4135962711435</v>
+        <v>93.5262721461128</v>
       </c>
     </row>
     <row r="91">
@@ -48389,31 +48389,31 @@
         <v>367</v>
       </c>
       <c r="E91" t="n">
-        <v>-0.1155100571715192</v>
+        <v>-0.009865069985845782</v>
       </c>
       <c r="F91" t="n">
-        <v>-0.01815857188203698</v>
+        <v>-0.001342344085840788</v>
       </c>
       <c r="G91" t="n">
-        <v>0.1831976456405261</v>
+        <v>0.05647018423478301</v>
       </c>
       <c r="H91" t="n">
-        <v>0.3745664983422245</v>
+        <v>0.08031786190564888</v>
       </c>
       <c r="I91" t="n">
-        <v>0.08044778349380935</v>
+        <v>0.02952017232565331</v>
       </c>
       <c r="J91" t="n">
-        <v>0.4782198265417524</v>
+        <v>0.127411833902573</v>
       </c>
       <c r="K91" t="n">
-        <v>1.262215828894065</v>
+        <v>0.4383964189330244</v>
       </c>
       <c r="L91" t="n">
-        <v>4.42384913837086</v>
+        <v>0.4820897466125609</v>
       </c>
       <c r="M91" t="n">
-        <v>67.23353595007308</v>
+        <v>20.72455761416537</v>
       </c>
     </row>
     <row r="92">
@@ -48436,31 +48436,31 @@
         <v>20434</v>
       </c>
       <c r="E92" t="n">
-        <v>0.3097934844515605</v>
+        <v>0.5533409015258857</v>
       </c>
       <c r="F92" t="n">
-        <v>0.2547633238136768</v>
+        <v>0.4221763014793396</v>
       </c>
       <c r="G92" t="n">
-        <v>0.3160863209688456</v>
+        <v>0.5596398471429758</v>
       </c>
       <c r="H92" t="n">
-        <v>0.2808142409669299</v>
+        <v>0.5516085464059312</v>
       </c>
       <c r="I92" t="n">
-        <v>0.2547633238136768</v>
+        <v>0.4221763014793396</v>
       </c>
       <c r="J92" t="n">
-        <v>0.627305492013693</v>
+        <v>1.336280769109726</v>
       </c>
       <c r="K92" t="n">
-        <v>1.564366452842944</v>
+        <v>2.458656559437512</v>
       </c>
       <c r="L92" t="n">
-        <v>2.108025431632996</v>
+        <v>2.987923845648766</v>
       </c>
       <c r="M92" t="n">
-        <v>6458.907882677391</v>
+        <v>11435.68063651957</v>
       </c>
     </row>
     <row r="93">
@@ -48483,31 +48483,31 @@
         <v>273</v>
       </c>
       <c r="E93" t="n">
-        <v>0.09559138995960301</v>
+        <v>0.06916838279164536</v>
       </c>
       <c r="F93" t="n">
-        <v>0.09843835234642029</v>
+        <v>0.05499283224344254</v>
       </c>
       <c r="G93" t="n">
-        <v>0.118227839449441</v>
+        <v>0.09353186005228387</v>
       </c>
       <c r="H93" t="n">
-        <v>0.08894446118552474</v>
+        <v>0.09548376026825428</v>
       </c>
       <c r="I93" t="n">
-        <v>0.1052609346807003</v>
+        <v>0.06359253823757172</v>
       </c>
       <c r="J93" t="n">
-        <v>0.2381200503557921</v>
+        <v>0.1859775006771088</v>
       </c>
       <c r="K93" t="n">
-        <v>0.4019138836860656</v>
+        <v>0.4667626237869261</v>
       </c>
       <c r="L93" t="n">
-        <v>0.4076554179191589</v>
+        <v>0.4751025438308716</v>
       </c>
       <c r="M93" t="n">
-        <v>32.2762001696974</v>
+        <v>25.5341977942735</v>
       </c>
     </row>
     <row r="94">
@@ -48530,31 +48530,31 @@
         <v>1111</v>
       </c>
       <c r="E94" t="n">
-        <v>0.08942901133203378</v>
+        <v>0.1160491596166343</v>
       </c>
       <c r="F94" t="n">
-        <v>0.06362152099609375</v>
+        <v>0.04425889253616333</v>
       </c>
       <c r="G94" t="n">
-        <v>0.1015361233352005</v>
+        <v>0.1314035678880908</v>
       </c>
       <c r="H94" t="n">
-        <v>0.09643656969345997</v>
+        <v>0.1947065289609738</v>
       </c>
       <c r="I94" t="n">
-        <v>0.07164677977561951</v>
+        <v>0.05168677866458893</v>
       </c>
       <c r="J94" t="n">
-        <v>0.2156399190425873</v>
+        <v>0.3704605102539062</v>
       </c>
       <c r="K94" t="n">
-        <v>0.5002710148692131</v>
+        <v>0.9513797402381897</v>
       </c>
       <c r="L94" t="n">
-        <v>0.5223894268274307</v>
+        <v>1.364548563957214</v>
       </c>
       <c r="M94" t="n">
-        <v>112.8066330254078</v>
+        <v>145.9893639236689</v>
       </c>
     </row>
     <row r="95">
@@ -48577,31 +48577,31 @@
         <v>59</v>
       </c>
       <c r="E95" t="n">
-        <v>0.06139091187614506</v>
+        <v>0.04755756587295209</v>
       </c>
       <c r="F95" t="n">
-        <v>0.03168120980262756</v>
+        <v>0.01267385482788086</v>
       </c>
       <c r="G95" t="n">
-        <v>0.06420053743709953</v>
+        <v>0.05359941039044978</v>
       </c>
       <c r="H95" t="n">
-        <v>0.06942384928830123</v>
+        <v>0.07955871445398027</v>
       </c>
       <c r="I95" t="n">
-        <v>0.03168120980262756</v>
+        <v>0.01703539490699768</v>
       </c>
       <c r="J95" t="n">
-        <v>0.1683460891246796</v>
+        <v>0.1436116695404053</v>
       </c>
       <c r="K95" t="n">
-        <v>0.2533300030231477</v>
+        <v>0.3366567033529284</v>
       </c>
       <c r="L95" t="n">
-        <v>0.2773351669311523</v>
+        <v>0.4039902687072754</v>
       </c>
       <c r="M95" t="n">
-        <v>3.787831708788872</v>
+        <v>3.162365213036537</v>
       </c>
     </row>
     <row r="96">
@@ -48624,31 +48624,31 @@
         <v>161</v>
       </c>
       <c r="E96" t="n">
-        <v>0.04348914095009706</v>
+        <v>0.03781843089400241</v>
       </c>
       <c r="F96" t="n">
-        <v>0.0461871474981308</v>
+        <v>0.02464759349822998</v>
       </c>
       <c r="G96" t="n">
-        <v>0.05503463172440573</v>
+        <v>0.04710132953774485</v>
       </c>
       <c r="H96" t="n">
-        <v>0.03710004316733299</v>
+        <v>0.05969614163355332</v>
       </c>
       <c r="I96" t="n">
-        <v>0.04803496599197388</v>
+        <v>0.0313677191734314</v>
       </c>
       <c r="J96" t="n">
-        <v>0.1042470186948776</v>
+        <v>0.1059256792068481</v>
       </c>
       <c r="K96" t="n">
-        <v>0.1725299835205079</v>
+        <v>0.3061472535133368</v>
       </c>
       <c r="L96" t="n">
-        <v>0.1771013736724854</v>
+        <v>0.445391058921814</v>
       </c>
       <c r="M96" t="n">
-        <v>8.860575707629323</v>
+        <v>7.583314055576921</v>
       </c>
     </row>
     <row r="97">
@@ -48671,31 +48671,31 @@
         <v>59</v>
       </c>
       <c r="E97" t="n">
-        <v>0.03321855256365518</v>
+        <v>0.01806353859729686</v>
       </c>
       <c r="F97" t="n">
-        <v>0.02873852849006653</v>
+        <v>0.01220111548900604</v>
       </c>
       <c r="G97" t="n">
-        <v>0.03907493924943067</v>
+        <v>0.0221526212990284</v>
       </c>
       <c r="H97" t="n">
-        <v>0.03347026404701783</v>
+        <v>0.02249413087212752</v>
       </c>
       <c r="I97" t="n">
-        <v>0.03236269950866699</v>
+        <v>0.01669459044933319</v>
       </c>
       <c r="J97" t="n">
-        <v>0.07626482844352722</v>
+        <v>0.05378288328647614</v>
       </c>
       <c r="K97" t="n">
-        <v>0.1479947803169489</v>
+        <v>0.09804112970829017</v>
       </c>
       <c r="L97" t="n">
-        <v>0.1530881822109222</v>
+        <v>0.1212095618247986</v>
       </c>
       <c r="M97" t="n">
-        <v>2.30542141571641</v>
+        <v>1.307004656642675</v>
       </c>
     </row>
     <row r="98">
@@ -48718,31 +48718,31 @@
         <v>236379</v>
       </c>
       <c r="E98" t="n">
-        <v>0.2609586879566171</v>
+        <v>0.07653388267991036</v>
       </c>
       <c r="F98" t="n">
-        <v>0.2728640913641308</v>
+        <v>0.08884460283653391</v>
       </c>
       <c r="G98" t="n">
-        <v>0.3206015639573654</v>
+        <v>0.1470347557154845</v>
       </c>
       <c r="H98" t="n">
-        <v>0.2367663603133333</v>
+        <v>0.1287301072907588</v>
       </c>
       <c r="I98" t="n">
-        <v>0.2941269520965161</v>
+        <v>0.1210170342063517</v>
       </c>
       <c r="J98" t="n">
-        <v>0.6162539097845267</v>
+        <v>0.2895816228443313</v>
       </c>
       <c r="K98" t="n">
-        <v>0.7754307024047401</v>
+        <v>0.6122967003519982</v>
       </c>
       <c r="L98" t="n">
-        <v>3.492071613580211</v>
+        <v>1.39515763818035</v>
       </c>
       <c r="M98" t="n">
-        <v>75783.47708667809</v>
+        <v>34755.92852127051</v>
       </c>
     </row>
     <row r="99">
@@ -48765,31 +48765,31 @@
         <v>2069</v>
       </c>
       <c r="E99" t="n">
-        <v>0.02194621234844191</v>
+        <v>0.01221473365038215</v>
       </c>
       <c r="F99" t="n">
-        <v>0.00694818980247796</v>
+        <v>0.005944117249955644</v>
       </c>
       <c r="G99" t="n">
-        <v>0.1056134400798683</v>
+        <v>0.05842221954891586</v>
       </c>
       <c r="H99" t="n">
-        <v>0.1180163820741841</v>
+        <v>0.06212767795923553</v>
       </c>
       <c r="I99" t="n">
-        <v>0.06657857583599615</v>
+        <v>0.03789373839019945</v>
       </c>
       <c r="J99" t="n">
-        <v>0.2646847289120228</v>
+        <v>0.1359276880486202</v>
       </c>
       <c r="K99" t="n">
-        <v>0.5332560992902823</v>
+        <v>0.2851547673314327</v>
       </c>
       <c r="L99" t="n">
-        <v>1.040481287007071</v>
+        <v>0.3909755903856317</v>
       </c>
       <c r="M99" t="n">
-        <v>218.5142075252476</v>
+        <v>120.8755722467069</v>
       </c>
     </row>
     <row r="100">
@@ -48812,31 +48812,31 @@
         <v>11617</v>
       </c>
       <c r="E100" t="n">
-        <v>0.0314367437300976</v>
+        <v>0.01210458640934991</v>
       </c>
       <c r="F100" t="n">
-        <v>0.01437845773867241</v>
+        <v>0.008871432173724414</v>
       </c>
       <c r="G100" t="n">
-        <v>0.1326995369242247</v>
+        <v>0.06039323240552159</v>
       </c>
       <c r="H100" t="n">
-        <v>0.1603714144650911</v>
+        <v>0.06465671187343422</v>
       </c>
       <c r="I100" t="n">
-        <v>0.07837876691011317</v>
+        <v>0.03977588852300705</v>
       </c>
       <c r="J100" t="n">
-        <v>0.3276702962218008</v>
+        <v>0.1484219902839864</v>
       </c>
       <c r="K100" t="n">
-        <v>0.6518192500384181</v>
+        <v>0.2797438307927861</v>
       </c>
       <c r="L100" t="n">
-        <v>4.239168618724774</v>
+        <v>0.6265322478054089</v>
       </c>
       <c r="M100" t="n">
-        <v>1541.570520448719</v>
+        <v>701.5881808549443</v>
       </c>
     </row>
     <row r="101">
@@ -48859,31 +48859,31 @@
         <v>334</v>
       </c>
       <c r="E101" t="n">
-        <v>-0.02129281322957924</v>
+        <v>0.002580711878214766</v>
       </c>
       <c r="F101" t="n">
-        <v>-0.002210914250637875</v>
+        <v>0.002158466160290799</v>
       </c>
       <c r="G101" t="n">
-        <v>0.07688376330776477</v>
+        <v>0.03823905480697166</v>
       </c>
       <c r="H101" t="n">
-        <v>0.2472320127378959</v>
+        <v>0.04938637544365089</v>
       </c>
       <c r="I101" t="n">
-        <v>0.02936052494451013</v>
+        <v>0.0216837075763824</v>
       </c>
       <c r="J101" t="n">
-        <v>0.1155936167948172</v>
+        <v>0.08952846129109056</v>
       </c>
       <c r="K101" t="n">
-        <v>1.052853144844331</v>
+        <v>0.2332815840424945</v>
       </c>
       <c r="L101" t="n">
-        <v>2.937256214313749</v>
+        <v>0.3949870189663346</v>
       </c>
       <c r="M101" t="n">
-        <v>25.67917694479343</v>
+        <v>12.77184430552853</v>
       </c>
     </row>
     <row r="102">
@@ -48906,31 +48906,31 @@
         <v>1580</v>
       </c>
       <c r="E102" t="n">
-        <v>-0.02098375138456107</v>
+        <v>-0.0113683513988942</v>
       </c>
       <c r="F102" t="n">
-        <v>-0.0004467373881810682</v>
+        <v>-0.0007150118256690189</v>
       </c>
       <c r="G102" t="n">
-        <v>0.1097096165589928</v>
+        <v>0.05187310998418953</v>
       </c>
       <c r="H102" t="n">
-        <v>0.1532792855708957</v>
+        <v>0.06862127780055924</v>
       </c>
       <c r="I102" t="n">
-        <v>0.0560406019141535</v>
+        <v>0.02888665617489182</v>
       </c>
       <c r="J102" t="n">
-        <v>0.2965135999618462</v>
+        <v>0.1189973256523683</v>
       </c>
       <c r="K102" t="n">
-        <v>0.7648264072831353</v>
+        <v>0.3116953855814814</v>
       </c>
       <c r="L102" t="n">
-        <v>1.761662199572962</v>
+        <v>0.6710388875370868</v>
       </c>
       <c r="M102" t="n">
-        <v>173.3411941632087</v>
+        <v>81.95951377501946</v>
       </c>
     </row>
     <row r="103">
@@ -48953,31 +48953,31 @@
         <v>457</v>
       </c>
       <c r="E103" t="n">
-        <v>-0.06938924677192786</v>
+        <v>-0.02243593238291101</v>
       </c>
       <c r="F103" t="n">
-        <v>-0.01414633438142178</v>
+        <v>-0.01326184899928678</v>
       </c>
       <c r="G103" t="n">
-        <v>0.1008769181747226</v>
+        <v>0.03914459725741223</v>
       </c>
       <c r="H103" t="n">
-        <v>0.196025639100969</v>
+        <v>0.05239824646164297</v>
       </c>
       <c r="I103" t="n">
-        <v>0.03600368766090128</v>
+        <v>0.02564045813938338</v>
       </c>
       <c r="J103" t="n">
-        <v>0.2533750520342243</v>
+        <v>0.08632026135657703</v>
       </c>
       <c r="K103" t="n">
-        <v>1.143695243550018</v>
+        <v>0.2009174127940483</v>
       </c>
       <c r="L103" t="n">
-        <v>1.482741904935558</v>
+        <v>0.73548683953516</v>
       </c>
       <c r="M103" t="n">
-        <v>46.10075160584825</v>
+        <v>17.88908094663739</v>
       </c>
     </row>
     <row r="104">
@@ -49000,31 +49000,31 @@
         <v>6673</v>
       </c>
       <c r="E104" t="n">
-        <v>0.3178176494993836</v>
+        <v>0.2091311639607194</v>
       </c>
       <c r="F104" t="n">
-        <v>0.2728102505207062</v>
+        <v>0.2239806950092316</v>
       </c>
       <c r="G104" t="n">
-        <v>0.3188810612278937</v>
+        <v>0.2101192388214058</v>
       </c>
       <c r="H104" t="n">
-        <v>0.2300408312408416</v>
+        <v>0.1091131736449704</v>
       </c>
       <c r="I104" t="n">
-        <v>0.2728102505207062</v>
+        <v>0.2239806950092316</v>
       </c>
       <c r="J104" t="n">
-        <v>0.5409507632255555</v>
+        <v>0.3501486778259277</v>
       </c>
       <c r="K104" t="n">
-        <v>1.146840177774429</v>
+        <v>0.3878208446502686</v>
       </c>
       <c r="L104" t="n">
-        <v>1.414313077926636</v>
+        <v>0.4602931439876556</v>
       </c>
       <c r="M104" t="n">
-        <v>2127.893321573734</v>
+        <v>1402.125680655241</v>
       </c>
     </row>
     <row r="105">
@@ -49047,31 +49047,31 @@
         <v>52</v>
       </c>
       <c r="E105" t="n">
-        <v>0.1717198135761114</v>
+        <v>0.1495275165026005</v>
       </c>
       <c r="F105" t="n">
-        <v>0.2501893788576126</v>
+        <v>0.2063999325037003</v>
       </c>
       <c r="G105" t="n">
-        <v>0.1717198135761114</v>
+        <v>0.1495275165026005</v>
       </c>
       <c r="H105" t="n">
-        <v>0.1012025979763416</v>
+        <v>0.08795542303481726</v>
       </c>
       <c r="I105" t="n">
-        <v>0.2501893788576126</v>
+        <v>0.2063999325037003</v>
       </c>
       <c r="J105" t="n">
-        <v>0.2616419047117233</v>
+        <v>0.2327317386865616</v>
       </c>
       <c r="K105" t="n">
-        <v>0.2735912615060807</v>
+        <v>0.2481489133834839</v>
       </c>
       <c r="L105" t="n">
-        <v>0.2762672603130341</v>
+        <v>0.249596118927002</v>
       </c>
       <c r="M105" t="n">
-        <v>8.929430305957794</v>
+        <v>7.775430858135223</v>
       </c>
     </row>
     <row r="106">
@@ -49094,31 +49094,31 @@
         <v>357</v>
       </c>
       <c r="E106" t="n">
-        <v>0.05742909711282126</v>
+        <v>0.0484572527121429</v>
       </c>
       <c r="F106" t="n">
-        <v>0.04665493965148926</v>
+        <v>0.03176033496856689</v>
       </c>
       <c r="G106" t="n">
-        <v>0.06840535455725107</v>
+        <v>0.05850081300201202</v>
       </c>
       <c r="H106" t="n">
-        <v>0.07005718430911292</v>
+        <v>0.06108282936653623</v>
       </c>
       <c r="I106" t="n">
-        <v>0.04739159345626831</v>
+        <v>0.03598940372467041</v>
       </c>
       <c r="J106" t="n">
-        <v>0.1854405701160431</v>
+        <v>0.1675100445747376</v>
       </c>
       <c r="K106" t="n">
-        <v>0.3050570893287656</v>
+        <v>0.2304195380210876</v>
       </c>
       <c r="L106" t="n">
-        <v>0.3790422081947327</v>
+        <v>0.243817150592804</v>
       </c>
       <c r="M106" t="n">
-        <v>24.42071157693863</v>
+        <v>20.88479024171829</v>
       </c>
     </row>
     <row r="107">
@@ -49141,31 +49141,31 @@
         <v>2</v>
       </c>
       <c r="E107" t="n">
-        <v>0.03422722220420837</v>
+        <v>0.03463286161422729</v>
       </c>
       <c r="F107" t="n">
-        <v>0.03422722220420837</v>
+        <v>0.03463286161422729</v>
       </c>
       <c r="G107" t="n">
-        <v>0.03422722220420837</v>
+        <v>0.03463286161422729</v>
       </c>
       <c r="H107" t="n">
-        <v>0.007219523191452026</v>
+        <v>0.007356941699981689</v>
       </c>
       <c r="I107" t="n">
-        <v>0.03422722220420837</v>
+        <v>0.03463286161422729</v>
       </c>
       <c r="J107" t="n">
-        <v>0.04000284075737</v>
+        <v>0.04051841497421264</v>
       </c>
       <c r="K107" t="n">
-        <v>0.04130235493183136</v>
+        <v>0.04184266448020935</v>
       </c>
       <c r="L107" t="n">
-        <v>0.0414467453956604</v>
+        <v>0.04198980331420898</v>
       </c>
       <c r="M107" t="n">
-        <v>0.06845444440841675</v>
+        <v>0.06926572322845459</v>
       </c>
     </row>
     <row r="108">
@@ -49188,31 +49188,31 @@
         <v>48</v>
       </c>
       <c r="E108" t="n">
-        <v>0.02333837747573853</v>
+        <v>0.01808476820588112</v>
       </c>
       <c r="F108" t="n">
-        <v>0.02668285369873047</v>
+        <v>0.01936942338943481</v>
       </c>
       <c r="G108" t="n">
-        <v>0.03001692146062851</v>
+        <v>0.02121974403659503</v>
       </c>
       <c r="H108" t="n">
-        <v>0.01880589500452282</v>
+        <v>0.01472257660295114</v>
       </c>
       <c r="I108" t="n">
-        <v>0.02909229695796967</v>
+        <v>0.01980456709861755</v>
       </c>
       <c r="J108" t="n">
-        <v>0.05382022857666016</v>
+        <v>0.04062275290489199</v>
       </c>
       <c r="K108" t="n">
-        <v>0.06197227984666825</v>
+        <v>0.05492635250091554</v>
       </c>
       <c r="L108" t="n">
-        <v>0.0639459490776062</v>
+        <v>0.06274443864822388</v>
       </c>
       <c r="M108" t="n">
-        <v>1.440812230110168</v>
+        <v>1.018547713756561</v>
       </c>
     </row>
     <row r="109">
@@ -49235,31 +49235,31 @@
         <v>16</v>
       </c>
       <c r="E109" t="n">
-        <v>0.03188847750425339</v>
+        <v>0.01634141057729721</v>
       </c>
       <c r="F109" t="n">
-        <v>0.03190934658050537</v>
+        <v>0.01051077246665955</v>
       </c>
       <c r="G109" t="n">
-        <v>0.03194162249565125</v>
+        <v>0.01638299971818924</v>
       </c>
       <c r="H109" t="n">
-        <v>0.01720318392923717</v>
+        <v>0.01802483541192073</v>
       </c>
       <c r="I109" t="n">
-        <v>0.03190934658050537</v>
+        <v>0.01051077246665955</v>
       </c>
       <c r="J109" t="n">
-        <v>0.04822143912315369</v>
+        <v>0.02679914236068726</v>
       </c>
       <c r="K109" t="n">
-        <v>0.06989299207925796</v>
+        <v>0.07164852321147917</v>
       </c>
       <c r="L109" t="n">
-        <v>0.0730588436126709</v>
+        <v>0.07926774024963379</v>
       </c>
       <c r="M109" t="n">
-        <v>0.5110659599304199</v>
+        <v>0.2621279954910278</v>
       </c>
     </row>
     <row r="110">
@@ -49282,31 +49282,31 @@
         <v>184261</v>
       </c>
       <c r="E110" t="n">
-        <v>0.2170086326076403</v>
+        <v>0.0992932698720583</v>
       </c>
       <c r="F110" t="n">
-        <v>0.2078663389869271</v>
+        <v>0.0998039826900313</v>
       </c>
       <c r="G110" t="n">
-        <v>0.268879770311335</v>
+        <v>0.1634464443877506</v>
       </c>
       <c r="H110" t="n">
-        <v>0.2014496089494393</v>
+        <v>0.1435578485315573</v>
       </c>
       <c r="I110" t="n">
-        <v>0.2322259995609305</v>
+        <v>0.1329352495735109</v>
       </c>
       <c r="J110" t="n">
-        <v>0.5709606158584152</v>
+        <v>0.3364051265334887</v>
       </c>
       <c r="K110" t="n">
-        <v>0.7216925076559868</v>
+        <v>0.6084210338054405</v>
       </c>
       <c r="L110" t="n">
-        <v>1.536106148894931</v>
+        <v>2.0216142200039</v>
       </c>
       <c r="M110" t="n">
-        <v>49544.0553573369</v>
+        <v>30116.80528933131</v>
       </c>
     </row>
     <row r="111">
@@ -49329,31 +49329,31 @@
         <v>1751</v>
       </c>
       <c r="E111" t="n">
-        <v>0.009944573307657727</v>
+        <v>0.008921291839734278</v>
       </c>
       <c r="F111" t="n">
-        <v>0.002770289032760253</v>
+        <v>0.004631372330702548</v>
       </c>
       <c r="G111" t="n">
-        <v>0.06743474318374221</v>
+        <v>0.05142821271457132</v>
       </c>
       <c r="H111" t="n">
-        <v>0.07856686972141619</v>
+        <v>0.06654136192896085</v>
       </c>
       <c r="I111" t="n">
-        <v>0.03890265476242977</v>
+        <v>0.02643018344692747</v>
       </c>
       <c r="J111" t="n">
-        <v>0.1830470079492523</v>
+        <v>0.1304592645552156</v>
       </c>
       <c r="K111" t="n">
-        <v>0.3618139469506081</v>
+        <v>0.3377372106053629</v>
       </c>
       <c r="L111" t="n">
-        <v>0.5341371537935028</v>
+        <v>0.4504204689922457</v>
       </c>
       <c r="M111" t="n">
-        <v>118.0782353147326</v>
+        <v>90.05080046321439</v>
       </c>
     </row>
     <row r="112">
@@ -49376,31 +49376,31 @@
         <v>10063</v>
       </c>
       <c r="E112" t="n">
-        <v>0.0117131748475663</v>
+        <v>0.004906939738646358</v>
       </c>
       <c r="F112" t="n">
-        <v>0.005676342414988535</v>
+        <v>0.005611873267231115</v>
       </c>
       <c r="G112" t="n">
-        <v>0.0973056434872865</v>
+        <v>0.0667600727152784</v>
       </c>
       <c r="H112" t="n">
-        <v>0.1190989088792374</v>
+        <v>0.08909700924543928</v>
       </c>
       <c r="I112" t="n">
-        <v>0.05280391040606029</v>
+        <v>0.03614330367041349</v>
       </c>
       <c r="J112" t="n">
-        <v>0.2515411594178223</v>
+        <v>0.1651818029216527</v>
       </c>
       <c r="K112" t="n">
-        <v>0.5387664816120836</v>
+        <v>0.4301488721779364</v>
       </c>
       <c r="L112" t="n">
-        <v>1.17157837496133</v>
+        <v>1.146905295963797</v>
       </c>
       <c r="M112" t="n">
-        <v>979.1866904125641</v>
+        <v>671.8066117338465</v>
       </c>
     </row>
     <row r="113">
@@ -49423,31 +49423,31 @@
         <v>297</v>
       </c>
       <c r="E113" t="n">
-        <v>2.886806188846824e-05</v>
+        <v>0.004637324815525906</v>
       </c>
       <c r="F113" t="n">
-        <v>0.003495543306135658</v>
+        <v>0.002176328024084922</v>
       </c>
       <c r="G113" t="n">
-        <v>0.03972044733844884</v>
+        <v>0.03052405773429075</v>
       </c>
       <c r="H113" t="n">
-        <v>0.04872820882789518</v>
+        <v>0.04196451310748444</v>
       </c>
       <c r="I113" t="n">
-        <v>0.02324873669718625</v>
+        <v>0.01591558295075271</v>
       </c>
       <c r="J113" t="n">
-        <v>0.09135346405113771</v>
+        <v>0.07764864683059071</v>
       </c>
       <c r="K113" t="n">
-        <v>0.2585448363674431</v>
+        <v>0.2186824151394001</v>
       </c>
       <c r="L113" t="n">
-        <v>0.3103093223462408</v>
+        <v>0.3258883366892073</v>
       </c>
       <c r="M113" t="n">
-        <v>11.79697285951931</v>
+        <v>9.065645147084352</v>
       </c>
     </row>
     <row r="114">
@@ -49470,31 +49470,31 @@
         <v>1219</v>
       </c>
       <c r="E114" t="n">
-        <v>-0.000373228772562063</v>
+        <v>0.001880381778916642</v>
       </c>
       <c r="F114" t="n">
-        <v>0.002360721353142567</v>
+        <v>0.002972626588139423</v>
       </c>
       <c r="G114" t="n">
-        <v>0.06584980201229537</v>
+        <v>0.04677681296352274</v>
       </c>
       <c r="H114" t="n">
-        <v>0.08657223404798575</v>
+        <v>0.06178216610270971</v>
       </c>
       <c r="I114" t="n">
-        <v>0.03339093433144707</v>
+        <v>0.02263137571196128</v>
       </c>
       <c r="J114" t="n">
-        <v>0.1665710983125046</v>
+        <v>0.1253125878637352</v>
       </c>
       <c r="K114" t="n">
-        <v>0.4052418060907871</v>
+        <v>0.2595644590469228</v>
       </c>
       <c r="L114" t="n">
-        <v>0.7987955699900937</v>
+        <v>0.8612701956721962</v>
       </c>
       <c r="M114" t="n">
-        <v>80.27090865298806</v>
+        <v>57.02093500253422</v>
       </c>
     </row>
     <row r="115">
@@ -49517,31 +49517,31 @@
         <v>369</v>
       </c>
       <c r="E115" t="n">
-        <v>-0.008625539988152303</v>
+        <v>-0.01046263624913443</v>
       </c>
       <c r="F115" t="n">
-        <v>-0.006288237550441163</v>
+        <v>-0.00379120313364205</v>
       </c>
       <c r="G115" t="n">
-        <v>0.04046637822911706</v>
+        <v>0.03281001737929501</v>
       </c>
       <c r="H115" t="n">
-        <v>0.05406693005207772</v>
+        <v>0.03927966498577724</v>
       </c>
       <c r="I115" t="n">
-        <v>0.02300858960506649</v>
+        <v>0.01697398504578893</v>
       </c>
       <c r="J115" t="n">
-        <v>0.08991149459527839</v>
+        <v>0.09403037267791001</v>
       </c>
       <c r="K115" t="n">
-        <v>0.2666662583409372</v>
+        <v>0.1674813455846358</v>
       </c>
       <c r="L115" t="n">
-        <v>0.499266350429402</v>
+        <v>0.1936154942904033</v>
       </c>
       <c r="M115" t="n">
-        <v>14.93209356654419</v>
+        <v>12.10689641295986</v>
       </c>
     </row>
     <row r="116">
@@ -49564,31 +49564,31 @@
         <v>1375</v>
       </c>
       <c r="E116" t="n">
-        <v>0.4134421534104781</v>
+        <v>0.5729479193037207</v>
       </c>
       <c r="F116" t="n">
-        <v>0.4312188029289246</v>
+        <v>0.4572971165180206</v>
       </c>
       <c r="G116" t="n">
-        <v>0.4135816969004544</v>
+        <v>0.573105194980448</v>
       </c>
       <c r="H116" t="n">
-        <v>0.2549384276219877</v>
+        <v>0.4575805247351312</v>
       </c>
       <c r="I116" t="n">
-        <v>0.4312188029289246</v>
+        <v>0.4572971165180206</v>
       </c>
       <c r="J116" t="n">
-        <v>0.7541897237300873</v>
+        <v>1.281583124399186</v>
       </c>
       <c r="K116" t="n">
-        <v>0.8315310657024384</v>
+        <v>1.428924481272698</v>
       </c>
       <c r="L116" t="n">
-        <v>0.852442741394043</v>
+        <v>1.456828474998474</v>
       </c>
       <c r="M116" t="n">
-        <v>568.6748332381248</v>
+        <v>788.0196430981159</v>
       </c>
     </row>
     <row r="117">
@@ -49611,31 +49611,31 @@
         <v>17</v>
       </c>
       <c r="E117" t="n">
-        <v>0.1102333349340102</v>
+        <v>0.1054999653030844</v>
       </c>
       <c r="F117" t="n">
-        <v>0.08079466223716736</v>
+        <v>0.07858753204345703</v>
       </c>
       <c r="G117" t="n">
-        <v>0.1102333349340102</v>
+        <v>0.1054999653030844</v>
       </c>
       <c r="H117" t="n">
-        <v>0.07217920531443123</v>
+        <v>0.0729836824164391</v>
       </c>
       <c r="I117" t="n">
-        <v>0.08079466223716736</v>
+        <v>0.07858753204345703</v>
       </c>
       <c r="J117" t="n">
-        <v>0.2291019320487976</v>
+        <v>0.2261502861976624</v>
       </c>
       <c r="K117" t="n">
-        <v>0.2509232544898987</v>
+        <v>0.2489656066894531</v>
       </c>
       <c r="L117" t="n">
-        <v>0.2516377568244934</v>
+        <v>0.2498250007629395</v>
       </c>
       <c r="M117" t="n">
-        <v>1.873966693878174</v>
+        <v>1.793499410152435</v>
       </c>
     </row>
     <row r="118">
@@ -49658,31 +49658,31 @@
         <v>219</v>
       </c>
       <c r="E118" t="n">
-        <v>0.1420718639680784</v>
+        <v>0.1577156128948682</v>
       </c>
       <c r="F118" t="n">
-        <v>0.08701357245445251</v>
+        <v>0.08407703042030334</v>
       </c>
       <c r="G118" t="n">
-        <v>0.1426962656245384</v>
+        <v>0.1584099778845974</v>
       </c>
       <c r="H118" t="n">
-        <v>0.1457229542412136</v>
+        <v>0.1841811135420856</v>
       </c>
       <c r="I118" t="n">
-        <v>0.08701357245445251</v>
+        <v>0.08407703042030334</v>
       </c>
       <c r="J118" t="n">
-        <v>0.4212315917015077</v>
+        <v>0.4625292778015138</v>
       </c>
       <c r="K118" t="n">
-        <v>0.5463060462474822</v>
+        <v>0.741587997674942</v>
       </c>
       <c r="L118" t="n">
-        <v>0.55384761095047</v>
+        <v>0.7539101839065552</v>
       </c>
       <c r="M118" t="n">
-        <v>31.25048217177391</v>
+        <v>34.69178515672684</v>
       </c>
     </row>
     <row r="119">
@@ -49705,31 +49705,31 @@
         <v>15</v>
       </c>
       <c r="E119" t="n">
-        <v>0.06684593756993612</v>
+        <v>0.06600919365882874</v>
       </c>
       <c r="F119" t="n">
-        <v>0.05637750029563904</v>
+        <v>0.0514393150806427</v>
       </c>
       <c r="G119" t="n">
-        <v>0.06718355417251587</v>
+        <v>0.06677947640419006</v>
       </c>
       <c r="H119" t="n">
-        <v>0.06127804330807049</v>
+        <v>0.06072646158887653</v>
       </c>
       <c r="I119" t="n">
-        <v>0.05637750029563904</v>
+        <v>0.0514393150806427</v>
       </c>
       <c r="J119" t="n">
-        <v>0.1471901416778564</v>
+        <v>0.1433761715888977</v>
       </c>
       <c r="K119" t="n">
-        <v>0.2151048803329468</v>
+        <v>0.2131077849864959</v>
       </c>
       <c r="L119" t="n">
-        <v>0.2236323952674866</v>
+        <v>0.2224627137184143</v>
       </c>
       <c r="M119" t="n">
-        <v>1.007753312587738</v>
+        <v>1.001692146062851</v>
       </c>
     </row>
     <row r="120">
@@ -49752,31 +49752,31 @@
         <v>45</v>
       </c>
       <c r="E120" t="n">
-        <v>0.04815972248713175</v>
+        <v>0.04777245256635878</v>
       </c>
       <c r="F120" t="n">
-        <v>0.03249552845954895</v>
+        <v>0.02966365218162537</v>
       </c>
       <c r="G120" t="n">
-        <v>0.0499629643228319</v>
+        <v>0.04944525957107544</v>
       </c>
       <c r="H120" t="n">
-        <v>0.04541155325646787</v>
+        <v>0.04623920383171528</v>
       </c>
       <c r="I120" t="n">
-        <v>0.03249552845954895</v>
+        <v>0.02966365218162537</v>
       </c>
       <c r="J120" t="n">
-        <v>0.1154637515544891</v>
+        <v>0.1150082886219025</v>
       </c>
       <c r="K120" t="n">
-        <v>0.1653107690811158</v>
+        <v>0.160716941356659</v>
       </c>
       <c r="L120" t="n">
-        <v>0.1779768466949463</v>
+        <v>0.1729884743690491</v>
       </c>
       <c r="M120" t="n">
-        <v>2.248333394527435</v>
+        <v>2.225036680698395</v>
       </c>
     </row>
     <row r="121">
@@ -49799,31 +49799,31 @@
         <v>49</v>
       </c>
       <c r="E121" t="n">
-        <v>0.03282471700590484</v>
+        <v>0.03152254223823547</v>
       </c>
       <c r="F121" t="n">
-        <v>0.03065672516822815</v>
+        <v>0.03022429347038269</v>
       </c>
       <c r="G121" t="n">
-        <v>0.03787933320415263</v>
+        <v>0.03622451059672297</v>
       </c>
       <c r="H121" t="n">
-        <v>0.0310530207120186</v>
+        <v>0.03121930007434505</v>
       </c>
       <c r="I121" t="n">
-        <v>0.03065672516822815</v>
+        <v>0.03022429347038269</v>
       </c>
       <c r="J121" t="n">
-        <v>0.09212130904197693</v>
+        <v>0.08965537548065186</v>
       </c>
       <c r="K121" t="n">
-        <v>0.1152221274375915</v>
+        <v>0.1136303901672363</v>
       </c>
       <c r="L121" t="n">
-        <v>0.1182054877281189</v>
+        <v>0.1182982921600342</v>
       </c>
       <c r="M121" t="n">
-        <v>1.856087327003479</v>
+        <v>1.775001019239426</v>
       </c>
     </row>
   </sheetData>
@@ -49927,31 +49927,31 @@
         <v>5782</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.009045506090298491</v>
+        <v>-0.00206654610429041</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.0003058238606446763</v>
+        <v>-0.001590101337208019</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05607298084967317</v>
+        <v>0.02731288363281609</v>
       </c>
       <c r="H2" t="n">
-        <v>0.09795780394395949</v>
+        <v>0.03276321507227122</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0235408494911335</v>
+        <v>0.01535465739634401</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1340133274572588</v>
+        <v>0.06810359466175846</v>
       </c>
       <c r="K2" t="n">
-        <v>0.468170265595801</v>
+        <v>0.1598314094009269</v>
       </c>
       <c r="L2" t="n">
-        <v>1.246573796986787</v>
+        <v>0.2478063608671251</v>
       </c>
       <c r="M2" t="n">
-        <v>324.2139752728103</v>
+        <v>157.9230931649427</v>
       </c>
     </row>
     <row r="3">
@@ -49974,31 +49974,31 @@
         <v>23121</v>
       </c>
       <c r="E3" t="n">
-        <v>0.005143366466911005</v>
+        <v>0.007155198977026975</v>
       </c>
       <c r="F3" t="n">
-        <v>0.006602069424262557</v>
+        <v>0.004154815906501463</v>
       </c>
       <c r="G3" t="n">
-        <v>0.06695906600459807</v>
+        <v>0.03334449470569905</v>
       </c>
       <c r="H3" t="n">
-        <v>0.09776974366244436</v>
+        <v>0.03652895634531841</v>
       </c>
       <c r="I3" t="n">
-        <v>0.03372017052408782</v>
+        <v>0.02091749033581361</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1712884103074578</v>
+        <v>0.07958385014579793</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4562983685160215</v>
+        <v>0.1787193391645708</v>
       </c>
       <c r="L3" t="n">
-        <v>1.47597273269042</v>
+        <v>0.2739914616723302</v>
       </c>
       <c r="M3" t="n">
-        <v>1548.160565092312</v>
+        <v>770.9580620904677</v>
       </c>
     </row>
     <row r="4">
@@ -50021,31 +50021,31 @@
         <v>39508</v>
       </c>
       <c r="E4" t="n">
-        <v>0.04734299145337136</v>
+        <v>0.02982310319407799</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03026044364335089</v>
+        <v>0.02159924241114662</v>
       </c>
       <c r="G4" t="n">
-        <v>0.09471527138904411</v>
+        <v>0.05047071780593064</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1009989720426443</v>
+        <v>0.04779898178404497</v>
       </c>
       <c r="I4" t="n">
-        <v>0.05963302147955613</v>
+        <v>0.03575948184507996</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2336160884980753</v>
+        <v>0.1171210759315785</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4496793621850471</v>
+        <v>0.2208350597663539</v>
       </c>
       <c r="L4" t="n">
-        <v>1.297964627579174</v>
+        <v>0.3016058918250162</v>
       </c>
       <c r="M4" t="n">
-        <v>3742.010942038355</v>
+        <v>1993.997119076708</v>
       </c>
     </row>
     <row r="5">
@@ -50068,31 +50068,31 @@
         <v>83743</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1302887084482406</v>
+        <v>0.0763081985051416</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1079680434942725</v>
+        <v>0.07061847592527716</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1551796298211187</v>
+        <v>0.0878752552243086</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1261863292816929</v>
+        <v>0.06533034482969144</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1203914587619012</v>
+        <v>0.07473656872440579</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3425280455497435</v>
+        <v>0.1800120084230433</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4956576523459765</v>
+        <v>0.2742580441123599</v>
       </c>
       <c r="L5" t="n">
-        <v>0.633767527636384</v>
+        <v>0.4387024803545267</v>
       </c>
       <c r="M5" t="n">
-        <v>12995.20774010995</v>
+        <v>7358.937498249275</v>
       </c>
     </row>
     <row r="6">
@@ -50115,31 +50115,31 @@
         <v>155901</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2737109344446654</v>
+        <v>0.1520491151808037</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2937538355190542</v>
+        <v>0.1564250101336092</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2844539321006708</v>
+        <v>0.1593572384715133</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1574049092039563</v>
+        <v>0.08522000802763424</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2943174808442253</v>
+        <v>0.1574754355337893</v>
       </c>
       <c r="J6" t="n">
-        <v>0.491203765579582</v>
+        <v>0.2719807078194502</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5947075909887272</v>
+        <v>0.3729182131161459</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6570716548662094</v>
+        <v>0.456261616363046</v>
       </c>
       <c r="M6" t="n">
-        <v>44346.65246842668</v>
+        <v>24843.95283494739</v>
       </c>
     </row>
     <row r="7">
@@ -50162,31 +50162,31 @@
         <v>76905</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3829148851504742</v>
+        <v>0.2081880517731854</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4514180272905409</v>
+        <v>0.2085154248099697</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4111043169219636</v>
+        <v>0.2103769982957572</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1635646058337113</v>
+        <v>0.0921641957800057</v>
       </c>
       <c r="I7" t="n">
-        <v>0.455125332179827</v>
+        <v>0.2085844499744935</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6002650005131683</v>
+        <v>0.326763172299663</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6636796453990307</v>
+        <v>0.4372057468506746</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8778803330227836</v>
+        <v>0.468392863571744</v>
       </c>
       <c r="M7" t="n">
-        <v>31615.97749288361</v>
+        <v>16179.04305393521</v>
       </c>
     </row>
     <row r="8">
@@ -50209,31 +50209,31 @@
         <v>6563</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1586881608695964</v>
+        <v>0.1576657915649705</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3145054470286422</v>
+        <v>0.139505529593378</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3970250981420035</v>
+        <v>0.1579092634252638</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1851043474816923</v>
+        <v>0.09699126980296859</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4220713922805651</v>
+        <v>0.139505529593378</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6129673195124173</v>
+        <v>0.3158658944286863</v>
       </c>
       <c r="K8" t="n">
-        <v>0.770461821546284</v>
+        <v>0.4244008109059099</v>
       </c>
       <c r="L8" t="n">
-        <v>0.9100709101880237</v>
+        <v>0.4434363924962221</v>
       </c>
       <c r="M8" t="n">
-        <v>2605.675719105969</v>
+        <v>1036.358495860007</v>
       </c>
     </row>
     <row r="9">
@@ -50256,31 +50256,31 @@
         <v>157</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1186889650843471</v>
+        <v>0.06033457224722395</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1165839053306391</v>
+        <v>0.06537393452633876</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1193315599928219</v>
+        <v>0.06033457224722395</v>
       </c>
       <c r="H9" t="n">
-        <v>0.05279702761545554</v>
+        <v>0.01506889920701019</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1165839053306391</v>
+        <v>0.06537393452633876</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1866414715338734</v>
+        <v>0.07688485753023147</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1979060517078561</v>
+        <v>0.07750410368592565</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1983888492288625</v>
+        <v>0.07773060005779048</v>
       </c>
       <c r="M9" t="n">
-        <v>18.73505491887304</v>
+        <v>9.472527842814159</v>
       </c>
     </row>
     <row r="10">
@@ -50773,31 +50773,31 @@
         <v>6083</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0192624113050139</v>
+        <v>-0.004523961974753824</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0003718052376952031</v>
+        <v>-0.001331363260518284</v>
       </c>
       <c r="G20" t="n">
-        <v>0.07401789400916779</v>
+        <v>0.0381882047360864</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1536764325402157</v>
+        <v>0.04527543009774005</v>
       </c>
       <c r="I20" t="n">
-        <v>0.03119366310479784</v>
+        <v>0.02327583139689324</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1598401352946869</v>
+        <v>0.09095733490683666</v>
       </c>
       <c r="K20" t="n">
-        <v>0.7769555415427005</v>
+        <v>0.2140306763312041</v>
       </c>
       <c r="L20" t="n">
-        <v>2.344705610186359</v>
+        <v>0.3302370243441404</v>
       </c>
       <c r="M20" t="n">
-        <v>450.2508492577676</v>
+        <v>232.2988494096136</v>
       </c>
     </row>
     <row r="21">
@@ -50820,31 +50820,31 @@
         <v>24156</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.003309263349224463</v>
+        <v>0.008060936134755581</v>
       </c>
       <c r="F21" t="n">
-        <v>0.002290031922227216</v>
+        <v>0.006499459542464651</v>
       </c>
       <c r="G21" t="n">
-        <v>0.07595226512619795</v>
+        <v>0.04302825748906062</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1132945161072095</v>
+        <v>0.04342528484569945</v>
       </c>
       <c r="I21" t="n">
-        <v>0.04054581310466643</v>
+        <v>0.02926579285541973</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1832157597843476</v>
+        <v>0.09853347915548435</v>
       </c>
       <c r="K21" t="n">
-        <v>0.48642785469908</v>
+        <v>0.2047869416873598</v>
       </c>
       <c r="L21" t="n">
-        <v>2.28111877347812</v>
+        <v>0.3343180939385582</v>
       </c>
       <c r="M21" t="n">
-        <v>1834.702916388438</v>
+        <v>1039.390587905748</v>
       </c>
     </row>
     <row r="22">
@@ -50867,31 +50867,31 @@
         <v>39430</v>
       </c>
       <c r="E22" t="n">
-        <v>0.03552407283075346</v>
+        <v>0.03857676160314201</v>
       </c>
       <c r="F22" t="n">
-        <v>0.02204149723759182</v>
+        <v>0.03308533816569138</v>
       </c>
       <c r="G22" t="n">
-        <v>0.09981182591190339</v>
+        <v>0.06441084032822411</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1009659568083</v>
+        <v>0.05553055996694523</v>
       </c>
       <c r="I22" t="n">
-        <v>0.06513429978482621</v>
+        <v>0.04990230055607516</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2406962558476052</v>
+        <v>0.1408797790981726</v>
       </c>
       <c r="K22" t="n">
-        <v>0.444285110528176</v>
+        <v>0.2456162418405985</v>
       </c>
       <c r="L22" t="n">
-        <v>1.245742900024691</v>
+        <v>0.3552468960435402</v>
       </c>
       <c r="M22" t="n">
-        <v>3935.580295706351</v>
+        <v>2539.719434141877</v>
       </c>
     </row>
     <row r="23">
@@ -50914,31 +50914,31 @@
         <v>77358</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1267867579419548</v>
+        <v>0.09886932628643219</v>
       </c>
       <c r="F23" t="n">
-        <v>0.108560161995653</v>
+        <v>0.09836331027677184</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1629936876663868</v>
+        <v>0.1149720589179094</v>
       </c>
       <c r="H23" t="n">
-        <v>0.130665902241708</v>
+        <v>0.07992885277716126</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1294770263057748</v>
+        <v>0.1034684384937446</v>
       </c>
       <c r="J23" t="n">
-        <v>0.3537408039775954</v>
+        <v>0.2262550746629733</v>
       </c>
       <c r="K23" t="n">
-        <v>0.5230586679902002</v>
+        <v>0.3249633736698617</v>
       </c>
       <c r="L23" t="n">
-        <v>0.9079739489279116</v>
+        <v>0.8907721608734436</v>
       </c>
       <c r="M23" t="n">
-        <v>12608.86569049635</v>
+        <v>8894.008533771639</v>
       </c>
     </row>
     <row r="24">
@@ -50961,31 +50961,31 @@
         <v>133467</v>
       </c>
       <c r="E24" t="n">
-        <v>0.2897983867965442</v>
+        <v>0.17902661161042</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3158132680148373</v>
+        <v>0.2023006574655161</v>
       </c>
       <c r="G24" t="n">
-        <v>0.3082574967472403</v>
+        <v>0.2004652173154812</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1663756744372658</v>
+        <v>0.103986594992051</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3186559930866131</v>
+        <v>0.2064405872795257</v>
       </c>
       <c r="J24" t="n">
-        <v>0.5211415806402085</v>
+        <v>0.322727026275352</v>
       </c>
       <c r="K24" t="n">
-        <v>0.6112555827370345</v>
+        <v>0.3998655900977687</v>
       </c>
       <c r="L24" t="n">
-        <v>1.424133645288415</v>
+        <v>2.030356831502568</v>
       </c>
       <c r="M24" t="n">
-        <v>41142.20331836392</v>
+        <v>26755.49115944533</v>
       </c>
     </row>
     <row r="25">
@@ -51008,31 +51008,31 @@
         <v>80002</v>
       </c>
       <c r="E25" t="n">
-        <v>0.3910741749817025</v>
+        <v>0.1875367437619095</v>
       </c>
       <c r="F25" t="n">
-        <v>0.446945723402391</v>
+        <v>0.241050789698961</v>
       </c>
       <c r="G25" t="n">
-        <v>0.4163888718057518</v>
+        <v>0.2584164356307683</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1766589997653401</v>
+        <v>0.18501897656819</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4509919882595073</v>
+        <v>0.2508609665938061</v>
       </c>
       <c r="J25" t="n">
-        <v>0.6166114146232918</v>
+        <v>0.388344425819536</v>
       </c>
       <c r="K25" t="n">
-        <v>0.7029772656329457</v>
+        <v>1.009166533523546</v>
       </c>
       <c r="L25" t="n">
-        <v>1.350378916307483</v>
+        <v>2.380097723252358</v>
       </c>
       <c r="M25" t="n">
-        <v>33311.94252220375</v>
+        <v>20673.83168333273</v>
       </c>
     </row>
     <row r="26">
@@ -51055,31 +51055,31 @@
         <v>9036</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1364436236558556</v>
+        <v>0.08762788561065443</v>
       </c>
       <c r="F26" t="n">
-        <v>0.2495629730878795</v>
+        <v>0.1145314372694085</v>
       </c>
       <c r="G26" t="n">
-        <v>0.3662176165487553</v>
+        <v>0.1934453941552082</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2571034959669038</v>
+        <v>0.112978266048193</v>
       </c>
       <c r="I26" t="n">
-        <v>0.3514469630846252</v>
+        <v>0.166413882196273</v>
       </c>
       <c r="J26" t="n">
-        <v>0.6169769287274692</v>
+        <v>0.3496401068100901</v>
       </c>
       <c r="K26" t="n">
-        <v>1.434180887237824</v>
+        <v>0.4347554153482499</v>
       </c>
       <c r="L26" t="n">
-        <v>1.679877863113425</v>
+        <v>0.6195110497775013</v>
       </c>
       <c r="M26" t="n">
-        <v>3309.142383134553</v>
+        <v>1747.972581586461</v>
       </c>
     </row>
     <row r="27">
@@ -51102,31 +51102,31 @@
         <v>443</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.3860940403822785</v>
+        <v>-0.06742707775492317</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.1311245244698242</v>
+        <v>-0.1378665640956759</v>
       </c>
       <c r="G27" t="n">
-        <v>0.4513218730107089</v>
+        <v>0.1798163459703755</v>
       </c>
       <c r="H27" t="n">
-        <v>0.4520822823441872</v>
+        <v>0.06026033700155398</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1542573433865857</v>
+        <v>0.1783896884084415</v>
       </c>
       <c r="J27" t="n">
-        <v>0.9535926184720327</v>
+        <v>0.2575184205639197</v>
       </c>
       <c r="K27" t="n">
-        <v>1.711883584539672</v>
+        <v>0.2789139556957542</v>
       </c>
       <c r="L27" t="n">
-        <v>1.755457166380913</v>
+        <v>0.2800345841169781</v>
       </c>
       <c r="M27" t="n">
-        <v>199.935589743744</v>
+        <v>79.65864126487634</v>
       </c>
     </row>
     <row r="28">
@@ -51384,31 +51384,31 @@
         <v>13</v>
       </c>
       <c r="E33" t="n">
-        <v>1.026523436491306</v>
+        <v>0.9781900025331057</v>
       </c>
       <c r="F33" t="n">
-        <v>1.028694659471512</v>
+        <v>0.9820536673069</v>
       </c>
       <c r="G33" t="n">
-        <v>1.026523436491306</v>
+        <v>0.9781900025331057</v>
       </c>
       <c r="H33" t="n">
-        <v>0.01303731125843756</v>
+        <v>0.01498433682281055</v>
       </c>
       <c r="I33" t="n">
-        <v>1.028694659471512</v>
+        <v>0.9820536673069</v>
       </c>
       <c r="J33" t="n">
-        <v>1.040167981386185</v>
+        <v>0.9937905132770538</v>
       </c>
       <c r="K33" t="n">
-        <v>1.046811014413834</v>
+        <v>0.9998029625415802</v>
       </c>
       <c r="L33" t="n">
-        <v>1.047696858644485</v>
+        <v>1.000607281923294</v>
       </c>
       <c r="M33" t="n">
-        <v>13.34480467438698</v>
+        <v>12.71647003293037</v>
       </c>
     </row>
     <row r="34">
@@ -51431,31 +51431,31 @@
         <v>918</v>
       </c>
       <c r="E34" t="n">
-        <v>0.8457584441045835</v>
+        <v>1.382175094572292</v>
       </c>
       <c r="F34" t="n">
-        <v>0.8242017775774002</v>
+        <v>1.389496922492981</v>
       </c>
       <c r="G34" t="n">
-        <v>0.8457584441045835</v>
+        <v>1.382175094572292</v>
       </c>
       <c r="H34" t="n">
-        <v>0.1687300308012512</v>
+        <v>0.2875076868671126</v>
       </c>
       <c r="I34" t="n">
-        <v>0.8242017775774002</v>
+        <v>1.389496922492981</v>
       </c>
       <c r="J34" t="n">
-        <v>1.068922062963247</v>
+        <v>1.86444326415658</v>
       </c>
       <c r="K34" t="n">
-        <v>1.188491763742641</v>
+        <v>2.01190915604464</v>
       </c>
       <c r="L34" t="n">
-        <v>1.197588013252243</v>
+        <v>2.020037545822561</v>
       </c>
       <c r="M34" t="n">
-        <v>776.4062516880076</v>
+        <v>1268.836736817364</v>
       </c>
     </row>
     <row r="35">
@@ -51478,31 +51478,31 @@
         <v>806</v>
       </c>
       <c r="E35" t="n">
-        <v>0.6563832751785198</v>
+        <v>1.544696184089456</v>
       </c>
       <c r="F35" t="n">
-        <v>0.543915331363678</v>
+        <v>1.447330892086029</v>
       </c>
       <c r="G35" t="n">
-        <v>0.6563832751785198</v>
+        <v>1.544696184089456</v>
       </c>
       <c r="H35" t="n">
-        <v>0.245486415435858</v>
+        <v>0.2050377714191228</v>
       </c>
       <c r="I35" t="n">
-        <v>0.543915331363678</v>
+        <v>1.447330892086029</v>
       </c>
       <c r="J35" t="n">
-        <v>1.142198697772983</v>
+        <v>2.008976095356047</v>
       </c>
       <c r="K35" t="n">
-        <v>1.176982670948564</v>
+        <v>2.026682704613267</v>
       </c>
       <c r="L35" t="n">
-        <v>1.184070005081594</v>
+        <v>2.028131218081398</v>
       </c>
       <c r="M35" t="n">
-        <v>529.0449197938869</v>
+        <v>1245.025124376101</v>
       </c>
     </row>
     <row r="36">
@@ -51619,31 +51619,31 @@
         <v>4417</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.03439226511548613</v>
+        <v>-0.008945790095413554</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.004824516041451331</v>
+        <v>-0.001695177060101709</v>
       </c>
       <c r="G38" t="n">
-        <v>0.1660730522005008</v>
+        <v>0.0705375016135</v>
       </c>
       <c r="H38" t="n">
-        <v>0.3161930648414824</v>
+        <v>0.09300745598779456</v>
       </c>
       <c r="I38" t="n">
-        <v>0.07802857905427568</v>
+        <v>0.03813540419386363</v>
       </c>
       <c r="J38" t="n">
-        <v>0.3959424739193416</v>
+        <v>0.1735573016329146</v>
       </c>
       <c r="K38" t="n">
-        <v>1.451160297194873</v>
+        <v>0.4578181322124086</v>
       </c>
       <c r="L38" t="n">
-        <v>7.631818100156119</v>
+        <v>1.116002622355348</v>
       </c>
       <c r="M38" t="n">
-        <v>733.5446715696122</v>
+        <v>311.5641446268295</v>
       </c>
     </row>
     <row r="39">
@@ -51666,31 +51666,31 @@
         <v>16469</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.006325935502266855</v>
+        <v>-0.00722401459808374</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.007762644446238452</v>
+        <v>0.001043987223534766</v>
       </c>
       <c r="G39" t="n">
-        <v>0.1642399932701286</v>
+        <v>0.08685492152881517</v>
       </c>
       <c r="H39" t="n">
-        <v>0.2086849299858418</v>
+        <v>0.1092555182501936</v>
       </c>
       <c r="I39" t="n">
-        <v>0.09323013633709229</v>
+        <v>0.04862059505119447</v>
       </c>
       <c r="J39" t="n">
-        <v>0.4113801632791901</v>
+        <v>0.2188932926857495</v>
       </c>
       <c r="K39" t="n">
-        <v>0.9403211363232831</v>
+        <v>0.492557152654759</v>
       </c>
       <c r="L39" t="n">
-        <v>3.41957818235757</v>
+        <v>1.386017480028532</v>
       </c>
       <c r="M39" t="n">
-        <v>2704.868449165749</v>
+        <v>1430.413702658057</v>
       </c>
     </row>
     <row r="40">
@@ -51713,31 +51713,31 @@
         <v>24552</v>
       </c>
       <c r="E40" t="n">
-        <v>0.07473202225886087</v>
+        <v>-0.009170584107670783</v>
       </c>
       <c r="F40" t="n">
-        <v>0.04574739138933751</v>
+        <v>0.006590946316015808</v>
       </c>
       <c r="G40" t="n">
-        <v>0.2106217804011053</v>
+        <v>0.135936628502936</v>
       </c>
       <c r="H40" t="n">
-        <v>0.2052645227987211</v>
+        <v>0.1590675324927918</v>
       </c>
       <c r="I40" t="n">
-        <v>0.1435480104133649</v>
+        <v>0.08736709794029048</v>
       </c>
       <c r="J40" t="n">
-        <v>0.5107565596265375</v>
+        <v>0.3160473549735474</v>
       </c>
       <c r="K40" t="n">
-        <v>0.7964932198666467</v>
+        <v>0.7030043049876161</v>
       </c>
       <c r="L40" t="n">
-        <v>2.292997559587154</v>
+        <v>4.064106591818883</v>
       </c>
       <c r="M40" t="n">
-        <v>5171.185952407937</v>
+        <v>3337.516103004084</v>
       </c>
     </row>
     <row r="41">
@@ -51760,31 +51760,31 @@
         <v>45552</v>
       </c>
       <c r="E41" t="n">
-        <v>0.2140959268883719</v>
+        <v>-0.02850279296960371</v>
       </c>
       <c r="F41" t="n">
-        <v>0.214048454840627</v>
+        <v>0.01170367589464229</v>
       </c>
       <c r="G41" t="n">
-        <v>0.3364455138695971</v>
+        <v>0.2218955042192242</v>
       </c>
       <c r="H41" t="n">
-        <v>0.2582027876171039</v>
+        <v>0.2719333983552369</v>
       </c>
       <c r="I41" t="n">
-        <v>0.2954716850615494</v>
+        <v>0.1548979893326258</v>
       </c>
       <c r="J41" t="n">
-        <v>0.6830671485669516</v>
+        <v>0.4410369392608335</v>
       </c>
       <c r="K41" t="n">
-        <v>0.9002108000622941</v>
+        <v>1.302838891781408</v>
       </c>
       <c r="L41" t="n">
-        <v>2.962936608432782</v>
+        <v>4.137833365061724</v>
       </c>
       <c r="M41" t="n">
-        <v>15325.76604778789</v>
+        <v>10107.7840081941</v>
       </c>
     </row>
     <row r="42">
@@ -51807,31 +51807,31 @@
         <v>77826</v>
       </c>
       <c r="E42" t="n">
-        <v>0.4051183558685324</v>
+        <v>-0.1154929168894974</v>
       </c>
       <c r="F42" t="n">
-        <v>0.4999269177833625</v>
+        <v>0.03012663823097604</v>
       </c>
       <c r="G42" t="n">
-        <v>0.4946194113491152</v>
+        <v>0.3983598226325052</v>
       </c>
       <c r="H42" t="n">
-        <v>0.2713099165822545</v>
+        <v>0.5087739014094035</v>
       </c>
       <c r="I42" t="n">
-        <v>0.5228303553612974</v>
+        <v>0.2736150283947488</v>
       </c>
       <c r="J42" t="n">
-        <v>0.8172664324398813</v>
+        <v>0.766824791845565</v>
       </c>
       <c r="K42" t="n">
-        <v>0.9022272606920598</v>
+        <v>2.944123803078937</v>
       </c>
       <c r="L42" t="n">
-        <v>2.905227546895211</v>
+        <v>4.795767843901819</v>
       </c>
       <c r="M42" t="n">
-        <v>38494.25030765624</v>
+        <v>31002.75155619735</v>
       </c>
     </row>
     <row r="43">
@@ -51854,31 +51854,31 @@
         <v>42101</v>
       </c>
       <c r="E43" t="n">
-        <v>0.5347820368024513</v>
+        <v>-0.2191521360556417</v>
       </c>
       <c r="F43" t="n">
-        <v>0.6303763118493146</v>
+        <v>0.003678986600121355</v>
       </c>
       <c r="G43" t="n">
-        <v>0.5660159496933455</v>
+        <v>0.5429796676329794</v>
       </c>
       <c r="H43" t="n">
-        <v>0.2468440352717569</v>
+        <v>0.6482351662265893</v>
       </c>
       <c r="I43" t="n">
-        <v>0.6320409443099274</v>
+        <v>0.3691676210637942</v>
       </c>
       <c r="J43" t="n">
-        <v>0.8518652855561534</v>
+        <v>1.281462677963419</v>
       </c>
       <c r="K43" t="n">
-        <v>0.9040872250332109</v>
+        <v>3.618669223364873</v>
       </c>
       <c r="L43" t="n">
-        <v>0.9245347705357787</v>
+        <v>4.794474588073633</v>
       </c>
       <c r="M43" t="n">
-        <v>23829.83749803954</v>
+        <v>22859.98698701607</v>
       </c>
     </row>
     <row r="44">
@@ -51901,31 +51901,31 @@
         <v>1527</v>
       </c>
       <c r="E44" t="n">
-        <v>0.1468392201721961</v>
+        <v>-0.5567082901084974</v>
       </c>
       <c r="F44" t="n">
-        <v>0.3938006892870843</v>
+        <v>-0.09807759581443445</v>
       </c>
       <c r="G44" t="n">
-        <v>0.64950888380806</v>
+        <v>0.9380641691155547</v>
       </c>
       <c r="H44" t="n">
-        <v>0.4747541339561968</v>
+        <v>0.8829570995609693</v>
       </c>
       <c r="I44" t="n">
-        <v>0.5533212026371104</v>
+        <v>0.6105414106691636</v>
       </c>
       <c r="J44" t="n">
-        <v>1.065592609810438</v>
+        <v>2.614336841957638</v>
       </c>
       <c r="K44" t="n">
-        <v>2.541667193233822</v>
+        <v>2.734728503790023</v>
       </c>
       <c r="L44" t="n">
-        <v>2.855870367962275</v>
+        <v>2.954545600853682</v>
       </c>
       <c r="M44" t="n">
-        <v>991.8000655749078</v>
+        <v>1432.423986239452</v>
       </c>
     </row>
     <row r="45">
@@ -52042,31 +52042,31 @@
         <v>532</v>
       </c>
       <c r="E47" t="n">
-        <v>0.07211570265261751</v>
+        <v>0.04137161242446505</v>
       </c>
       <c r="F47" t="n">
-        <v>0.04784828424453735</v>
+        <v>0.02792175114154816</v>
       </c>
       <c r="G47" t="n">
-        <v>0.09388627058693341</v>
+        <v>0.07642695097658868</v>
       </c>
       <c r="H47" t="n">
-        <v>0.1327561312397275</v>
+        <v>0.12310884021442</v>
       </c>
       <c r="I47" t="n">
-        <v>0.05608780682086945</v>
+        <v>0.04343597590923309</v>
       </c>
       <c r="J47" t="n">
-        <v>0.1589672669768334</v>
+        <v>0.1191063940525056</v>
       </c>
       <c r="K47" t="n">
-        <v>0.6349315756559372</v>
+        <v>0.5980428421497345</v>
       </c>
       <c r="L47" t="n">
-        <v>0.6653261184692383</v>
+        <v>0.636717677116394</v>
       </c>
       <c r="M47" t="n">
-        <v>49.94749595224857</v>
+        <v>40.65913791954517</v>
       </c>
     </row>
     <row r="48">
@@ -52089,31 +52089,31 @@
         <v>2112</v>
       </c>
       <c r="E48" t="n">
-        <v>0.0701315842681762</v>
+        <v>0.03808989988950392</v>
       </c>
       <c r="F48" t="n">
-        <v>0.04647067189216614</v>
+        <v>0.0235406756401062</v>
       </c>
       <c r="G48" t="n">
-        <v>0.09307115708449573</v>
+        <v>0.07995744817890227</v>
       </c>
       <c r="H48" t="n">
-        <v>0.1218105691558442</v>
+        <v>0.1162843441846048</v>
       </c>
       <c r="I48" t="n">
-        <v>0.06057046353816986</v>
+        <v>0.04900650680065155</v>
       </c>
       <c r="J48" t="n">
-        <v>0.1943937748670578</v>
+        <v>0.1569606810808182</v>
       </c>
       <c r="K48" t="n">
-        <v>0.6773172342777243</v>
+        <v>0.6631655824184414</v>
       </c>
       <c r="L48" t="n">
-        <v>1.162625014781952</v>
+        <v>1.042850613594055</v>
       </c>
       <c r="M48" t="n">
-        <v>196.566283762455</v>
+        <v>168.8701305538416</v>
       </c>
     </row>
     <row r="49">
@@ -52136,31 +52136,31 @@
         <v>3172</v>
       </c>
       <c r="E49" t="n">
-        <v>0.1012431006751776</v>
+        <v>0.06044399286391305</v>
       </c>
       <c r="F49" t="n">
-        <v>0.07316218316555023</v>
+        <v>0.03839747607707977</v>
       </c>
       <c r="G49" t="n">
-        <v>0.1133894077014803</v>
+        <v>0.09432305605121398</v>
       </c>
       <c r="H49" t="n">
-        <v>0.1414886693284699</v>
+        <v>0.1481273275473764</v>
       </c>
       <c r="I49" t="n">
-        <v>0.07596307992935181</v>
+        <v>0.05847097933292389</v>
       </c>
       <c r="J49" t="n">
-        <v>0.2341008961200715</v>
+        <v>0.1589152932167053</v>
       </c>
       <c r="K49" t="n">
-        <v>0.7989101421833036</v>
+        <v>0.879116131067275</v>
       </c>
       <c r="L49" t="n">
-        <v>1.426825806498528</v>
+        <v>1.24364572763443</v>
       </c>
       <c r="M49" t="n">
-        <v>359.6712012290955</v>
+        <v>299.1927337944508</v>
       </c>
     </row>
     <row r="50">
@@ -52183,31 +52183,31 @@
         <v>5920</v>
       </c>
       <c r="E50" t="n">
-        <v>0.1623087066502587</v>
+        <v>0.118419445713831</v>
       </c>
       <c r="F50" t="n">
-        <v>0.1266597211360931</v>
+        <v>0.0644650012254715</v>
       </c>
       <c r="G50" t="n">
-        <v>0.1637236254088379</v>
+        <v>0.1435387874223493</v>
       </c>
       <c r="H50" t="n">
-        <v>0.1586329612612727</v>
+        <v>0.2874129263621578</v>
       </c>
       <c r="I50" t="n">
-        <v>0.1266597211360931</v>
+        <v>0.07744072377681732</v>
       </c>
       <c r="J50" t="n">
-        <v>0.3075093656778336</v>
+        <v>0.2158824980258942</v>
       </c>
       <c r="K50" t="n">
-        <v>0.8755953428149262</v>
+        <v>1.301535856723788</v>
       </c>
       <c r="L50" t="n">
-        <v>2.395393297076225</v>
+        <v>3.462271392345428</v>
       </c>
       <c r="M50" t="n">
-        <v>969.2438624203205</v>
+        <v>849.749621540308</v>
       </c>
     </row>
     <row r="51">
@@ -52230,31 +52230,31 @@
         <v>11191</v>
       </c>
       <c r="E51" t="n">
-        <v>0.2513723950742762</v>
+        <v>0.2259849724511246</v>
       </c>
       <c r="F51" t="n">
-        <v>0.2282349169254303</v>
+        <v>0.08967557549476624</v>
       </c>
       <c r="G51" t="n">
-        <v>0.2517613608558755</v>
+        <v>0.2495062318102871</v>
       </c>
       <c r="H51" t="n">
-        <v>0.154548848891833</v>
+        <v>0.498734704281759</v>
       </c>
       <c r="I51" t="n">
-        <v>0.2282349169254303</v>
+        <v>0.0966455340385437</v>
       </c>
       <c r="J51" t="n">
-        <v>0.4519622921943665</v>
+        <v>0.582019567489624</v>
       </c>
       <c r="K51" t="n">
-        <v>0.7912494778633126</v>
+        <v>2.845612329244615</v>
       </c>
       <c r="L51" t="n">
-        <v>1.099142909049988</v>
+        <v>3.710021734237671</v>
       </c>
       <c r="M51" t="n">
-        <v>2817.461389338103</v>
+        <v>2792.224240188923</v>
       </c>
     </row>
     <row r="52">
@@ -52277,31 +52277,31 @@
         <v>3764</v>
       </c>
       <c r="E52" t="n">
-        <v>0.829257759681897</v>
+        <v>1.150483063573195</v>
       </c>
       <c r="F52" t="n">
-        <v>0.760570652782917</v>
+        <v>0.9032644033432007</v>
       </c>
       <c r="G52" t="n">
-        <v>0.829257759681897</v>
+        <v>1.152569138142722</v>
       </c>
       <c r="H52" t="n">
-        <v>0.5288033170414868</v>
+        <v>0.8823639435342022</v>
       </c>
       <c r="I52" t="n">
-        <v>0.760570652782917</v>
+        <v>0.9032644033432007</v>
       </c>
       <c r="J52" t="n">
-        <v>1.423890486359597</v>
+        <v>2.32011481821537</v>
       </c>
       <c r="K52" t="n">
-        <v>2.936633792221546</v>
+        <v>2.901641991138458</v>
       </c>
       <c r="L52" t="n">
-        <v>3.16245299577713</v>
+        <v>3.053767442703247</v>
       </c>
       <c r="M52" t="n">
-        <v>3121.32620744266</v>
+        <v>4338.270235969205</v>
       </c>
     </row>
     <row r="53">
@@ -52324,31 +52324,31 @@
         <v>481</v>
       </c>
       <c r="E53" t="n">
-        <v>2.989523562689829</v>
+        <v>1.580773492086206</v>
       </c>
       <c r="F53" t="n">
-        <v>2.817423805594444</v>
+        <v>1.582239896059036</v>
       </c>
       <c r="G53" t="n">
-        <v>2.989523562689829</v>
+        <v>1.580773492086206</v>
       </c>
       <c r="H53" t="n">
-        <v>1.201070323031378</v>
+        <v>0.3434459533294651</v>
       </c>
       <c r="I53" t="n">
-        <v>2.817423805594444</v>
+        <v>1.582239896059036</v>
       </c>
       <c r="J53" t="n">
-        <v>4.773405596613884</v>
+        <v>2.054743036627769</v>
       </c>
       <c r="K53" t="n">
-        <v>6.132623812556266</v>
+        <v>2.140637290477753</v>
       </c>
       <c r="L53" t="n">
-        <v>6.475658938288689</v>
+        <v>2.167102128267288</v>
       </c>
       <c r="M53" t="n">
-        <v>1437.960833653808</v>
+        <v>760.3520496934652</v>
       </c>
     </row>
     <row r="54">
@@ -52465,31 +52465,31 @@
         <v>6103</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.02657007072675623</v>
+        <v>-0.01195165337740156</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.004586585886830557</v>
+        <v>-0.002701463177661957</v>
       </c>
       <c r="G56" t="n">
-        <v>0.09299442246553098</v>
+        <v>0.06251288944583067</v>
       </c>
       <c r="H56" t="n">
-        <v>0.1805457126495488</v>
+        <v>0.07417967770400216</v>
       </c>
       <c r="I56" t="n">
-        <v>0.04652153059413793</v>
+        <v>0.03676447555516953</v>
       </c>
       <c r="J56" t="n">
-        <v>0.2132267660828263</v>
+        <v>0.1579325786528158</v>
       </c>
       <c r="K56" t="n">
-        <v>0.5986563142587377</v>
+        <v>0.3156248851420799</v>
       </c>
       <c r="L56" t="n">
-        <v>4.914401962793144</v>
+        <v>0.6755232576604295</v>
       </c>
       <c r="M56" t="n">
-        <v>567.5449603071356</v>
+        <v>381.5161642879046</v>
       </c>
     </row>
     <row r="57">
@@ -52512,31 +52512,31 @@
         <v>23929</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.01086507659986017</v>
+        <v>-0.002850521667769615</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.002747729400950692</v>
+        <v>-0.000308830780583203</v>
       </c>
       <c r="G57" t="n">
-        <v>0.09906887068805569</v>
+        <v>0.06930718926780834</v>
       </c>
       <c r="H57" t="n">
-        <v>0.12310957108836</v>
+        <v>0.07424885651878686</v>
       </c>
       <c r="I57" t="n">
-        <v>0.05998285576668758</v>
+        <v>0.04474463735311027</v>
       </c>
       <c r="J57" t="n">
-        <v>0.2343639633251006</v>
+        <v>0.1666107849482798</v>
       </c>
       <c r="K57" t="n">
-        <v>0.5525479700537697</v>
+        <v>0.3285958368055339</v>
       </c>
       <c r="L57" t="n">
-        <v>2.460070442163943</v>
+        <v>0.6627152202928085</v>
       </c>
       <c r="M57" t="n">
-        <v>2370.619006694485</v>
+        <v>1658.451731989386</v>
       </c>
     </row>
     <row r="58">
@@ -52559,31 +52559,31 @@
         <v>39741</v>
       </c>
       <c r="E58" t="n">
-        <v>0.02940297738220826</v>
+        <v>0.01272488552628001</v>
       </c>
       <c r="F58" t="n">
-        <v>0.02561672242086847</v>
+        <v>0.01725470246302648</v>
       </c>
       <c r="G58" t="n">
-        <v>0.135944369035926</v>
+        <v>0.09504655570105426</v>
       </c>
       <c r="H58" t="n">
-        <v>0.125279659141711</v>
+        <v>0.08954828026276725</v>
       </c>
       <c r="I58" t="n">
-        <v>0.09887399187905713</v>
+        <v>0.06927595993275919</v>
       </c>
       <c r="J58" t="n">
-        <v>0.3113098840443639</v>
+        <v>0.2083389933257528</v>
       </c>
       <c r="K58" t="n">
-        <v>0.5586479053738863</v>
+        <v>0.4204799497684587</v>
       </c>
       <c r="L58" t="n">
-        <v>1.46669315702075</v>
+        <v>0.6660683923713455</v>
       </c>
       <c r="M58" t="n">
-        <v>5402.565169856734</v>
+        <v>3777.245170115597</v>
       </c>
     </row>
     <row r="59">
@@ -52606,31 +52606,31 @@
         <v>80472</v>
       </c>
       <c r="E59" t="n">
-        <v>0.1087351648726803</v>
+        <v>0.04167217380492533</v>
       </c>
       <c r="F59" t="n">
-        <v>0.1110550685654127</v>
+        <v>0.05707615845684922</v>
       </c>
       <c r="G59" t="n">
-        <v>0.2021907422094908</v>
+        <v>0.1336582155159396</v>
       </c>
       <c r="H59" t="n">
-        <v>0.1502006351081779</v>
+        <v>0.1088594694110972</v>
       </c>
       <c r="I59" t="n">
-        <v>0.1711439661804973</v>
+        <v>0.1076032141621001</v>
       </c>
       <c r="J59" t="n">
-        <v>0.4261040651545088</v>
+        <v>0.2796219478322616</v>
       </c>
       <c r="K59" t="n">
-        <v>0.589706230628723</v>
+        <v>0.4937457591475647</v>
       </c>
       <c r="L59" t="n">
-        <v>0.888430210806184</v>
+        <v>0.9523287604814238</v>
       </c>
       <c r="M59" t="n">
-        <v>16270.69340708215</v>
+        <v>10755.7439189987</v>
       </c>
     </row>
     <row r="60">
@@ -52653,31 +52653,31 @@
         <v>141166</v>
       </c>
       <c r="E60" t="n">
-        <v>0.2580864224416616</v>
+        <v>0.09312947385701571</v>
       </c>
       <c r="F60" t="n">
-        <v>0.3115462961460149</v>
+        <v>0.1270767048785336</v>
       </c>
       <c r="G60" t="n">
-        <v>0.3297310363783183</v>
+        <v>0.1927747219771679</v>
       </c>
       <c r="H60" t="n">
-        <v>0.1835809922022144</v>
+        <v>0.1323703638147042</v>
       </c>
       <c r="I60" t="n">
-        <v>0.3329573750763073</v>
+        <v>0.1758578738244929</v>
       </c>
       <c r="J60" t="n">
-        <v>0.5633362320792488</v>
+        <v>0.3627382217456199</v>
       </c>
       <c r="K60" t="n">
-        <v>0.7104349849154016</v>
+        <v>0.5701688024930637</v>
       </c>
       <c r="L60" t="n">
-        <v>1.106260707456246</v>
+        <v>1.064540354704751</v>
       </c>
       <c r="M60" t="n">
-        <v>46546.81148138168</v>
+        <v>27213.23640262888</v>
       </c>
     </row>
     <row r="61">
@@ -52700,31 +52700,31 @@
         <v>69306</v>
       </c>
       <c r="E61" t="n">
-        <v>0.3641134083356553</v>
+        <v>0.09099580569799623</v>
       </c>
       <c r="F61" t="n">
-        <v>0.4465765781211046</v>
+        <v>0.1125359257376447</v>
       </c>
       <c r="G61" t="n">
-        <v>0.421225838397218</v>
+        <v>0.2109827867857492</v>
       </c>
       <c r="H61" t="n">
-        <v>0.189105991822046</v>
+        <v>0.154457141125935</v>
       </c>
       <c r="I61" t="n">
-        <v>0.456703091288494</v>
+        <v>0.1889576631885601</v>
       </c>
       <c r="J61" t="n">
-        <v>0.6365279182358932</v>
+        <v>0.4154899989583286</v>
       </c>
       <c r="K61" t="n">
-        <v>0.7535912597144299</v>
+        <v>0.6445602978923181</v>
       </c>
       <c r="L61" t="n">
-        <v>1.192412536412511</v>
+        <v>1.243206545081916</v>
       </c>
       <c r="M61" t="n">
-        <v>29193.47795595759</v>
+        <v>14622.37302097313</v>
       </c>
     </row>
     <row r="62">
@@ -52747,31 +52747,31 @@
         <v>2684</v>
       </c>
       <c r="E62" t="n">
-        <v>0.07591770785247484</v>
+        <v>-0.07729812895725839</v>
       </c>
       <c r="F62" t="n">
-        <v>0.2154712112011921</v>
+        <v>-0.06846153990058761</v>
       </c>
       <c r="G62" t="n">
-        <v>0.4648606409510359</v>
+        <v>0.2220708913151259</v>
       </c>
       <c r="H62" t="n">
-        <v>0.3397596897186312</v>
+        <v>0.1763652926846797</v>
       </c>
       <c r="I62" t="n">
-        <v>0.4701950082915508</v>
+        <v>0.1754878924938826</v>
       </c>
       <c r="J62" t="n">
-        <v>0.6872487020672896</v>
+        <v>0.4471066005770451</v>
       </c>
       <c r="K62" t="n">
-        <v>1.877301497964551</v>
+        <v>0.6345371180715688</v>
       </c>
       <c r="L62" t="n">
-        <v>2.370167712620956</v>
+        <v>0.6353180741430873</v>
       </c>
       <c r="M62" t="n">
-        <v>1247.68596031258</v>
+        <v>596.038272289798</v>
       </c>
     </row>
     <row r="63">
@@ -52888,31 +52888,31 @@
         <v>5</v>
       </c>
       <c r="E65" t="n">
-        <v>0.3081309676170349</v>
+        <v>0.3086057543754578</v>
       </c>
       <c r="F65" t="n">
-        <v>0.309478223323822</v>
+        <v>0.3090832829475403</v>
       </c>
       <c r="G65" t="n">
-        <v>0.3081309676170349</v>
+        <v>0.3086057543754578</v>
       </c>
       <c r="H65" t="n">
-        <v>0.03648038368269375</v>
+        <v>0.03708423689913685</v>
       </c>
       <c r="I65" t="n">
-        <v>0.309478223323822</v>
+        <v>0.3090832829475403</v>
       </c>
       <c r="J65" t="n">
-        <v>0.3501454830169678</v>
+        <v>0.3514577746391296</v>
       </c>
       <c r="K65" t="n">
-        <v>0.3600344443321228</v>
+        <v>0.360882842540741</v>
       </c>
       <c r="L65" t="n">
-        <v>0.3611332178115845</v>
+        <v>0.3619300723075867</v>
       </c>
       <c r="M65" t="n">
-        <v>1.540654838085175</v>
+        <v>1.543028771877289</v>
       </c>
     </row>
     <row r="66">
@@ -52935,31 +52935,31 @@
         <v>57</v>
       </c>
       <c r="E66" t="n">
-        <v>0.2447729717221176</v>
+        <v>0.2447037383129722</v>
       </c>
       <c r="F66" t="n">
-        <v>0.2515091896057129</v>
+        <v>0.2463347315788269</v>
       </c>
       <c r="G66" t="n">
-        <v>0.2447729717221176</v>
+        <v>0.2447037383129722</v>
       </c>
       <c r="H66" t="n">
-        <v>0.1182237465360619</v>
+        <v>0.1195075500663037</v>
       </c>
       <c r="I66" t="n">
-        <v>0.2515091896057129</v>
+        <v>0.2463347315788269</v>
       </c>
       <c r="J66" t="n">
-        <v>0.3990333676338196</v>
+        <v>0.4001929521560669</v>
       </c>
       <c r="K66" t="n">
-        <v>0.4091384601593017</v>
+        <v>0.4150546956062316</v>
       </c>
       <c r="L66" t="n">
-        <v>0.411823034286499</v>
+        <v>0.4191907048225403</v>
       </c>
       <c r="M66" t="n">
-        <v>13.95205938816071</v>
+        <v>13.94811308383942</v>
       </c>
     </row>
     <row r="67">
@@ -52982,31 +52982,31 @@
         <v>178</v>
       </c>
       <c r="E67" t="n">
-        <v>0.2240724419609884</v>
+        <v>0.2239539254917188</v>
       </c>
       <c r="F67" t="n">
-        <v>0.2164376974105835</v>
+        <v>0.2170394361019135</v>
       </c>
       <c r="G67" t="n">
-        <v>0.2240724419609884</v>
+        <v>0.2239539254917188</v>
       </c>
       <c r="H67" t="n">
-        <v>0.1107542150390205</v>
+        <v>0.1144294850701614</v>
       </c>
       <c r="I67" t="n">
-        <v>0.2164376974105835</v>
+        <v>0.2170394361019135</v>
       </c>
       <c r="J67" t="n">
-        <v>0.4013378441333772</v>
+        <v>0.4058348119258881</v>
       </c>
       <c r="K67" t="n">
-        <v>0.4385977637767791</v>
+        <v>0.4509467440843581</v>
       </c>
       <c r="L67" t="n">
-        <v>0.4522165656089783</v>
+        <v>0.4637700915336609</v>
       </c>
       <c r="M67" t="n">
-        <v>39.88489466905594</v>
+        <v>39.86379873752594</v>
       </c>
     </row>
     <row r="68">
@@ -53029,31 +53029,31 @@
         <v>481</v>
       </c>
       <c r="E68" t="n">
-        <v>0.2159943749156167</v>
+        <v>0.2229459122164086</v>
       </c>
       <c r="F68" t="n">
-        <v>0.215010404586792</v>
+        <v>0.212742805480957</v>
       </c>
       <c r="G68" t="n">
-        <v>0.2159943749156167</v>
+        <v>0.2229459122164086</v>
       </c>
       <c r="H68" t="n">
-        <v>0.08309623527329629</v>
+        <v>0.09344056577313571</v>
       </c>
       <c r="I68" t="n">
-        <v>0.215010404586792</v>
+        <v>0.212742805480957</v>
       </c>
       <c r="J68" t="n">
-        <v>0.3340384960174561</v>
+        <v>0.348785400390625</v>
       </c>
       <c r="K68" t="n">
-        <v>0.4635311961174011</v>
+        <v>0.4810386180877685</v>
       </c>
       <c r="L68" t="n">
-        <v>0.4809874892234802</v>
+        <v>0.5013360381126404</v>
       </c>
       <c r="M68" t="n">
-        <v>103.8932943344116</v>
+        <v>107.2369837760925</v>
       </c>
     </row>
     <row r="69">
@@ -53076,31 +53076,31 @@
         <v>938</v>
       </c>
       <c r="E69" t="n">
-        <v>0.3024680007304718</v>
+        <v>0.3320934019808068</v>
       </c>
       <c r="F69" t="n">
-        <v>0.2611753046512604</v>
+        <v>0.2846477627754211</v>
       </c>
       <c r="G69" t="n">
-        <v>0.3024680007304718</v>
+        <v>0.3320934019808068</v>
       </c>
       <c r="H69" t="n">
-        <v>0.1373018977943839</v>
+        <v>0.162802679993374</v>
       </c>
       <c r="I69" t="n">
-        <v>0.2611753046512604</v>
+        <v>0.2846477627754211</v>
       </c>
       <c r="J69" t="n">
-        <v>0.554729163646698</v>
+        <v>0.6147586405277254</v>
       </c>
       <c r="K69" t="n">
-        <v>0.5944423675537109</v>
+        <v>0.6947143390774727</v>
       </c>
       <c r="L69" t="n">
-        <v>0.6029233932495117</v>
+        <v>0.7052217721939087</v>
       </c>
       <c r="M69" t="n">
-        <v>283.7149846851826</v>
+        <v>311.5036110579967</v>
       </c>
     </row>
     <row r="70">
@@ -53123,31 +53123,31 @@
         <v>1529</v>
       </c>
       <c r="E70" t="n">
-        <v>0.5790982999350995</v>
+        <v>0.6607951048817644</v>
       </c>
       <c r="F70" t="n">
-        <v>0.5617955327033997</v>
+        <v>0.6520892977714539</v>
       </c>
       <c r="G70" t="n">
-        <v>0.5790982999350995</v>
+        <v>0.6607951048817644</v>
       </c>
       <c r="H70" t="n">
-        <v>0.1471807436595628</v>
+        <v>0.1865143084239847</v>
       </c>
       <c r="I70" t="n">
-        <v>0.5617955327033997</v>
+        <v>0.6520892977714539</v>
       </c>
       <c r="J70" t="n">
-        <v>0.7831342637538911</v>
+        <v>0.9109561383724213</v>
       </c>
       <c r="K70" t="n">
-        <v>0.8474013286828995</v>
+        <v>0.9543749397993088</v>
       </c>
       <c r="L70" t="n">
-        <v>0.853394627571106</v>
+        <v>0.961571216583252</v>
       </c>
       <c r="M70" t="n">
-        <v>885.4413006007671</v>
+        <v>1010.355715364218</v>
       </c>
     </row>
     <row r="71">
@@ -53170,31 +53170,31 @@
         <v>709</v>
       </c>
       <c r="E71" t="n">
-        <v>0.7721950548066533</v>
+        <v>0.7517630355393222</v>
       </c>
       <c r="F71" t="n">
-        <v>0.8716187495738268</v>
+        <v>0.8642666395753622</v>
       </c>
       <c r="G71" t="n">
-        <v>0.7721950548066533</v>
+        <v>0.7517630355393222</v>
       </c>
       <c r="H71" t="n">
-        <v>0.1556168836735756</v>
+        <v>0.176422111679742</v>
       </c>
       <c r="I71" t="n">
-        <v>0.8716187495738268</v>
+        <v>0.8642666395753622</v>
       </c>
       <c r="J71" t="n">
-        <v>0.9102834671735763</v>
+        <v>0.9195179551839828</v>
       </c>
       <c r="K71" t="n">
-        <v>0.9474271115660667</v>
+        <v>0.9278263029456139</v>
       </c>
       <c r="L71" t="n">
-        <v>0.9539253935217857</v>
+        <v>0.930720292031765</v>
       </c>
       <c r="M71" t="n">
-        <v>547.4862938579172</v>
+        <v>532.9999921973795</v>
       </c>
     </row>
     <row r="72">
@@ -53217,31 +53217,31 @@
         <v>62</v>
       </c>
       <c r="E72" t="n">
-        <v>0.9391085881619684</v>
+        <v>0.9297793153072557</v>
       </c>
       <c r="F72" t="n">
-        <v>0.948795311152935</v>
+        <v>0.9309066757559776</v>
       </c>
       <c r="G72" t="n">
-        <v>0.9391085881619684</v>
+        <v>0.9297793153072557</v>
       </c>
       <c r="H72" t="n">
-        <v>0.01931394919002043</v>
+        <v>0.006791843388764891</v>
       </c>
       <c r="I72" t="n">
-        <v>0.948795311152935</v>
+        <v>0.9309066757559776</v>
       </c>
       <c r="J72" t="n">
-        <v>0.9558013245463371</v>
+        <v>0.9379844054579735</v>
       </c>
       <c r="K72" t="n">
-        <v>0.9573203781247139</v>
+        <v>0.9412718304991722</v>
       </c>
       <c r="L72" t="n">
-        <v>0.9573894962668419</v>
+        <v>0.9417734369635582</v>
       </c>
       <c r="M72" t="n">
-        <v>58.22473246604204</v>
+        <v>57.64631754904985</v>
       </c>
     </row>
     <row r="73">
@@ -53311,31 +53311,31 @@
         <v>3583</v>
       </c>
       <c r="E74" t="n">
-        <v>-0.1042429278452546</v>
+        <v>-0.0617602227134629</v>
       </c>
       <c r="F74" t="n">
-        <v>0.004446438262725175</v>
+        <v>0.002072006641956645</v>
       </c>
       <c r="G74" t="n">
-        <v>0.2487878826972931</v>
+        <v>0.1635855106396012</v>
       </c>
       <c r="H74" t="n">
-        <v>0.5022334234774145</v>
+        <v>0.2971237838250539</v>
       </c>
       <c r="I74" t="n">
-        <v>0.1098799639372584</v>
+        <v>0.07484623452701644</v>
       </c>
       <c r="J74" t="n">
-        <v>0.5049129302835661</v>
+        <v>0.3520271215206924</v>
       </c>
       <c r="K74" t="n">
-        <v>2.77140259276096</v>
+        <v>1.703915797377585</v>
       </c>
       <c r="L74" t="n">
-        <v>8.038418351576947</v>
+        <v>3.862229827749076</v>
       </c>
       <c r="M74" t="n">
-        <v>891.4069837044012</v>
+        <v>586.126884621691</v>
       </c>
     </row>
     <row r="75">
@@ -53358,31 +53358,31 @@
         <v>14154</v>
       </c>
       <c r="E75" t="n">
-        <v>-0.05098602958416483</v>
+        <v>-0.04509815934068659</v>
       </c>
       <c r="F75" t="n">
-        <v>0.009228082311191248</v>
+        <v>0.007863345054596063</v>
       </c>
       <c r="G75" t="n">
-        <v>0.2305527079759005</v>
+        <v>0.1704421887756485</v>
       </c>
       <c r="H75" t="n">
-        <v>0.3167412258530964</v>
+        <v>0.2351650052198152</v>
       </c>
       <c r="I75" t="n">
-        <v>0.1385292666917779</v>
+        <v>0.09909565625596725</v>
       </c>
       <c r="J75" t="n">
-        <v>0.4984754165278784</v>
+        <v>0.3677284253827981</v>
       </c>
       <c r="K75" t="n">
-        <v>1.701033860467214</v>
+        <v>1.343940514421535</v>
       </c>
       <c r="L75" t="n">
-        <v>4.877977037250182</v>
+        <v>2.951350006221227</v>
       </c>
       <c r="M75" t="n">
-        <v>3263.243028690895</v>
+        <v>2412.438739930529</v>
       </c>
     </row>
     <row r="76">
@@ -53405,31 +53405,31 @@
         <v>22959</v>
       </c>
       <c r="E76" t="n">
-        <v>0.03419055549996438</v>
+        <v>-0.05365886158659798</v>
       </c>
       <c r="F76" t="n">
-        <v>0.06175476531809333</v>
+        <v>0.01132423341420062</v>
       </c>
       <c r="G76" t="n">
-        <v>0.2538662927924788</v>
+        <v>0.2162030902116746</v>
       </c>
       <c r="H76" t="n">
-        <v>0.2394496582154252</v>
+        <v>0.2551753116974972</v>
       </c>
       <c r="I76" t="n">
-        <v>0.1900343547111506</v>
+        <v>0.1425771886650513</v>
       </c>
       <c r="J76" t="n">
-        <v>0.5449012987999295</v>
+        <v>0.463038128631802</v>
       </c>
       <c r="K76" t="n">
-        <v>1.205606093804282</v>
+        <v>1.377744517901433</v>
       </c>
       <c r="L76" t="n">
-        <v>2.71002203548595</v>
+        <v>2.834884285967992</v>
       </c>
       <c r="M76" t="n">
-        <v>5828.516216222521</v>
+        <v>4963.806748169838</v>
       </c>
     </row>
     <row r="77">
@@ -53452,31 +53452,31 @@
         <v>44934</v>
       </c>
       <c r="E77" t="n">
-        <v>0.1960827378159363</v>
+        <v>-0.09194751708701369</v>
       </c>
       <c r="F77" t="n">
-        <v>0.2468763589411367</v>
+        <v>0.01361946174953994</v>
       </c>
       <c r="G77" t="n">
-        <v>0.3510725596033456</v>
+        <v>0.3104452320037314</v>
       </c>
       <c r="H77" t="n">
-        <v>0.2393432044534866</v>
+        <v>0.3790074821752798</v>
       </c>
       <c r="I77" t="n">
-        <v>0.3151067246695328</v>
+        <v>0.2152674534786443</v>
       </c>
       <c r="J77" t="n">
-        <v>0.6693659144050286</v>
+        <v>0.659862350693894</v>
       </c>
       <c r="K77" t="n">
-        <v>1.047990388055719</v>
+        <v>1.763439148798178</v>
       </c>
       <c r="L77" t="n">
-        <v>2.119302031112719</v>
+        <v>8.261525178140156</v>
       </c>
       <c r="M77" t="n">
-        <v>15775.09439321673</v>
+        <v>13949.54605485566</v>
       </c>
     </row>
     <row r="78">
@@ -53499,31 +53499,31 @@
         <v>73777</v>
       </c>
       <c r="E78" t="n">
-        <v>0.3823760022999058</v>
+        <v>-0.2866738228327208</v>
       </c>
       <c r="F78" t="n">
-        <v>0.4775968383551109</v>
+        <v>-0.07576761582481982</v>
       </c>
       <c r="G78" t="n">
-        <v>0.4902038417294085</v>
+        <v>0.532831532691961</v>
       </c>
       <c r="H78" t="n">
-        <v>0.2508016310496665</v>
+        <v>0.8177444978644637</v>
       </c>
       <c r="I78" t="n">
-        <v>0.5158265343496706</v>
+        <v>0.3260770973645999</v>
       </c>
       <c r="J78" t="n">
-        <v>0.7780227387467917</v>
+        <v>1.06169539017012</v>
       </c>
       <c r="K78" t="n">
-        <v>0.8818884794420736</v>
+        <v>3.937387161651145</v>
       </c>
       <c r="L78" t="n">
-        <v>3.461539405721656</v>
+        <v>10.53718535982954</v>
       </c>
       <c r="M78" t="n">
-        <v>36165.76883127057</v>
+        <v>39310.71198741481</v>
       </c>
     </row>
     <row r="79">
@@ -53546,31 +53546,31 @@
         <v>34233</v>
       </c>
       <c r="E79" t="n">
-        <v>0.4355083979015833</v>
+        <v>-0.600830170667904</v>
       </c>
       <c r="F79" t="n">
-        <v>0.5490799709543612</v>
+        <v>-0.2822557271417941</v>
       </c>
       <c r="G79" t="n">
-        <v>0.5074012476092408</v>
+        <v>0.776066891363233</v>
       </c>
       <c r="H79" t="n">
-        <v>0.2621851396813956</v>
+        <v>1.011840322656275</v>
       </c>
       <c r="I79" t="n">
-        <v>0.5568666922374912</v>
+        <v>0.4138255499366485</v>
       </c>
       <c r="J79" t="n">
-        <v>0.8137079118649161</v>
+        <v>1.885654640636547</v>
       </c>
       <c r="K79" t="n">
-        <v>0.8869371822903446</v>
+        <v>5.506895574103625</v>
       </c>
       <c r="L79" t="n">
-        <v>4.38152729689803</v>
+        <v>9.651859033163827</v>
       </c>
       <c r="M79" t="n">
-        <v>17369.86690940714</v>
+        <v>26567.09789203756</v>
       </c>
     </row>
     <row r="80">
@@ -53593,31 +53593,31 @@
         <v>685</v>
       </c>
       <c r="E80" t="n">
-        <v>0.06048093727337394</v>
+        <v>-1.973624738973572</v>
       </c>
       <c r="F80" t="n">
-        <v>0.1715396395959134</v>
+        <v>-1.18855789290365</v>
       </c>
       <c r="G80" t="n">
-        <v>0.5126925784609248</v>
+        <v>1.997720497244293</v>
       </c>
       <c r="H80" t="n">
-        <v>0.3191965488050191</v>
+        <v>2.175305753309888</v>
       </c>
       <c r="I80" t="n">
-        <v>0.5789897770360382</v>
+        <v>1.18855789290365</v>
       </c>
       <c r="J80" t="n">
-        <v>0.9077931207574361</v>
+        <v>5.772705999603504</v>
       </c>
       <c r="K80" t="n">
-        <v>1.463287480755048</v>
+        <v>8.36489995895117</v>
       </c>
       <c r="L80" t="n">
-        <v>1.748058779664104</v>
+        <v>8.466542981965061</v>
       </c>
       <c r="M80" t="n">
-        <v>351.1944162457335</v>
+        <v>1368.438540612341</v>
       </c>
     </row>
     <row r="81">
@@ -53734,31 +53734,31 @@
         <v>1663</v>
       </c>
       <c r="E83" t="n">
-        <v>0.03634280879588118</v>
+        <v>0.03507748284442681</v>
       </c>
       <c r="F83" t="n">
-        <v>0.01110470294952393</v>
+        <v>0.006834611296653748</v>
       </c>
       <c r="G83" t="n">
-        <v>0.04492371906293976</v>
+        <v>0.04425809680418712</v>
       </c>
       <c r="H83" t="n">
-        <v>0.09798404202492279</v>
+        <v>0.1049117223224358</v>
       </c>
       <c r="I83" t="n">
-        <v>0.01783205568790436</v>
+        <v>0.01594185829162598</v>
       </c>
       <c r="J83" t="n">
-        <v>0.1012050509452819</v>
+        <v>0.1129806637763977</v>
       </c>
       <c r="K83" t="n">
-        <v>0.3836507177352887</v>
+        <v>0.4085023474693291</v>
       </c>
       <c r="L83" t="n">
-        <v>1.520093575119972</v>
+        <v>1.749957576394081</v>
       </c>
       <c r="M83" t="n">
-        <v>74.70814480166882</v>
+        <v>73.60121498536319</v>
       </c>
     </row>
     <row r="84">
@@ -53781,31 +53781,31 @@
         <v>6289</v>
       </c>
       <c r="E84" t="n">
-        <v>0.05623593240812294</v>
+        <v>0.05458906412894138</v>
       </c>
       <c r="F84" t="n">
-        <v>0.0211828351020813</v>
+        <v>0.01607643067836761</v>
       </c>
       <c r="G84" t="n">
-        <v>0.06606893806594678</v>
+        <v>0.0677167313165243</v>
       </c>
       <c r="H84" t="n">
-        <v>0.1219459729722606</v>
+        <v>0.1375908275449458</v>
       </c>
       <c r="I84" t="n">
-        <v>0.02914398908615112</v>
+        <v>0.02612996101379395</v>
       </c>
       <c r="J84" t="n">
-        <v>0.1782132983207702</v>
+        <v>0.1907278299331664</v>
       </c>
       <c r="K84" t="n">
-        <v>0.4983663976192472</v>
+        <v>0.5698840516805636</v>
       </c>
       <c r="L84" t="n">
-        <v>1.631305396556854</v>
+        <v>2.033716216683388</v>
       </c>
       <c r="M84" t="n">
-        <v>415.5075514967393</v>
+        <v>425.8705232496213</v>
       </c>
     </row>
     <row r="85">
@@ -53828,31 +53828,31 @@
         <v>10113</v>
       </c>
       <c r="E85" t="n">
-        <v>0.1006702138998886</v>
+        <v>0.1039926768376929</v>
       </c>
       <c r="F85" t="n">
-        <v>0.04405069351196289</v>
+        <v>0.03062494099140167</v>
       </c>
       <c r="G85" t="n">
-        <v>0.1086234268808472</v>
+        <v>0.1172483342269858</v>
       </c>
       <c r="H85" t="n">
-        <v>0.1706863641171509</v>
+        <v>0.2113313061359292</v>
       </c>
       <c r="I85" t="n">
-        <v>0.04718410968780518</v>
+        <v>0.03476671874523163</v>
       </c>
       <c r="J85" t="n">
-        <v>0.2785035133361818</v>
+        <v>0.3384229481220248</v>
       </c>
       <c r="K85" t="n">
-        <v>0.7957664477825146</v>
+        <v>0.9009155404567646</v>
       </c>
       <c r="L85" t="n">
-        <v>1.706420049071312</v>
+        <v>2.190909639000893</v>
       </c>
       <c r="M85" t="n">
-        <v>1098.508716046008</v>
+        <v>1185.732404037508</v>
       </c>
     </row>
     <row r="86">
@@ -53875,31 +53875,31 @@
         <v>19474</v>
       </c>
       <c r="E86" t="n">
-        <v>0.1721962311411702</v>
+        <v>0.2066500573581681</v>
       </c>
       <c r="F86" t="n">
-        <v>0.09728970378637314</v>
+        <v>0.07080140709877014</v>
       </c>
       <c r="G86" t="n">
-        <v>0.1763956343588839</v>
+        <v>0.2170247900509433</v>
       </c>
       <c r="H86" t="n">
-        <v>0.2227177171771842</v>
+        <v>0.3427551671328272</v>
       </c>
       <c r="I86" t="n">
-        <v>0.09755533188581467</v>
+        <v>0.07458540052175522</v>
       </c>
       <c r="J86" t="n">
-        <v>0.4127410590648651</v>
+        <v>0.6000929871341215</v>
       </c>
       <c r="K86" t="n">
-        <v>1.183308382481337</v>
+        <v>1.757358313798909</v>
       </c>
       <c r="L86" t="n">
-        <v>1.640799507498741</v>
+        <v>2.72085902094841</v>
       </c>
       <c r="M86" t="n">
-        <v>3435.128583504906</v>
+        <v>4226.340761452069</v>
       </c>
     </row>
     <row r="87">
@@ -53922,31 +53922,31 @@
         <v>36293</v>
       </c>
       <c r="E87" t="n">
-        <v>0.234914617762987</v>
+        <v>0.3222727125059944</v>
       </c>
       <c r="F87" t="n">
-        <v>0.1651052087545395</v>
+        <v>0.1386795789003372</v>
       </c>
       <c r="G87" t="n">
-        <v>0.2370883915753636</v>
+        <v>0.3325862670207341</v>
       </c>
       <c r="H87" t="n">
-        <v>0.224618485486359</v>
+        <v>0.4670532717757173</v>
       </c>
       <c r="I87" t="n">
-        <v>0.1651052087545395</v>
+        <v>0.1393122225999832</v>
       </c>
       <c r="J87" t="n">
-        <v>0.5021272003650665</v>
+        <v>0.8845983505249023</v>
       </c>
       <c r="K87" t="n">
-        <v>1.123010990619663</v>
+        <v>2.055536620616915</v>
       </c>
       <c r="L87" t="n">
-        <v>1.870495676994324</v>
+        <v>5.169138729572296</v>
       </c>
       <c r="M87" t="n">
-        <v>8604.64899544467</v>
+        <v>12070.5533889835</v>
       </c>
     </row>
     <row r="88">
@@ -53969,31 +53969,31 @@
         <v>25600</v>
       </c>
       <c r="E88" t="n">
-        <v>0.310550827358906</v>
+        <v>0.5284658529428401</v>
       </c>
       <c r="F88" t="n">
-        <v>0.2476837337017059</v>
+        <v>0.3513936698436737</v>
       </c>
       <c r="G88" t="n">
-        <v>0.3110420913254477</v>
+        <v>0.5304501154907615</v>
       </c>
       <c r="H88" t="n">
-        <v>0.2434236423888628</v>
+        <v>0.659169038420609</v>
       </c>
       <c r="I88" t="n">
-        <v>0.2476837337017059</v>
+        <v>0.3513936698436737</v>
       </c>
       <c r="J88" t="n">
-        <v>0.6583208933472644</v>
+        <v>1.264649862051011</v>
       </c>
       <c r="K88" t="n">
-        <v>1.042765769064425</v>
+        <v>2.254531489908694</v>
       </c>
       <c r="L88" t="n">
-        <v>2.651568412780762</v>
+        <v>6.218338310718536</v>
       </c>
       <c r="M88" t="n">
-        <v>7962.677537931462</v>
+        <v>13579.52295656349</v>
       </c>
     </row>
     <row r="89">
@@ -54016,31 +54016,31 @@
         <v>1155</v>
       </c>
       <c r="E89" t="n">
-        <v>0.8128695202467245</v>
+        <v>1.069736276805659</v>
       </c>
       <c r="F89" t="n">
-        <v>0.4788781404495239</v>
+        <v>0.7930287718772888</v>
       </c>
       <c r="G89" t="n">
-        <v>0.8128702931976938</v>
+        <v>1.070540385522368</v>
       </c>
       <c r="H89" t="n">
-        <v>0.7714282040534598</v>
+        <v>0.7649709539438916</v>
       </c>
       <c r="I89" t="n">
-        <v>0.4788781404495239</v>
+        <v>0.7930287718772888</v>
       </c>
       <c r="J89" t="n">
-        <v>2.00793319940567</v>
+        <v>2.145333033800126</v>
       </c>
       <c r="K89" t="n">
-        <v>3.111451807022096</v>
+        <v>2.223906328082085</v>
       </c>
       <c r="L89" t="n">
-        <v>3.417383909225464</v>
+        <v>2.234119907021523</v>
       </c>
       <c r="M89" t="n">
-        <v>938.8651886433363</v>
+        <v>1236.474145278335</v>
       </c>
     </row>
     <row r="90">
@@ -54157,31 +54157,31 @@
         <v>4011</v>
       </c>
       <c r="E92" t="n">
-        <v>-0.02547223393720958</v>
+        <v>-0.0119939615510891</v>
       </c>
       <c r="F92" t="n">
-        <v>-0.00179189779831547</v>
+        <v>-0.003123493163206176</v>
       </c>
       <c r="G92" t="n">
-        <v>0.1095256188196409</v>
+        <v>0.06351046891825395</v>
       </c>
       <c r="H92" t="n">
-        <v>0.1805715186189959</v>
+        <v>0.07514251597546516</v>
       </c>
       <c r="I92" t="n">
-        <v>0.0535261952111904</v>
+        <v>0.03648328303422877</v>
       </c>
       <c r="J92" t="n">
-        <v>0.2709648688752957</v>
+        <v>0.157839775285751</v>
       </c>
       <c r="K92" t="n">
-        <v>0.6253850862541732</v>
+        <v>0.3419831517676359</v>
       </c>
       <c r="L92" t="n">
-        <v>3.891849661572965</v>
+        <v>0.719481495682224</v>
       </c>
       <c r="M92" t="n">
-        <v>439.3072570855796</v>
+        <v>254.7404908311166</v>
       </c>
     </row>
     <row r="93">
@@ -54204,31 +54204,31 @@
         <v>16335</v>
       </c>
       <c r="E93" t="n">
-        <v>-0.003538219016056267</v>
+        <v>0.0003077295046655689</v>
       </c>
       <c r="F93" t="n">
-        <v>0.006919923860315082</v>
+        <v>0.002880173625283615</v>
       </c>
       <c r="G93" t="n">
-        <v>0.11745890571087</v>
+        <v>0.06964017666130111</v>
       </c>
       <c r="H93" t="n">
-        <v>0.1577918229473631</v>
+        <v>0.0816987970546553</v>
       </c>
       <c r="I93" t="n">
-        <v>0.0666095195048567</v>
+        <v>0.04292117393488894</v>
       </c>
       <c r="J93" t="n">
-        <v>0.2782459263004262</v>
+        <v>0.1657072633340929</v>
       </c>
       <c r="K93" t="n">
-        <v>0.6604768763040513</v>
+        <v>0.3644051233080261</v>
       </c>
       <c r="L93" t="n">
-        <v>2.981968689844811</v>
+        <v>0.8371089182234354</v>
       </c>
       <c r="M93" t="n">
-        <v>1918.691224787062</v>
+        <v>1137.572285762354</v>
       </c>
     </row>
     <row r="94">
@@ -54251,31 +54251,31 @@
         <v>26722</v>
       </c>
       <c r="E94" t="n">
-        <v>0.05260396878202254</v>
+        <v>0.0209335020556137</v>
       </c>
       <c r="F94" t="n">
-        <v>0.0442259353311319</v>
+        <v>0.02322020109786302</v>
       </c>
       <c r="G94" t="n">
-        <v>0.1503081921873439</v>
+        <v>0.09681934918874918</v>
       </c>
       <c r="H94" t="n">
-        <v>0.1403681367767593</v>
+        <v>0.09913636674272046</v>
       </c>
       <c r="I94" t="n">
-        <v>0.1097251597660237</v>
+        <v>0.06690856211897964</v>
       </c>
       <c r="J94" t="n">
-        <v>0.3427992737720517</v>
+        <v>0.2220871947541903</v>
       </c>
       <c r="K94" t="n">
-        <v>0.6031134036885873</v>
+        <v>0.4600731864932268</v>
       </c>
       <c r="L94" t="n">
-        <v>1.435842804837437</v>
+        <v>0.9426464112343665</v>
       </c>
       <c r="M94" t="n">
-        <v>4016.535511630203</v>
+        <v>2587.206649021756</v>
       </c>
     </row>
     <row r="95">
@@ -54298,31 +54298,31 @@
         <v>52143</v>
       </c>
       <c r="E95" t="n">
-        <v>0.1531932879433265</v>
+        <v>0.05220259579309018</v>
       </c>
       <c r="F95" t="n">
-        <v>0.1551247992591247</v>
+        <v>0.06275860125731555</v>
       </c>
       <c r="G95" t="n">
-        <v>0.220989076563513</v>
+        <v>0.1293248639884186</v>
       </c>
       <c r="H95" t="n">
-        <v>0.1606385864510344</v>
+        <v>0.1166839180734646</v>
       </c>
       <c r="I95" t="n">
-        <v>0.1892137096177642</v>
+        <v>0.1014278652719019</v>
       </c>
       <c r="J95" t="n">
-        <v>0.4577033973394621</v>
+        <v>0.2732638919111777</v>
       </c>
       <c r="K95" t="n">
-        <v>0.6441798363396094</v>
+        <v>0.5571798999470449</v>
       </c>
       <c r="L95" t="n">
-        <v>1.027214222552206</v>
+        <v>1.487299259037755</v>
       </c>
       <c r="M95" t="n">
-        <v>11523.03341925126</v>
+        <v>6743.386382948113</v>
       </c>
     </row>
     <row r="96">
@@ -54345,31 +54345,31 @@
         <v>81377</v>
       </c>
       <c r="E96" t="n">
-        <v>0.3220405306317367</v>
+        <v>0.07001693051935158</v>
       </c>
       <c r="F96" t="n">
-        <v>0.3885228642238886</v>
+        <v>0.1055137100634783</v>
       </c>
       <c r="G96" t="n">
-        <v>0.3761334570770419</v>
+        <v>0.1943280669847254</v>
       </c>
       <c r="H96" t="n">
-        <v>0.191383086982507</v>
+        <v>0.1823784159880825</v>
       </c>
       <c r="I96" t="n">
-        <v>0.4024446471585403</v>
+        <v>0.1556041999399017</v>
       </c>
       <c r="J96" t="n">
-        <v>0.6096456008714304</v>
+        <v>0.3662941841945669</v>
       </c>
       <c r="K96" t="n">
-        <v>0.7307865808763977</v>
+        <v>1.061311204275075</v>
       </c>
       <c r="L96" t="n">
-        <v>1.125223908310104</v>
+        <v>2.011956054469076</v>
       </c>
       <c r="M96" t="n">
-        <v>30608.61233655844</v>
+        <v>15813.835107016</v>
       </c>
     </row>
     <row r="97">
@@ -54392,31 +54392,31 @@
         <v>43280</v>
       </c>
       <c r="E97" t="n">
-        <v>0.4431505885010694</v>
+        <v>0.01488761388591324</v>
       </c>
       <c r="F97" t="n">
-        <v>0.5212878459707427</v>
+        <v>0.06685098397687736</v>
       </c>
       <c r="G97" t="n">
-        <v>0.4948000492956483</v>
+        <v>0.249481227258554</v>
       </c>
       <c r="H97" t="n">
-        <v>0.1940758709745789</v>
+        <v>0.2430471112284678</v>
       </c>
       <c r="I97" t="n">
-        <v>0.5294514165582145</v>
+        <v>0.1993123051626691</v>
       </c>
       <c r="J97" t="n">
-        <v>0.7155132753049704</v>
+        <v>0.4735962081452328</v>
       </c>
       <c r="K97" t="n">
-        <v>0.7909115643010842</v>
+        <v>1.312600115250575</v>
       </c>
       <c r="L97" t="n">
-        <v>0.8992640360235256</v>
+        <v>2.029819488179555</v>
       </c>
       <c r="M97" t="n">
-        <v>21414.94613351566</v>
+        <v>10797.54751575022</v>
       </c>
     </row>
     <row r="98">
@@ -54439,31 +54439,31 @@
         <v>1688</v>
       </c>
       <c r="E98" t="n">
-        <v>0.3005713603923545</v>
+        <v>-0.02077999586918201</v>
       </c>
       <c r="F98" t="n">
-        <v>0.3426345645119449</v>
+        <v>0.02825206409175175</v>
       </c>
       <c r="G98" t="n">
-        <v>0.4333821236900652</v>
+        <v>0.2220473613228471</v>
       </c>
       <c r="H98" t="n">
-        <v>0.2364659354607818</v>
+        <v>0.2155951597135102</v>
       </c>
       <c r="I98" t="n">
-        <v>0.3995356856263024</v>
+        <v>0.1582962629802644</v>
       </c>
       <c r="J98" t="n">
-        <v>0.7571939556985194</v>
+        <v>0.6031192537559724</v>
       </c>
       <c r="K98" t="n">
-        <v>0.7876892718589474</v>
+        <v>0.9048777201228486</v>
       </c>
       <c r="L98" t="n">
-        <v>1.105844995570992</v>
+        <v>0.9108345014404433</v>
       </c>
       <c r="M98" t="n">
-        <v>731.5490247888301</v>
+        <v>374.8159459129658</v>
       </c>
     </row>
     <row r="99">
@@ -54580,31 +54580,31 @@
         <v>29</v>
       </c>
       <c r="E101" t="n">
-        <v>0.4184770891904542</v>
+        <v>0.4058755224646904</v>
       </c>
       <c r="F101" t="n">
-        <v>0.4115245044231415</v>
+        <v>0.3878373042680323</v>
       </c>
       <c r="G101" t="n">
-        <v>0.4184770891904542</v>
+        <v>0.4058755224646904</v>
       </c>
       <c r="H101" t="n">
-        <v>0.1616831883851327</v>
+        <v>0.161013088925239</v>
       </c>
       <c r="I101" t="n">
-        <v>0.4115245044231415</v>
+        <v>0.3878373042680323</v>
       </c>
       <c r="J101" t="n">
-        <v>0.6391099328175187</v>
+        <v>0.6234696382656693</v>
       </c>
       <c r="K101" t="n">
-        <v>0.7100368010997772</v>
+        <v>0.7113521063327789</v>
       </c>
       <c r="L101" t="n">
-        <v>0.7120126932859421</v>
+        <v>0.7167739719152451</v>
       </c>
       <c r="M101" t="n">
-        <v>12.13583558652317</v>
+        <v>11.77039015147602</v>
       </c>
     </row>
     <row r="102">
@@ -54627,31 +54627,31 @@
         <v>95</v>
       </c>
       <c r="E102" t="n">
-        <v>0.5694655866717527</v>
+        <v>0.5780765526891245</v>
       </c>
       <c r="F102" t="n">
-        <v>0.5591897269478068</v>
+        <v>0.5323843657970428</v>
       </c>
       <c r="G102" t="n">
-        <v>0.5694655866717527</v>
+        <v>0.5780765526891245</v>
       </c>
       <c r="H102" t="n">
-        <v>0.224146793347127</v>
+        <v>0.2570493154817762</v>
       </c>
       <c r="I102" t="n">
-        <v>0.5591897269478068</v>
+        <v>0.5323843657970428</v>
       </c>
       <c r="J102" t="n">
-        <v>0.8626229822635652</v>
+        <v>0.9396874308586121</v>
       </c>
       <c r="K102" t="n">
-        <v>0.9518671518564225</v>
+        <v>1.022042983174324</v>
       </c>
       <c r="L102" t="n">
-        <v>0.9854162931442261</v>
+        <v>1.03106951713562</v>
       </c>
       <c r="M102" t="n">
-        <v>54.09923073381651</v>
+        <v>54.91727250546683</v>
       </c>
     </row>
     <row r="103">
@@ -54674,31 +54674,31 @@
         <v>244</v>
       </c>
       <c r="E103" t="n">
-        <v>0.7376734470816417</v>
+        <v>0.7592622485643035</v>
       </c>
       <c r="F103" t="n">
-        <v>0.8007415682077408</v>
+        <v>0.8520713895559311</v>
       </c>
       <c r="G103" t="n">
-        <v>0.7381155874967082</v>
+        <v>0.759719777237538</v>
       </c>
       <c r="H103" t="n">
-        <v>0.2476442413665085</v>
+        <v>0.2734605028034346</v>
       </c>
       <c r="I103" t="n">
-        <v>0.8007415682077408</v>
+        <v>0.8520713895559311</v>
       </c>
       <c r="J103" t="n">
-        <v>1.03052346110344</v>
+        <v>1.069845786690712</v>
       </c>
       <c r="K103" t="n">
-        <v>1.134226026237011</v>
+        <v>1.141593321859837</v>
       </c>
       <c r="L103" t="n">
-        <v>1.144247531890869</v>
+        <v>1.160690546035767</v>
       </c>
       <c r="M103" t="n">
-        <v>180.1002033491968</v>
+        <v>185.3716256459593</v>
       </c>
     </row>
     <row r="104">
@@ -54721,31 +54721,31 @@
         <v>751</v>
       </c>
       <c r="E104" t="n">
-        <v>0.7421954031238461</v>
+        <v>0.7900210184759129</v>
       </c>
       <c r="F104" t="n">
-        <v>0.7416056394577026</v>
+        <v>0.7743850946426392</v>
       </c>
       <c r="G104" t="n">
-        <v>0.7421954031238461</v>
+        <v>0.7900210184759129</v>
       </c>
       <c r="H104" t="n">
-        <v>0.2862597951875252</v>
+        <v>0.3758544145047704</v>
       </c>
       <c r="I104" t="n">
-        <v>0.7416056394577026</v>
+        <v>0.7743850946426392</v>
       </c>
       <c r="J104" t="n">
-        <v>1.177512288093567</v>
+        <v>1.388970367610455</v>
       </c>
       <c r="K104" t="n">
-        <v>1.273471599677578</v>
+        <v>1.54336878657341</v>
       </c>
       <c r="L104" t="n">
-        <v>1.293378174304962</v>
+        <v>1.575278332573362</v>
       </c>
       <c r="M104" t="n">
-        <v>557.3887477460084</v>
+        <v>593.3057848754106</v>
       </c>
     </row>
     <row r="105">
@@ -54768,31 +54768,31 @@
         <v>2356</v>
       </c>
       <c r="E105" t="n">
-        <v>0.7145257096404993</v>
+        <v>0.9401942359282986</v>
       </c>
       <c r="F105" t="n">
-        <v>0.6892310529947281</v>
+        <v>0.7702516913414001</v>
       </c>
       <c r="G105" t="n">
-        <v>0.7145257096404993</v>
+        <v>0.9401942359282986</v>
       </c>
       <c r="H105" t="n">
-        <v>0.3103191064489859</v>
+        <v>0.5977679646149462</v>
       </c>
       <c r="I105" t="n">
-        <v>0.6892310529947281</v>
+        <v>0.7702516913414001</v>
       </c>
       <c r="J105" t="n">
-        <v>1.184043280780315</v>
+        <v>1.757941682823002</v>
       </c>
       <c r="K105" t="n">
-        <v>1.262261253595352</v>
+        <v>1.842850989103317</v>
       </c>
       <c r="L105" t="n">
-        <v>1.269817998749204</v>
+        <v>1.877601742744446</v>
       </c>
       <c r="M105" t="n">
-        <v>1683.422571913016</v>
+        <v>2215.097619847072</v>
       </c>
     </row>
     <row r="106">
@@ -54815,31 +54815,31 @@
         <v>1369</v>
       </c>
       <c r="E106" t="n">
-        <v>0.9167574562897349</v>
+        <v>1.664659521348095</v>
       </c>
       <c r="F106" t="n">
-        <v>0.8759693503379822</v>
+        <v>1.842497456818819</v>
       </c>
       <c r="G106" t="n">
-        <v>0.9167574562897349</v>
+        <v>1.664659521348095</v>
       </c>
       <c r="H106" t="n">
-        <v>0.2278754771299379</v>
+        <v>0.5661165440359924</v>
       </c>
       <c r="I106" t="n">
-        <v>0.8759693503379822</v>
+        <v>1.842497456818819</v>
       </c>
       <c r="J106" t="n">
-        <v>1.182051580026746</v>
+        <v>2.146015110611916</v>
       </c>
       <c r="K106" t="n">
-        <v>1.231388664394617</v>
+        <v>2.217600666284561</v>
       </c>
       <c r="L106" t="n">
-        <v>1.248100463300943</v>
+        <v>2.224749810993671</v>
       </c>
       <c r="M106" t="n">
-        <v>1255.040957660647</v>
+        <v>2278.918884725543</v>
       </c>
     </row>
     <row r="107">
@@ -55003,31 +55003,31 @@
         <v>3467</v>
       </c>
       <c r="E110" t="n">
-        <v>-0.006662772779367325</v>
+        <v>-0.004500232269060629</v>
       </c>
       <c r="F110" t="n">
-        <v>0.001505990199558476</v>
+        <v>0.0005691417729825688</v>
       </c>
       <c r="G110" t="n">
-        <v>0.0975022249874006</v>
+        <v>0.06295902312842767</v>
       </c>
       <c r="H110" t="n">
-        <v>0.117848706260372</v>
+        <v>0.06703846155293255</v>
       </c>
       <c r="I110" t="n">
-        <v>0.05640784342711742</v>
+        <v>0.03986104559946674</v>
       </c>
       <c r="J110" t="n">
-        <v>0.2385196607292716</v>
+        <v>0.1502506213468423</v>
       </c>
       <c r="K110" t="n">
-        <v>0.5404575133334373</v>
+        <v>0.3077014600946332</v>
       </c>
       <c r="L110" t="n">
-        <v>1.29145465115188</v>
+        <v>0.4729126947189212</v>
       </c>
       <c r="M110" t="n">
-        <v>338.0402140313179</v>
+        <v>218.2789331862588</v>
       </c>
     </row>
     <row r="111">
@@ -55050,31 +55050,31 @@
         <v>13594</v>
       </c>
       <c r="E111" t="n">
-        <v>0.00661326345912594</v>
+        <v>-0.001065142486479066</v>
       </c>
       <c r="F111" t="n">
-        <v>0.01008457742072135</v>
+        <v>0.004806092936534063</v>
       </c>
       <c r="G111" t="n">
-        <v>0.1121246710817423</v>
+        <v>0.07766796950723365</v>
       </c>
       <c r="H111" t="n">
-        <v>0.1208479000141863</v>
+        <v>0.07824526471493286</v>
       </c>
       <c r="I111" t="n">
-        <v>0.07402250461321352</v>
+        <v>0.05420940432566353</v>
       </c>
       <c r="J111" t="n">
-        <v>0.2499433647947639</v>
+        <v>0.1743984680074129</v>
       </c>
       <c r="K111" t="n">
-        <v>0.5546257518889518</v>
+        <v>0.3758670042845898</v>
       </c>
       <c r="L111" t="n">
-        <v>1.200053153926703</v>
+        <v>0.8549413635485907</v>
       </c>
       <c r="M111" t="n">
-        <v>1524.222778685205</v>
+        <v>1055.818377481334</v>
       </c>
     </row>
     <row r="112">
@@ -55097,31 +55097,31 @@
         <v>20261</v>
       </c>
       <c r="E112" t="n">
-        <v>0.04232601353245824</v>
+        <v>0.003104245666529817</v>
       </c>
       <c r="F112" t="n">
-        <v>0.03824007100160318</v>
+        <v>0.01363590543096137</v>
       </c>
       <c r="G112" t="n">
-        <v>0.1427214305190253</v>
+        <v>0.1031978463785773</v>
       </c>
       <c r="H112" t="n">
-        <v>0.1275788638513963</v>
+        <v>0.09364837026239449</v>
       </c>
       <c r="I112" t="n">
-        <v>0.1086791769652899</v>
+        <v>0.07940894988539425</v>
       </c>
       <c r="J112" t="n">
-        <v>0.3107955883037729</v>
+        <v>0.2157534296867794</v>
       </c>
       <c r="K112" t="n">
-        <v>0.5622846688644247</v>
+        <v>0.4429257589519652</v>
       </c>
       <c r="L112" t="n">
-        <v>1.336677749477113</v>
+        <v>1.141859323445582</v>
       </c>
       <c r="M112" t="n">
-        <v>2891.678903745972</v>
+        <v>2090.891565476355</v>
       </c>
     </row>
     <row r="113">
@@ -55144,31 +55144,31 @@
         <v>37190</v>
       </c>
       <c r="E113" t="n">
-        <v>0.1275423488523213</v>
+        <v>0.005719449253423801</v>
       </c>
       <c r="F113" t="n">
-        <v>0.1305925901976041</v>
+        <v>0.02226663731886147</v>
       </c>
       <c r="G113" t="n">
-        <v>0.2047043941133477</v>
+        <v>0.1389935598409908</v>
       </c>
       <c r="H113" t="n">
-        <v>0.1564879305661438</v>
+        <v>0.1201345330561581</v>
       </c>
       <c r="I113" t="n">
-        <v>0.1760786903534235</v>
+        <v>0.1133753477844253</v>
       </c>
       <c r="J113" t="n">
-        <v>0.4275797498401424</v>
+        <v>0.2829256772862057</v>
       </c>
       <c r="K113" t="n">
-        <v>0.6475291464807028</v>
+        <v>0.5536302398195715</v>
       </c>
       <c r="L113" t="n">
-        <v>1.514614333000409</v>
+        <v>1.344332502412986</v>
       </c>
       <c r="M113" t="n">
-        <v>7612.956417075402</v>
+        <v>5169.170490486446</v>
       </c>
     </row>
     <row r="114">
@@ -55191,31 +55191,31 @@
         <v>61874</v>
       </c>
       <c r="E114" t="n">
-        <v>0.2861267276702482</v>
+        <v>-0.0392082110986495</v>
       </c>
       <c r="F114" t="n">
-        <v>0.3131842176358106</v>
+        <v>-0.0146464873534686</v>
       </c>
       <c r="G114" t="n">
-        <v>0.3380741282784048</v>
+        <v>0.2101757723962866</v>
       </c>
       <c r="H114" t="n">
-        <v>0.2010470171323569</v>
+        <v>0.1926967127795003</v>
       </c>
       <c r="I114" t="n">
-        <v>0.3337549869484001</v>
+        <v>0.1660523240214327</v>
       </c>
       <c r="J114" t="n">
-        <v>0.6041299351108964</v>
+        <v>0.4339748592501181</v>
       </c>
       <c r="K114" t="n">
-        <v>0.7703452686405979</v>
+        <v>0.9952793883359845</v>
       </c>
       <c r="L114" t="n">
-        <v>0.8549024065858456</v>
+        <v>1.691679654045027</v>
       </c>
       <c r="M114" t="n">
-        <v>20917.99861309802</v>
+        <v>13004.41574124783</v>
       </c>
     </row>
     <row r="115">
@@ -55238,31 +55238,31 @@
         <v>30203</v>
       </c>
       <c r="E115" t="n">
-        <v>0.4023599296900517</v>
+        <v>-0.1713471903487895</v>
       </c>
       <c r="F115" t="n">
-        <v>0.4548088254808603</v>
+        <v>-0.08802415646167996</v>
       </c>
       <c r="G115" t="n">
-        <v>0.4484562330960665</v>
+        <v>0.3732575414248737</v>
       </c>
       <c r="H115" t="n">
-        <v>0.2209594354027491</v>
+        <v>0.3213479769964795</v>
       </c>
       <c r="I115" t="n">
-        <v>0.4655716707287004</v>
+        <v>0.2956607502244317</v>
       </c>
       <c r="J115" t="n">
-        <v>0.7374016879624973</v>
+        <v>0.8106507516153896</v>
       </c>
       <c r="K115" t="n">
-        <v>0.8227698606764953</v>
+        <v>1.521897664012015</v>
       </c>
       <c r="L115" t="n">
-        <v>1.245447162253324</v>
+        <v>1.807414186031119</v>
       </c>
       <c r="M115" t="n">
-        <v>13544.7236082005</v>
+        <v>11273.49752365546</v>
       </c>
     </row>
     <row r="116">
@@ -55285,31 +55285,31 @@
         <v>2828</v>
       </c>
       <c r="E116" t="n">
-        <v>-0.1916189025878572</v>
+        <v>-0.8921968504738728</v>
       </c>
       <c r="F116" t="n">
-        <v>-0.1253445501504644</v>
+        <v>-0.9140853686124397</v>
       </c>
       <c r="G116" t="n">
-        <v>0.3695355917493841</v>
+        <v>0.9330569310191442</v>
       </c>
       <c r="H116" t="n">
-        <v>0.4341233068049625</v>
+        <v>0.4565644445096451</v>
       </c>
       <c r="I116" t="n">
-        <v>0.1885388303861127</v>
+        <v>0.9140853686124397</v>
       </c>
       <c r="J116" t="n">
-        <v>0.9265435907983579</v>
+        <v>1.604794904530725</v>
       </c>
       <c r="K116" t="n">
-        <v>1.998603754713397</v>
+        <v>1.923347138561426</v>
       </c>
       <c r="L116" t="n">
-        <v>2.499162222240659</v>
+        <v>1.996368164816265</v>
       </c>
       <c r="M116" t="n">
-        <v>1045.046653467258</v>
+        <v>2638.68500092214</v>
       </c>
     </row>
     <row r="117">
@@ -55426,31 +55426,31 @@
         <v>143</v>
       </c>
       <c r="E119" t="n">
-        <v>0.04700272066609843</v>
+        <v>0.03702020811867881</v>
       </c>
       <c r="F119" t="n">
-        <v>0.05089312791824341</v>
+        <v>0.03600767254829407</v>
       </c>
       <c r="G119" t="n">
-        <v>0.05789384308394852</v>
+        <v>0.04775689490191586</v>
       </c>
       <c r="H119" t="n">
-        <v>0.03956099484000287</v>
+        <v>0.03993540557358555</v>
       </c>
       <c r="I119" t="n">
-        <v>0.05250644683837891</v>
+        <v>0.03830230236053467</v>
       </c>
       <c r="J119" t="n">
-        <v>0.08575838804244995</v>
+        <v>0.08008747100830078</v>
       </c>
       <c r="K119" t="n">
-        <v>0.2416941118240361</v>
+        <v>0.2357203984260565</v>
       </c>
       <c r="L119" t="n">
-        <v>0.2607690989971161</v>
+        <v>0.259772926568985</v>
       </c>
       <c r="M119" t="n">
-        <v>8.278819561004639</v>
+        <v>6.829235970973969</v>
       </c>
     </row>
     <row r="120">
@@ -55473,31 +55473,31 @@
         <v>514</v>
       </c>
       <c r="E120" t="n">
-        <v>0.04997441329148957</v>
+        <v>0.04351744884878745</v>
       </c>
       <c r="F120" t="n">
-        <v>0.05791467428207397</v>
+        <v>0.04132413864135742</v>
       </c>
       <c r="G120" t="n">
-        <v>0.07798247120491726</v>
+        <v>0.06953691131641893</v>
       </c>
       <c r="H120" t="n">
-        <v>0.0616390863342464</v>
+        <v>0.0629125249464348</v>
       </c>
       <c r="I120" t="n">
-        <v>0.06821812689304352</v>
+        <v>0.05329215526580811</v>
       </c>
       <c r="J120" t="n">
-        <v>0.1259757727384567</v>
+        <v>0.1249713957309723</v>
       </c>
       <c r="K120" t="n">
-        <v>0.3490932720899582</v>
+        <v>0.3528478538990021</v>
       </c>
       <c r="L120" t="n">
-        <v>0.4178086817264557</v>
+        <v>0.4139778316020966</v>
       </c>
       <c r="M120" t="n">
-        <v>40.08299019932747</v>
+        <v>35.74197241663933</v>
       </c>
     </row>
     <row r="121">
@@ -55520,31 +55520,31 @@
         <v>514</v>
       </c>
       <c r="E121" t="n">
-        <v>0.1022584130443951</v>
+        <v>0.08963499574809687</v>
       </c>
       <c r="F121" t="n">
-        <v>0.08324450254440308</v>
+        <v>0.07085868716239929</v>
       </c>
       <c r="G121" t="n">
-        <v>0.1113519042962256</v>
+        <v>0.09875336069077369</v>
       </c>
       <c r="H121" t="n">
-        <v>0.1005701529023599</v>
+        <v>0.09828521939690832</v>
       </c>
       <c r="I121" t="n">
-        <v>0.08431278169155121</v>
+        <v>0.07365554571151733</v>
       </c>
       <c r="J121" t="n">
-        <v>0.2402629882097244</v>
+        <v>0.2200685083866119</v>
       </c>
       <c r="K121" t="n">
-        <v>0.4589816689491272</v>
+        <v>0.4524811607599258</v>
       </c>
       <c r="L121" t="n">
-        <v>0.4806454181671143</v>
+        <v>0.4984588623046875</v>
       </c>
       <c r="M121" t="n">
-        <v>57.23487880825996</v>
+        <v>50.75922739505768</v>
       </c>
     </row>
     <row r="122">
@@ -55567,31 +55567,31 @@
         <v>801</v>
       </c>
       <c r="E122" t="n">
-        <v>0.2211641258142712</v>
+        <v>0.1816395592228155</v>
       </c>
       <c r="F122" t="n">
-        <v>0.1879702508449554</v>
+        <v>0.1488087475299835</v>
       </c>
       <c r="G122" t="n">
-        <v>0.2211914134308342</v>
+        <v>0.1816625937019543</v>
       </c>
       <c r="H122" t="n">
-        <v>0.1360451423448458</v>
+        <v>0.1101741581656829</v>
       </c>
       <c r="I122" t="n">
-        <v>0.1879702508449554</v>
+        <v>0.1488087475299835</v>
       </c>
       <c r="J122" t="n">
-        <v>0.4445316791534424</v>
+        <v>0.3554821014404297</v>
       </c>
       <c r="K122" t="n">
-        <v>0.4801727533340454</v>
+        <v>0.439931720495224</v>
       </c>
       <c r="L122" t="n">
-        <v>0.4874159395694733</v>
+        <v>0.4998721778392792</v>
       </c>
       <c r="M122" t="n">
-        <v>177.1743221580982</v>
+        <v>145.5117375552654</v>
       </c>
     </row>
     <row r="123">
@@ -55614,31 +55614,31 @@
         <v>1253</v>
       </c>
       <c r="E123" t="n">
-        <v>0.351168925797378</v>
+        <v>0.2647646491468571</v>
       </c>
       <c r="F123" t="n">
-        <v>0.3409375250339508</v>
+        <v>0.2040360569953918</v>
       </c>
       <c r="G123" t="n">
-        <v>0.351168925797378</v>
+        <v>0.2647646491468571</v>
       </c>
       <c r="H123" t="n">
-        <v>0.1519134035887393</v>
+        <v>0.1493667922287115</v>
       </c>
       <c r="I123" t="n">
-        <v>0.3409375250339508</v>
+        <v>0.2040360569953918</v>
       </c>
       <c r="J123" t="n">
-        <v>0.5661464154720306</v>
+        <v>0.5065653920173645</v>
       </c>
       <c r="K123" t="n">
-        <v>0.6162296712398529</v>
+        <v>0.7069355440139771</v>
       </c>
       <c r="L123" t="n">
-        <v>0.6203942894935608</v>
+        <v>0.74079430103302</v>
       </c>
       <c r="M123" t="n">
-        <v>440.0146640241146</v>
+        <v>331.750105381012</v>
       </c>
     </row>
     <row r="124">
@@ -55661,31 +55661,31 @@
         <v>414</v>
       </c>
       <c r="E124" t="n">
-        <v>0.4985453436772029</v>
+        <v>0.4296672815717937</v>
       </c>
       <c r="F124" t="n">
-        <v>0.4799178242683411</v>
+        <v>0.1932721585035324</v>
       </c>
       <c r="G124" t="n">
-        <v>0.4985453436772029</v>
+        <v>0.4296672815717937</v>
       </c>
       <c r="H124" t="n">
-        <v>0.07218260743256062</v>
+        <v>0.2945645142524089</v>
       </c>
       <c r="I124" t="n">
-        <v>0.4799178242683411</v>
+        <v>0.1932721585035324</v>
       </c>
       <c r="J124" t="n">
-        <v>0.5998641699552536</v>
+        <v>0.8322093605995178</v>
       </c>
       <c r="K124" t="n">
-        <v>0.6124465444684029</v>
+        <v>0.876291538476944</v>
       </c>
       <c r="L124" t="n">
-        <v>0.6138144433498383</v>
+        <v>0.8981576561927795</v>
       </c>
       <c r="M124" t="n">
-        <v>206.397772282362</v>
+        <v>177.8822545707226</v>
       </c>
     </row>
     <row r="125">
@@ -55849,31 +55849,31 @@
         <v>3770</v>
       </c>
       <c r="E128" t="n">
-        <v>-0.02723928588468973</v>
+        <v>-0.006625412356773551</v>
       </c>
       <c r="F128" t="n">
-        <v>0.006601346305060001</v>
+        <v>0.002044252193617977</v>
       </c>
       <c r="G128" t="n">
-        <v>0.1614455119074896</v>
+        <v>0.07542385344884535</v>
       </c>
       <c r="H128" t="n">
-        <v>0.2430017940366859</v>
+        <v>0.1004053980909719</v>
       </c>
       <c r="I128" t="n">
-        <v>0.08983779302324327</v>
+        <v>0.03970239718627477</v>
       </c>
       <c r="J128" t="n">
-        <v>0.3703391612007887</v>
+        <v>0.1917547559496254</v>
       </c>
       <c r="K128" t="n">
-        <v>1.077596898686818</v>
+        <v>0.485561472251068</v>
       </c>
       <c r="L128" t="n">
-        <v>4.42384913837086</v>
+        <v>0.9424822995202957</v>
       </c>
       <c r="M128" t="n">
-        <v>608.6495798912359</v>
+        <v>284.3479275021469</v>
       </c>
     </row>
     <row r="129">
@@ -55896,31 +55896,31 @@
         <v>15363</v>
       </c>
       <c r="E129" t="n">
-        <v>-0.009336097058762144</v>
+        <v>-0.0111301815216072</v>
       </c>
       <c r="F129" t="n">
-        <v>0.006338558556213771</v>
+        <v>0.004439262809453971</v>
       </c>
       <c r="G129" t="n">
-        <v>0.1664302194871233</v>
+        <v>0.08836842764303711</v>
       </c>
       <c r="H129" t="n">
-        <v>0.1900146658059537</v>
+        <v>0.108913159735599</v>
       </c>
       <c r="I129" t="n">
-        <v>0.1075664870853621</v>
+        <v>0.05364207109094928</v>
       </c>
       <c r="J129" t="n">
-        <v>0.3779514330720973</v>
+        <v>0.2035166764503533</v>
       </c>
       <c r="K129" t="n">
-        <v>0.9309111636596323</v>
+        <v>0.5494066735958129</v>
       </c>
       <c r="L129" t="n">
-        <v>2.748985558322753</v>
+        <v>1.022741302130076</v>
       </c>
       <c r="M129" t="n">
-        <v>2556.867461980675</v>
+        <v>1357.604153879979</v>
       </c>
     </row>
     <row r="130">
@@ -55943,31 +55943,31 @@
         <v>25243</v>
       </c>
       <c r="E130" t="n">
-        <v>0.08783673738151877</v>
+        <v>-0.02920978151343278</v>
       </c>
       <c r="F130" t="n">
-        <v>0.0859423257749818</v>
+        <v>0.0008708761408056682</v>
       </c>
       <c r="G130" t="n">
-        <v>0.196071552898076</v>
+        <v>0.1247434577291196</v>
       </c>
       <c r="H130" t="n">
-        <v>0.1676649553581025</v>
+        <v>0.1519180566944415</v>
       </c>
       <c r="I130" t="n">
-        <v>0.1498940640702668</v>
+        <v>0.08424142083082481</v>
       </c>
       <c r="J130" t="n">
-        <v>0.4320328080206274</v>
+        <v>0.2580672172991975</v>
       </c>
       <c r="K130" t="n">
-        <v>0.6868534831923947</v>
+        <v>0.7985506570757075</v>
       </c>
       <c r="L130" t="n">
-        <v>1.547533550881417</v>
+        <v>2.115217256678847</v>
       </c>
       <c r="M130" t="n">
-        <v>4949.434209806133</v>
+        <v>3148.899103456166</v>
       </c>
     </row>
     <row r="131">
@@ -55990,31 +55990,31 @@
         <v>49627</v>
       </c>
       <c r="E131" t="n">
-        <v>0.2509142788549135</v>
+        <v>-0.06637882272360229</v>
       </c>
       <c r="F131" t="n">
-        <v>0.2741651572196789</v>
+        <v>-0.01426248844152865</v>
       </c>
       <c r="G131" t="n">
-        <v>0.3092819045043315</v>
+        <v>0.1836148357591072</v>
       </c>
       <c r="H131" t="n">
-        <v>0.2031315512780125</v>
+        <v>0.2291897023559143</v>
       </c>
       <c r="I131" t="n">
-        <v>0.2944790692181004</v>
+        <v>0.1179071537275869</v>
       </c>
       <c r="J131" t="n">
-        <v>0.5804397150883015</v>
+        <v>0.3853620004640674</v>
       </c>
       <c r="K131" t="n">
-        <v>0.7614215944101845</v>
+        <v>1.18817212752447</v>
       </c>
       <c r="L131" t="n">
-        <v>1.933813314211456</v>
+        <v>2.647754350355521</v>
       </c>
       <c r="M131" t="n">
-        <v>15348.73307483646</v>
+        <v>9112.253454217214</v>
       </c>
     </row>
     <row r="132">
@@ -56037,31 +56037,31 @@
         <v>76585</v>
       </c>
       <c r="E132" t="n">
-        <v>0.4521715176533685</v>
+        <v>-0.128108402298924</v>
       </c>
       <c r="F132" t="n">
-        <v>0.5275446847677258</v>
+        <v>-0.02483307582616794</v>
       </c>
       <c r="G132" t="n">
-        <v>0.4817774736862024</v>
+        <v>0.292245733733514</v>
       </c>
       <c r="H132" t="n">
-        <v>0.228690876725433</v>
+        <v>0.3507216375176176</v>
       </c>
       <c r="I132" t="n">
-        <v>0.5296615673341697</v>
+        <v>0.1935340065616792</v>
       </c>
       <c r="J132" t="n">
-        <v>0.7538115406812145</v>
+        <v>0.6240618754467711</v>
       </c>
       <c r="K132" t="n">
-        <v>0.8253520404030659</v>
+        <v>1.952818041389196</v>
       </c>
       <c r="L132" t="n">
-        <v>1.47372570049522</v>
+        <v>2.821261619900875</v>
       </c>
       <c r="M132" t="n">
-        <v>36896.92782225781</v>
+        <v>22381.63951798117</v>
       </c>
     </row>
     <row r="133">
@@ -56084,31 +56084,31 @@
         <v>36672</v>
       </c>
       <c r="E133" t="n">
-        <v>0.5958482008402682</v>
+        <v>-0.1563955368748131</v>
       </c>
       <c r="F133" t="n">
-        <v>0.6953042399167189</v>
+        <v>-0.02047288259910649</v>
       </c>
       <c r="G133" t="n">
-        <v>0.6129837328801898</v>
+        <v>0.3594174623830941</v>
       </c>
       <c r="H133" t="n">
-        <v>0.2242909449861296</v>
+        <v>0.4172088225780553</v>
       </c>
       <c r="I133" t="n">
-        <v>0.6953607077155757</v>
+        <v>0.2395142767449738</v>
       </c>
       <c r="J133" t="n">
-        <v>0.8247004829604609</v>
+        <v>0.8162912511917433</v>
       </c>
       <c r="K133" t="n">
-        <v>0.8625903892249369</v>
+        <v>2.147080021591482</v>
       </c>
       <c r="L133" t="n">
-        <v>1.226194786413487</v>
+        <v>4.054564235607326</v>
       </c>
       <c r="M133" t="n">
-        <v>22479.33945218232</v>
+        <v>13180.55718051283</v>
       </c>
     </row>
     <row r="134">
@@ -56131,31 +56131,31 @@
         <v>4424</v>
       </c>
       <c r="E134" t="n">
-        <v>0.6323528904060859</v>
+        <v>-0.2738376911276541</v>
       </c>
       <c r="F134" t="n">
-        <v>0.6795843970869201</v>
+        <v>-0.1840314940741599</v>
       </c>
       <c r="G134" t="n">
-        <v>0.6323528904060859</v>
+        <v>0.392725007847736</v>
       </c>
       <c r="H134" t="n">
-        <v>0.1775463715953378</v>
+        <v>0.3638044280157016</v>
       </c>
       <c r="I134" t="n">
-        <v>0.6795843970869201</v>
+        <v>0.2741649803535758</v>
       </c>
       <c r="J134" t="n">
-        <v>0.8225737701579277</v>
+        <v>0.7584973455567594</v>
       </c>
       <c r="K134" t="n">
-        <v>0.8654471643301954</v>
+        <v>1.842236275908451</v>
       </c>
       <c r="L134" t="n">
-        <v>0.871170587496222</v>
+        <v>1.881016952025075</v>
       </c>
       <c r="M134" t="n">
-        <v>2797.529187156524</v>
+        <v>1737.415434718384</v>
       </c>
     </row>
     <row r="135">
@@ -56178,31 +56178,31 @@
         <v>1219</v>
       </c>
       <c r="E135" t="n">
-        <v>0.1775242950900173</v>
+        <v>-0.6876332938796217</v>
       </c>
       <c r="F135" t="n">
-        <v>0.1715645830747091</v>
+        <v>-0.7638315627845483</v>
       </c>
       <c r="G135" t="n">
-        <v>0.3643340806285263</v>
+        <v>0.7040462698498585</v>
       </c>
       <c r="H135" t="n">
-        <v>0.2311505340426657</v>
+        <v>0.5373601520605062</v>
       </c>
       <c r="I135" t="n">
-        <v>0.4119631467980954</v>
+        <v>0.7638315627845483</v>
       </c>
       <c r="J135" t="n">
-        <v>0.6420160651010209</v>
+        <v>1.429412697140854</v>
       </c>
       <c r="K135" t="n">
-        <v>0.7462641093874736</v>
+        <v>1.509048754198949</v>
       </c>
       <c r="L135" t="n">
-        <v>0.8200721130480035</v>
+        <v>1.519521372969873</v>
       </c>
       <c r="M135" t="n">
-        <v>444.1232442861735</v>
+        <v>858.2324029469776</v>
       </c>
     </row>
     <row r="136">
@@ -56225,31 +56225,31 @@
         <v>8</v>
       </c>
       <c r="E136" t="n">
-        <v>-0.1961008730278013</v>
+        <v>-1.483230591642633</v>
       </c>
       <c r="F136" t="n">
-        <v>-0.190789707624742</v>
+        <v>-1.482952797138974</v>
       </c>
       <c r="G136" t="n">
-        <v>0.1961008730278013</v>
+        <v>1.483230591642633</v>
       </c>
       <c r="H136" t="n">
-        <v>0.01384772988916478</v>
+        <v>0.001937344379035381</v>
       </c>
       <c r="I136" t="n">
-        <v>0.190789707624742</v>
+        <v>1.482952797138974</v>
       </c>
       <c r="J136" t="n">
-        <v>0.2143760769426374</v>
+        <v>1.484974284549758</v>
       </c>
       <c r="K136" t="n">
-        <v>0.221724876685475</v>
+        <v>1.487430555325081</v>
       </c>
       <c r="L136" t="n">
-        <v>0.2225414099902347</v>
+        <v>1.487703474300117</v>
       </c>
       <c r="M136" t="n">
-        <v>1.56880698422241</v>
+        <v>11.86584473314106</v>
       </c>
     </row>
     <row r="137">
@@ -56272,31 +56272,31 @@
         <v>557</v>
       </c>
       <c r="E137" t="n">
-        <v>0.0521660238016176</v>
+        <v>0.0449046866409815</v>
       </c>
       <c r="F137" t="n">
-        <v>0.04674222320318222</v>
+        <v>0.02546415477991104</v>
       </c>
       <c r="G137" t="n">
-        <v>0.06125638526621905</v>
+        <v>0.05387834103400125</v>
       </c>
       <c r="H137" t="n">
-        <v>0.05036166912706088</v>
+        <v>0.07025485084448536</v>
       </c>
       <c r="I137" t="n">
-        <v>0.05000686645507812</v>
+        <v>0.0333259105682373</v>
       </c>
       <c r="J137" t="n">
-        <v>0.1362911581993105</v>
+        <v>0.1293965458869935</v>
       </c>
       <c r="K137" t="n">
-        <v>0.1972411848604679</v>
+        <v>0.3717811584472654</v>
       </c>
       <c r="L137" t="n">
-        <v>0.2773351669311523</v>
+        <v>0.5038418173789978</v>
       </c>
       <c r="M137" t="n">
-        <v>34.11980659328401</v>
+        <v>30.0102359559387</v>
       </c>
     </row>
     <row r="138">
@@ -56319,31 +56319,31 @@
         <v>2106</v>
       </c>
       <c r="E138" t="n">
-        <v>0.06992665367644962</v>
+        <v>0.06693451559385116</v>
       </c>
       <c r="F138" t="n">
-        <v>0.05895459651947021</v>
+        <v>0.04318489134311676</v>
       </c>
       <c r="G138" t="n">
-        <v>0.08313864115749442</v>
+        <v>0.08238212297982753</v>
       </c>
       <c r="H138" t="n">
-        <v>0.06658511458205665</v>
+        <v>0.1139885730417757</v>
       </c>
       <c r="I138" t="n">
-        <v>0.06538677215576172</v>
+        <v>0.04981072619557381</v>
       </c>
       <c r="J138" t="n">
-        <v>0.1669373158365488</v>
+        <v>0.1763627231121063</v>
       </c>
       <c r="K138" t="n">
-        <v>0.2892262995243069</v>
+        <v>0.5803444325923903</v>
       </c>
       <c r="L138" t="n">
-        <v>0.5099031627178192</v>
+        <v>1.183417618274689</v>
       </c>
       <c r="M138" t="n">
-        <v>175.0899782776833</v>
+        <v>173.4967509955168</v>
       </c>
     </row>
     <row r="139">
@@ -56366,31 +56366,31 @@
         <v>3061</v>
       </c>
       <c r="E139" t="n">
-        <v>0.1076739321577514</v>
+        <v>0.1328768046053747</v>
       </c>
       <c r="F139" t="n">
-        <v>0.09629695862531662</v>
+        <v>0.06126153841614723</v>
       </c>
       <c r="G139" t="n">
-        <v>0.1252028933150906</v>
+        <v>0.1513749539939768</v>
       </c>
       <c r="H139" t="n">
-        <v>0.09491131451211469</v>
+        <v>0.2030471758319158</v>
       </c>
       <c r="I139" t="n">
-        <v>0.1030774712562561</v>
+        <v>0.07059923745691776</v>
       </c>
       <c r="J139" t="n">
-        <v>0.252304881811142</v>
+        <v>0.440805584192276</v>
       </c>
       <c r="K139" t="n">
-        <v>0.4100101888179782</v>
+        <v>0.9550666987895972</v>
       </c>
       <c r="L139" t="n">
-        <v>0.556124359369278</v>
+        <v>1.278088748455048</v>
       </c>
       <c r="M139" t="n">
-        <v>383.2460564374924</v>
+        <v>463.3587341755629</v>
       </c>
     </row>
     <row r="140">
@@ -56413,31 +56413,31 @@
         <v>5117</v>
       </c>
       <c r="E140" t="n">
-        <v>0.215821510541202</v>
+        <v>0.3103596156676702</v>
       </c>
       <c r="F140" t="n">
-        <v>0.2006195783615112</v>
+        <v>0.1453557312488556</v>
       </c>
       <c r="G140" t="n">
-        <v>0.2279560822696484</v>
+        <v>0.3221558011432708</v>
       </c>
       <c r="H140" t="n">
-        <v>0.1754583835494588</v>
+        <v>0.3467555513319469</v>
       </c>
       <c r="I140" t="n">
-        <v>0.2006195783615112</v>
+        <v>0.1456493437290192</v>
       </c>
       <c r="J140" t="n">
-        <v>0.4430889546871186</v>
+        <v>0.8462134361267092</v>
       </c>
       <c r="K140" t="n">
-        <v>0.6916048431396489</v>
+        <v>1.295702321529388</v>
       </c>
       <c r="L140" t="n">
-        <v>2.066849753260612</v>
+        <v>2.754157587885857</v>
       </c>
       <c r="M140" t="n">
-        <v>1166.451272973791</v>
+        <v>1648.471234450117</v>
       </c>
     </row>
     <row r="141">
@@ -56460,31 +56460,31 @@
         <v>8035</v>
       </c>
       <c r="E141" t="n">
-        <v>0.4134217762140825</v>
+        <v>0.7612639018569163</v>
       </c>
       <c r="F141" t="n">
-        <v>0.3611347675323486</v>
+        <v>0.7212923169136047</v>
       </c>
       <c r="G141" t="n">
-        <v>0.4134795800790274</v>
+        <v>0.7612639018569163</v>
       </c>
       <c r="H141" t="n">
-        <v>0.3191634153021059</v>
+        <v>0.5515966495840382</v>
       </c>
       <c r="I141" t="n">
-        <v>0.3611347675323486</v>
+        <v>0.7212923169136047</v>
       </c>
       <c r="J141" t="n">
-        <v>0.6798522979021073</v>
+        <v>1.442188662290573</v>
       </c>
       <c r="K141" t="n">
-        <v>1.743480100333691</v>
+        <v>2.585467149615287</v>
       </c>
       <c r="L141" t="n">
-        <v>2.108025431632996</v>
+        <v>2.984641060233116</v>
       </c>
       <c r="M141" t="n">
-        <v>3322.308425934985</v>
+        <v>6116.755451420322</v>
       </c>
     </row>
     <row r="142">
@@ -56507,31 +56507,31 @@
         <v>3221</v>
       </c>
       <c r="E142" t="n">
-        <v>0.4769454507520945</v>
+        <v>0.9894953353509182</v>
       </c>
       <c r="F142" t="n">
-        <v>0.433051586151123</v>
+        <v>0.9908875823020935</v>
       </c>
       <c r="G142" t="n">
-        <v>0.4774073283102748</v>
+        <v>0.9894953353509182</v>
       </c>
       <c r="H142" t="n">
-        <v>0.2668608512018169</v>
+        <v>0.5686375093260949</v>
       </c>
       <c r="I142" t="n">
-        <v>0.433051586151123</v>
+        <v>0.9908875823020935</v>
       </c>
       <c r="J142" t="n">
-        <v>0.7717067450284958</v>
+        <v>1.495177984237671</v>
       </c>
       <c r="K142" t="n">
-        <v>1.460569521784784</v>
+        <v>2.793407759070397</v>
       </c>
       <c r="L142" t="n">
-        <v>1.910151705145836</v>
+        <v>2.987923845648766</v>
       </c>
       <c r="M142" t="n">
-        <v>1537.729004487395</v>
+        <v>3187.164475165308</v>
       </c>
     </row>
     <row r="143">
@@ -56695,31 +56695,31 @@
         <v>4816</v>
       </c>
       <c r="E146" t="n">
-        <v>-0.02001355679579596</v>
+        <v>-0.006884249525913547</v>
       </c>
       <c r="F146" t="n">
-        <v>-0.001303003418055756</v>
+        <v>-0.0009056881460499805</v>
       </c>
       <c r="G146" t="n">
-        <v>0.1011912016205792</v>
+        <v>0.04781110851011351</v>
       </c>
       <c r="H146" t="n">
-        <v>0.1736056737126063</v>
+        <v>0.06067099121956385</v>
       </c>
       <c r="I146" t="n">
-        <v>0.04906340213672419</v>
+        <v>0.02813181387492294</v>
       </c>
       <c r="J146" t="n">
-        <v>0.2574238840839931</v>
+        <v>0.1127464323843717</v>
       </c>
       <c r="K146" t="n">
-        <v>0.7375697525958146</v>
+        <v>0.26340204800954</v>
       </c>
       <c r="L146" t="n">
-        <v>4.239168618724774</v>
+        <v>0.73548683953516</v>
       </c>
       <c r="M146" t="n">
-        <v>487.3368270047093</v>
+        <v>230.2582985847067</v>
       </c>
     </row>
     <row r="147">
@@ -56742,31 +56742,31 @@
         <v>18094</v>
       </c>
       <c r="E147" t="n">
-        <v>-0.002835480956699819</v>
+        <v>0.001617298823018782</v>
       </c>
       <c r="F147" t="n">
-        <v>0.004279068062877844</v>
+        <v>0.005570048625169284</v>
       </c>
       <c r="G147" t="n">
-        <v>0.1059841911033575</v>
+        <v>0.05612920563324664</v>
       </c>
       <c r="H147" t="n">
-        <v>0.1389018810197006</v>
+        <v>0.0634042373944429</v>
       </c>
       <c r="I147" t="n">
-        <v>0.06422415237020959</v>
+        <v>0.03556656496948205</v>
       </c>
       <c r="J147" t="n">
-        <v>0.2568551485887636</v>
+        <v>0.1338363300148908</v>
       </c>
       <c r="K147" t="n">
-        <v>0.5664379249612804</v>
+        <v>0.2734429249213402</v>
       </c>
       <c r="L147" t="n">
-        <v>3.492071613580211</v>
+        <v>0.8092647399601244</v>
       </c>
       <c r="M147" t="n">
-        <v>1917.67795382415</v>
+        <v>1015.601846727965</v>
       </c>
     </row>
     <row r="148">
@@ -56789,31 +56789,31 @@
         <v>27123</v>
       </c>
       <c r="E148" t="n">
-        <v>0.03911926631145516</v>
+        <v>0.02098072133883701</v>
       </c>
       <c r="F148" t="n">
-        <v>0.03115819249662271</v>
+        <v>0.02674819120756227</v>
       </c>
       <c r="G148" t="n">
-        <v>0.1373315281296303</v>
+        <v>0.07740073808496772</v>
       </c>
       <c r="H148" t="n">
-        <v>0.1255352857670634</v>
+        <v>0.07216195021993209</v>
       </c>
       <c r="I148" t="n">
-        <v>0.1032257984441902</v>
+        <v>0.05786499275104265</v>
       </c>
       <c r="J148" t="n">
-        <v>0.3097837546010947</v>
+        <v>0.1722863898722693</v>
       </c>
       <c r="K148" t="n">
-        <v>0.5578636242369484</v>
+        <v>0.3192343465743879</v>
       </c>
       <c r="L148" t="n">
-        <v>1.577812491094998</v>
+        <v>0.7583479574044694</v>
       </c>
       <c r="M148" t="n">
-        <v>3724.843037459964</v>
+        <v>2099.34021907858</v>
       </c>
     </row>
     <row r="149">
@@ -56836,31 +56836,31 @@
         <v>50301</v>
       </c>
       <c r="E149" t="n">
-        <v>0.1490023428339162</v>
+        <v>0.06614021409794475</v>
       </c>
       <c r="F149" t="n">
-        <v>0.1454104213460267</v>
+        <v>0.07561470792404548</v>
       </c>
       <c r="G149" t="n">
-        <v>0.2042152254236804</v>
+        <v>0.1085710553529202</v>
       </c>
       <c r="H149" t="n">
-        <v>0.1523884360483042</v>
+        <v>0.08294445857327101</v>
       </c>
       <c r="I149" t="n">
-        <v>0.1715686934739319</v>
+        <v>0.09296724858888135</v>
       </c>
       <c r="J149" t="n">
-        <v>0.4291734198981249</v>
+        <v>0.215005439702076</v>
       </c>
       <c r="K149" t="n">
-        <v>0.6163174843894587</v>
+        <v>0.3792419632051656</v>
       </c>
       <c r="L149" t="n">
-        <v>0.8553006898399799</v>
+        <v>0.707093875614361</v>
       </c>
       <c r="M149" t="n">
-        <v>10272.23005403655</v>
+        <v>5461.232655307238</v>
       </c>
     </row>
     <row r="150">
@@ -56883,31 +56883,31 @@
         <v>87496</v>
       </c>
       <c r="E150" t="n">
-        <v>0.329589213770711</v>
+        <v>0.1069171970399977</v>
       </c>
       <c r="F150" t="n">
-        <v>0.3562475601540399</v>
+        <v>0.1211437700770768</v>
       </c>
       <c r="G150" t="n">
-        <v>0.350446538536821</v>
+        <v>0.1498346209971928</v>
       </c>
       <c r="H150" t="n">
-        <v>0.1861128704764088</v>
+        <v>0.09989709612788462</v>
       </c>
       <c r="I150" t="n">
-        <v>0.3601477247513826</v>
+        <v>0.1373135484220165</v>
       </c>
       <c r="J150" t="n">
-        <v>0.5854786254846061</v>
+        <v>0.2771823789836021</v>
       </c>
       <c r="K150" t="n">
-        <v>0.7278668886598685</v>
+        <v>0.434425894904986</v>
       </c>
       <c r="L150" t="n">
-        <v>0.8657328972975372</v>
+        <v>0.6848101406910045</v>
       </c>
       <c r="M150" t="n">
-        <v>30662.67033581769</v>
+        <v>13109.92999877038</v>
       </c>
     </row>
     <row r="151">
@@ -56930,31 +56930,31 @@
         <v>51009</v>
       </c>
       <c r="E151" t="n">
-        <v>0.4142165336033125</v>
+        <v>0.08869696918861307</v>
       </c>
       <c r="F151" t="n">
-        <v>0.4941408402065821</v>
+        <v>0.1327591328043722</v>
       </c>
       <c r="G151" t="n">
-        <v>0.4523398719991397</v>
+        <v>0.1956011234579061</v>
       </c>
       <c r="H151" t="n">
-        <v>0.2058635913257297</v>
+        <v>0.1483381172094819</v>
       </c>
       <c r="I151" t="n">
-        <v>0.4993670793705603</v>
+        <v>0.1734610810026652</v>
       </c>
       <c r="J151" t="n">
-        <v>0.6951551197337371</v>
+        <v>0.355440567025121</v>
       </c>
       <c r="K151" t="n">
-        <v>0.7804013346556977</v>
+        <v>0.7830523801878356</v>
       </c>
       <c r="L151" t="n">
-        <v>1.563345833374826</v>
+        <v>1.340379778121382</v>
       </c>
       <c r="M151" t="n">
-        <v>23073.40453080412</v>
+        <v>9977.41770646433</v>
       </c>
     </row>
     <row r="152">
@@ -56977,31 +56977,31 @@
         <v>10280</v>
       </c>
       <c r="E152" t="n">
-        <v>0.2835871573795474</v>
+        <v>0.06566602710184609</v>
       </c>
       <c r="F152" t="n">
-        <v>0.5416575006121143</v>
+        <v>0.113511299445697</v>
       </c>
       <c r="G152" t="n">
-        <v>0.6020935283978597</v>
+        <v>0.2830540370129663</v>
       </c>
       <c r="H152" t="n">
-        <v>0.4121506394854151</v>
+        <v>0.2569521883525645</v>
       </c>
       <c r="I152" t="n">
-        <v>0.5819243738134523</v>
+        <v>0.2060945216658978</v>
       </c>
       <c r="J152" t="n">
-        <v>0.7853112272667935</v>
+        <v>0.5797164548332926</v>
       </c>
       <c r="K152" t="n">
-        <v>2.775453631446904</v>
+        <v>1.272747335131276</v>
       </c>
       <c r="L152" t="n">
-        <v>3.404687343390339</v>
+        <v>1.39515763818035</v>
       </c>
       <c r="M152" t="n">
-        <v>6189.521471929997</v>
+        <v>2909.795500493293</v>
       </c>
     </row>
     <row r="153">
@@ -57024,31 +57024,31 @@
         <v>3317</v>
       </c>
       <c r="E153" t="n">
-        <v>0.2211910882022987</v>
+        <v>-0.06534963698185214</v>
       </c>
       <c r="F153" t="n">
-        <v>0.3619188239778794</v>
+        <v>-0.1319973784452354</v>
       </c>
       <c r="G153" t="n">
-        <v>0.4404578614678136</v>
+        <v>0.2675419017102372</v>
       </c>
       <c r="H153" t="n">
-        <v>0.4787142629515822</v>
+        <v>0.1700577705413295</v>
       </c>
       <c r="I153" t="n">
-        <v>0.3818861376636147</v>
+        <v>0.239545718066858</v>
       </c>
       <c r="J153" t="n">
-        <v>0.6879658924797091</v>
+        <v>0.5503554150428203</v>
       </c>
       <c r="K153" t="n">
-        <v>3.355305116089626</v>
+        <v>0.6707088717490771</v>
       </c>
       <c r="L153" t="n">
-        <v>3.415554155717575</v>
+        <v>0.6861561104519893</v>
       </c>
       <c r="M153" t="n">
-        <v>1460.998726488738</v>
+        <v>887.4364879728569</v>
       </c>
     </row>
     <row r="154">
@@ -57118,31 +57118,31 @@
         <v>144</v>
       </c>
       <c r="E155" t="n">
-        <v>0.02391560085945659</v>
+        <v>0.01715020566350884</v>
       </c>
       <c r="F155" t="n">
-        <v>0.02832825481891632</v>
+        <v>0.01608647406101227</v>
       </c>
       <c r="G155" t="n">
-        <v>0.03223675448033544</v>
+        <v>0.02261626037458579</v>
       </c>
       <c r="H155" t="n">
-        <v>0.01982814479417133</v>
+        <v>0.01785313286795806</v>
       </c>
       <c r="I155" t="n">
-        <v>0.03030864894390106</v>
+        <v>0.01858307421207428</v>
       </c>
       <c r="J155" t="n">
-        <v>0.05825073122978214</v>
+        <v>0.04451752901077271</v>
       </c>
       <c r="K155" t="n">
-        <v>0.07630355834960934</v>
+        <v>0.07950814485549927</v>
       </c>
       <c r="L155" t="n">
-        <v>0.08198845386505127</v>
+        <v>0.08558464050292969</v>
       </c>
       <c r="M155" t="n">
-        <v>4.642092645168304</v>
+        <v>3.256741493940353</v>
       </c>
     </row>
     <row r="156">
@@ -57165,31 +57165,31 @@
         <v>538</v>
       </c>
       <c r="E156" t="n">
-        <v>0.03232491564794987</v>
+        <v>0.0246066760174847</v>
       </c>
       <c r="F156" t="n">
-        <v>0.04055653512477875</v>
+        <v>0.02558638155460358</v>
       </c>
       <c r="G156" t="n">
-        <v>0.04457904298730942</v>
+        <v>0.03615935772768183</v>
       </c>
       <c r="H156" t="n">
-        <v>0.02679093488559006</v>
+        <v>0.02455787787609619</v>
       </c>
       <c r="I156" t="n">
-        <v>0.04264964163303375</v>
+        <v>0.03223291039466858</v>
       </c>
       <c r="J156" t="n">
-        <v>0.07993717789649964</v>
+        <v>0.07131987810134888</v>
       </c>
       <c r="K156" t="n">
-        <v>0.1238418519496918</v>
+        <v>0.1006497871875763</v>
       </c>
       <c r="L156" t="n">
-        <v>0.1675695776939392</v>
+        <v>0.1557238101959229</v>
       </c>
       <c r="M156" t="n">
-        <v>23.98352512717247</v>
+        <v>19.45373445749283</v>
       </c>
     </row>
     <row r="157">
@@ -57212,31 +57212,31 @@
         <v>707</v>
       </c>
       <c r="E157" t="n">
-        <v>0.09061595612064616</v>
+        <v>0.0751715991250865</v>
       </c>
       <c r="F157" t="n">
-        <v>0.07157322764396667</v>
+        <v>0.05052369832992554</v>
       </c>
       <c r="G157" t="n">
-        <v>0.09434499957268107</v>
+        <v>0.07932399194345111</v>
       </c>
       <c r="H157" t="n">
-        <v>0.08881490707846508</v>
+        <v>0.08238082276096378</v>
       </c>
       <c r="I157" t="n">
-        <v>0.07157322764396667</v>
+        <v>0.05052369832992554</v>
       </c>
       <c r="J157" t="n">
-        <v>0.2453957974910736</v>
+        <v>0.2262419760227203</v>
       </c>
       <c r="K157" t="n">
-        <v>0.454252430796623</v>
+        <v>0.4211595410108565</v>
       </c>
       <c r="L157" t="n">
-        <v>0.4936101138591766</v>
+        <v>0.4523517191410065</v>
       </c>
       <c r="M157" t="n">
-        <v>66.70191469788551</v>
+        <v>56.08206230401993</v>
       </c>
     </row>
     <row r="158">
@@ -57259,31 +57259,31 @@
         <v>1257</v>
       </c>
       <c r="E158" t="n">
-        <v>0.2070774058074162</v>
+        <v>0.1760989788893015</v>
       </c>
       <c r="F158" t="n">
-        <v>0.2234679758548737</v>
+        <v>0.1963606476783752</v>
       </c>
       <c r="G158" t="n">
-        <v>0.2078003099065218</v>
+        <v>0.1764107708335397</v>
       </c>
       <c r="H158" t="n">
-        <v>0.1136047553889428</v>
+        <v>0.09794587765231072</v>
       </c>
       <c r="I158" t="n">
-        <v>0.2234679758548737</v>
+        <v>0.1963606476783752</v>
       </c>
       <c r="J158" t="n">
-        <v>0.3550814092159271</v>
+        <v>0.2968917489051819</v>
       </c>
       <c r="K158" t="n">
-        <v>0.4762107992172243</v>
+        <v>0.436753261089325</v>
       </c>
       <c r="L158" t="n">
-        <v>0.5047076642513275</v>
+        <v>0.4602931439876556</v>
       </c>
       <c r="M158" t="n">
-        <v>261.2049895524979</v>
+        <v>221.7483389377594</v>
       </c>
     </row>
     <row r="159">
@@ -57306,31 +57306,31 @@
         <v>2562</v>
       </c>
       <c r="E159" t="n">
-        <v>0.270972660819038</v>
+        <v>0.2027998648985208</v>
       </c>
       <c r="F159" t="n">
-        <v>0.2504311203956604</v>
+        <v>0.201803907752037</v>
       </c>
       <c r="G159" t="n">
-        <v>0.270972660819038</v>
+        <v>0.2027998648985208</v>
       </c>
       <c r="H159" t="n">
-        <v>0.09800122615790061</v>
+        <v>0.0718247488074641</v>
       </c>
       <c r="I159" t="n">
-        <v>0.2504311203956604</v>
+        <v>0.201803907752037</v>
       </c>
       <c r="J159" t="n">
-        <v>0.4021866589784622</v>
+        <v>0.3088699698448181</v>
       </c>
       <c r="K159" t="n">
-        <v>0.4643118190765379</v>
+        <v>0.3674217724800108</v>
       </c>
       <c r="L159" t="n">
-        <v>0.4881048798561096</v>
+        <v>0.3890271186828613</v>
       </c>
       <c r="M159" t="n">
-        <v>694.2319570183754</v>
+        <v>519.5732538700104</v>
       </c>
     </row>
     <row r="160">
@@ -57353,31 +57353,31 @@
         <v>1268</v>
       </c>
       <c r="E160" t="n">
-        <v>0.5763149898652022</v>
+        <v>0.3177904030455024</v>
       </c>
       <c r="F160" t="n">
-        <v>0.4861016273498535</v>
+        <v>0.3367090076208115</v>
       </c>
       <c r="G160" t="n">
-        <v>0.5763149898652022</v>
+        <v>0.3177904030455024</v>
       </c>
       <c r="H160" t="n">
-        <v>0.2157991504777311</v>
+        <v>0.05671721336472389</v>
       </c>
       <c r="I160" t="n">
-        <v>0.4861016273498535</v>
+        <v>0.3367090076208115</v>
       </c>
       <c r="J160" t="n">
-        <v>0.9275242120027541</v>
+        <v>0.3797230958938599</v>
       </c>
       <c r="K160" t="n">
-        <v>1.149943069815635</v>
+        <v>0.3880850553512573</v>
       </c>
       <c r="L160" t="n">
-        <v>1.233800262212753</v>
+        <v>0.3892191648483276</v>
       </c>
       <c r="M160" t="n">
-        <v>730.7674071490765</v>
+        <v>402.958231061697</v>
       </c>
     </row>
     <row r="161">
@@ -57400,31 +57400,31 @@
         <v>672</v>
       </c>
       <c r="E161" t="n">
-        <v>0.5680534373525352</v>
+        <v>0.3111063706289445</v>
       </c>
       <c r="F161" t="n">
-        <v>0.4614313840866089</v>
+        <v>0.3181209862232208</v>
       </c>
       <c r="G161" t="n">
-        <v>0.5680534373525352</v>
+        <v>0.3111063706289445</v>
       </c>
       <c r="H161" t="n">
-        <v>0.2542534995626305</v>
+        <v>0.03636378976987009</v>
       </c>
       <c r="I161" t="n">
-        <v>0.4614313840866089</v>
+        <v>0.3181209862232208</v>
       </c>
       <c r="J161" t="n">
-        <v>1.058615669608116</v>
+        <v>0.3565377235412598</v>
       </c>
       <c r="K161" t="n">
-        <v>1.368686451017857</v>
+        <v>0.3745282459259033</v>
       </c>
       <c r="L161" t="n">
-        <v>1.414313077926636</v>
+        <v>0.3787432312965393</v>
       </c>
       <c r="M161" t="n">
-        <v>381.7319099009037</v>
+        <v>209.0634810626507</v>
       </c>
     </row>
     <row r="162">
@@ -57541,31 +57541,31 @@
         <v>3936</v>
       </c>
       <c r="E164" t="n">
-        <v>0.001764364681598587</v>
+        <v>0.003245766919804275</v>
       </c>
       <c r="F164" t="n">
-        <v>0.002985481087988094</v>
+        <v>0.00275409286889645</v>
       </c>
       <c r="G164" t="n">
-        <v>0.06074325821978291</v>
+        <v>0.04502118192047845</v>
       </c>
       <c r="H164" t="n">
-        <v>0.0811087374931968</v>
+        <v>0.0628686613467862</v>
       </c>
       <c r="I164" t="n">
-        <v>0.03186188136217755</v>
+        <v>0.02133718648848303</v>
       </c>
       <c r="J164" t="n">
-        <v>0.1517880562576579</v>
+        <v>0.115310245009526</v>
       </c>
       <c r="K164" t="n">
-        <v>0.3921976269686485</v>
+        <v>0.2697770772755156</v>
       </c>
       <c r="L164" t="n">
-        <v>0.8289537243109601</v>
+        <v>0.8635280944346397</v>
       </c>
       <c r="M164" t="n">
-        <v>239.0854643530655</v>
+        <v>177.2033720390032</v>
       </c>
     </row>
     <row r="165">
@@ -57588,31 +57588,31 @@
         <v>15552</v>
       </c>
       <c r="E165" t="n">
-        <v>0.001223601054521919</v>
+        <v>0.004106721293481797</v>
       </c>
       <c r="F165" t="n">
-        <v>0.003370037350520644</v>
+        <v>0.005237524611406084</v>
       </c>
       <c r="G165" t="n">
-        <v>0.07667823787771563</v>
+        <v>0.05844312014789405</v>
       </c>
       <c r="H165" t="n">
-        <v>0.09518776736409489</v>
+        <v>0.07882495318112515</v>
       </c>
       <c r="I165" t="n">
-        <v>0.04305561455625999</v>
+        <v>0.03117607970043425</v>
       </c>
       <c r="J165" t="n">
-        <v>0.1852651369683462</v>
+        <v>0.1470462327521034</v>
       </c>
       <c r="K165" t="n">
-        <v>0.448205693974026</v>
+        <v>0.3816797618539879</v>
       </c>
       <c r="L165" t="n">
-        <v>0.8633449948049553</v>
+        <v>0.8591665231458675</v>
       </c>
       <c r="M165" t="n">
-        <v>1192.499955474234</v>
+        <v>908.9074045400482</v>
       </c>
     </row>
     <row r="166">
@@ -57635,31 +57635,31 @@
         <v>23107</v>
       </c>
       <c r="E166" t="n">
-        <v>0.01610804495260493</v>
+        <v>0.01497180666243814</v>
       </c>
       <c r="F166" t="n">
-        <v>0.01695192101198705</v>
+        <v>0.01931922070427777</v>
       </c>
       <c r="G166" t="n">
-        <v>0.1069182749753278</v>
+        <v>0.08104459915848941</v>
       </c>
       <c r="H166" t="n">
-        <v>0.1102387450625953</v>
+        <v>0.08971605939406453</v>
       </c>
       <c r="I166" t="n">
-        <v>0.07375322127069135</v>
+        <v>0.05468532308062751</v>
       </c>
       <c r="J166" t="n">
-        <v>0.2402269012990431</v>
+        <v>0.189169656710923</v>
       </c>
       <c r="K166" t="n">
-        <v>0.5134571609993237</v>
+        <v>0.4106780318554982</v>
       </c>
       <c r="L166" t="n">
-        <v>1.212830725056617</v>
+        <v>0.9763516221199905</v>
       </c>
       <c r="M166" t="n">
-        <v>2470.5605798549</v>
+        <v>1872.697552755215</v>
       </c>
     </row>
     <row r="167">
@@ -57682,31 +57682,31 @@
         <v>42250</v>
       </c>
       <c r="E167" t="n">
-        <v>0.08398037042706828</v>
+        <v>0.05285147057703403</v>
       </c>
       <c r="F167" t="n">
-        <v>0.08243503483116618</v>
+        <v>0.06302304449324464</v>
       </c>
       <c r="G167" t="n">
-        <v>0.1651787667628516</v>
+        <v>0.1211831283781304</v>
       </c>
       <c r="H167" t="n">
-        <v>0.1434349935567431</v>
+        <v>0.1152483239974928</v>
       </c>
       <c r="I167" t="n">
-        <v>0.1242112515020027</v>
+        <v>0.09092562999403084</v>
       </c>
       <c r="J167" t="n">
-        <v>0.3590581868655945</v>
+        <v>0.2485016714882187</v>
       </c>
       <c r="K167" t="n">
-        <v>0.6125104939823217</v>
+        <v>0.5918879817427261</v>
       </c>
       <c r="L167" t="n">
-        <v>1.202618644447905</v>
+        <v>1.306631120700792</v>
       </c>
       <c r="M167" t="n">
-        <v>6978.802895730481</v>
+        <v>5119.987173976011</v>
       </c>
     </row>
     <row r="168">
@@ -57729,31 +57729,31 @@
         <v>72142</v>
       </c>
       <c r="E168" t="n">
-        <v>0.2581086666006221</v>
+        <v>0.1258834395760668</v>
       </c>
       <c r="F168" t="n">
-        <v>0.2747728337139994</v>
+        <v>0.1462030003302968</v>
       </c>
       <c r="G168" t="n">
-        <v>0.2985989661497782</v>
+        <v>0.1843827977041158</v>
       </c>
       <c r="H168" t="n">
-        <v>0.1788574780804726</v>
+        <v>0.1446511359552518</v>
       </c>
       <c r="I168" t="n">
-        <v>0.2876424782078716</v>
+        <v>0.1657070806615904</v>
       </c>
       <c r="J168" t="n">
-        <v>0.5444572632996419</v>
+        <v>0.3438620593233254</v>
       </c>
       <c r="K168" t="n">
-        <v>0.7085829019274593</v>
+        <v>0.6610772885728272</v>
       </c>
       <c r="L168" t="n">
-        <v>1.017914056595747</v>
+        <v>1.460419155070291</v>
       </c>
       <c r="M168" t="n">
-        <v>21541.52661597729</v>
+        <v>13301.74379197032</v>
       </c>
     </row>
     <row r="169">
@@ -57776,31 +57776,31 @@
         <v>35074</v>
       </c>
       <c r="E169" t="n">
-        <v>0.4387554738803325</v>
+        <v>0.1865776442344755</v>
       </c>
       <c r="F169" t="n">
-        <v>0.472823536578042</v>
+        <v>0.2241099070574792</v>
       </c>
       <c r="G169" t="n">
-        <v>0.4476281206260984</v>
+        <v>0.2348555732214394</v>
       </c>
       <c r="H169" t="n">
-        <v>0.1787462967554532</v>
+        <v>0.149962752776956</v>
       </c>
       <c r="I169" t="n">
-        <v>0.4736510759661277</v>
+        <v>0.2347633536281744</v>
       </c>
       <c r="J169" t="n">
-        <v>0.6538818518154477</v>
+        <v>0.4199393337265129</v>
       </c>
       <c r="K169" t="n">
-        <v>0.783309912318938</v>
+        <v>0.6617225273095424</v>
       </c>
       <c r="L169" t="n">
-        <v>1.123678045395264</v>
+        <v>2.0216142200039</v>
       </c>
       <c r="M169" t="n">
-        <v>15700.10870283978</v>
+        <v>8237.324375168766</v>
       </c>
     </row>
     <row r="170">
@@ -57823,31 +57823,31 @@
         <v>4806</v>
       </c>
       <c r="E170" t="n">
-        <v>0.3926489733734497</v>
+        <v>0.09346529381761261</v>
       </c>
       <c r="F170" t="n">
-        <v>0.4754625320946501</v>
+        <v>0.05145018555300292</v>
       </c>
       <c r="G170" t="n">
-        <v>0.4820251769233509</v>
+        <v>0.2017073141439447</v>
       </c>
       <c r="H170" t="n">
-        <v>0.163314676089847</v>
+        <v>0.1557230839612266</v>
       </c>
       <c r="I170" t="n">
-        <v>0.4835657659296541</v>
+        <v>0.1788390274200122</v>
       </c>
       <c r="J170" t="n">
-        <v>0.6460248521431848</v>
+        <v>0.4527824444949397</v>
       </c>
       <c r="K170" t="n">
-        <v>1.122835149906815</v>
+        <v>0.5457613989116906</v>
       </c>
       <c r="L170" t="n">
-        <v>1.536106148894931</v>
+        <v>0.6165662959607325</v>
       </c>
       <c r="M170" t="n">
-        <v>2316.613000293624</v>
+        <v>969.4053517757983</v>
       </c>
     </row>
     <row r="171">
@@ -57870,31 +57870,31 @@
         <v>1093</v>
       </c>
       <c r="E171" t="n">
-        <v>0.2516669276215282</v>
+        <v>-0.338140124305388</v>
       </c>
       <c r="F171" t="n">
-        <v>0.2508743052334064</v>
+        <v>-0.2959595682876701</v>
       </c>
       <c r="G171" t="n">
-        <v>0.2828207169440669</v>
+        <v>0.338140124305388</v>
       </c>
       <c r="H171" t="n">
-        <v>0.1074299140664235</v>
+        <v>0.2158175844033921</v>
       </c>
       <c r="I171" t="n">
-        <v>0.2540179885754292</v>
+        <v>0.2959595682876701</v>
       </c>
       <c r="J171" t="n">
-        <v>0.4069057369523026</v>
+        <v>0.6041582956164053</v>
       </c>
       <c r="K171" t="n">
-        <v>0.5174858237901807</v>
+        <v>0.6121348840205287</v>
       </c>
       <c r="L171" t="n">
-        <v>0.8766729339022882</v>
+        <v>0.6169748365730983</v>
       </c>
       <c r="M171" t="n">
-        <v>309.1230436198651</v>
+        <v>369.587155865789</v>
       </c>
     </row>
     <row r="172">
@@ -57964,31 +57964,31 @@
         <v>183</v>
       </c>
       <c r="E173" t="n">
-        <v>0.0619959831237793</v>
+        <v>0.0601559098952455</v>
       </c>
       <c r="F173" t="n">
-        <v>0.04167398810386658</v>
+        <v>0.04054942727088928</v>
       </c>
       <c r="G173" t="n">
-        <v>0.06412090922965379</v>
+        <v>0.06236654617747323</v>
       </c>
       <c r="H173" t="n">
-        <v>0.07275945255615884</v>
+        <v>0.06995153591993555</v>
       </c>
       <c r="I173" t="n">
-        <v>0.04167398810386658</v>
+        <v>0.04054942727088928</v>
       </c>
       <c r="J173" t="n">
-        <v>0.1307953476905823</v>
+        <v>0.1382202029228211</v>
       </c>
       <c r="K173" t="n">
-        <v>0.3986829817295078</v>
+        <v>0.3745000064373019</v>
       </c>
       <c r="L173" t="n">
-        <v>0.4652965068817139</v>
+        <v>0.4376471638679504</v>
       </c>
       <c r="M173" t="n">
-        <v>11.73412638902664</v>
+        <v>11.4130779504776</v>
       </c>
     </row>
     <row r="174">
@@ -58011,31 +58011,31 @@
         <v>371</v>
       </c>
       <c r="E174" t="n">
-        <v>0.1264236223986849</v>
+        <v>0.1276985124115031</v>
       </c>
       <c r="F174" t="n">
-        <v>0.09843119978904724</v>
+        <v>0.09809371829032898</v>
       </c>
       <c r="G174" t="n">
-        <v>0.1271300325496499</v>
+        <v>0.1283632026849731</v>
       </c>
       <c r="H174" t="n">
-        <v>0.1036757660539696</v>
+        <v>0.1093051147906542</v>
       </c>
       <c r="I174" t="n">
-        <v>0.09843119978904724</v>
+        <v>0.09809371829032898</v>
       </c>
       <c r="J174" t="n">
-        <v>0.2718414664268494</v>
+        <v>0.2867468297481537</v>
       </c>
       <c r="K174" t="n">
-        <v>0.491825968027115</v>
+        <v>0.4827608466148378</v>
       </c>
       <c r="L174" t="n">
-        <v>0.511690080165863</v>
+        <v>0.5034229755401611</v>
       </c>
       <c r="M174" t="n">
-        <v>47.1652420759201</v>
+        <v>47.62274819612503</v>
       </c>
     </row>
     <row r="175">
@@ -58058,31 +58058,31 @@
         <v>370</v>
       </c>
       <c r="E175" t="n">
-        <v>0.2461058333113387</v>
+        <v>0.2503549909269487</v>
       </c>
       <c r="F175" t="n">
-        <v>0.2165865749120712</v>
+        <v>0.2117656618356705</v>
       </c>
       <c r="G175" t="n">
-        <v>0.2461370845098753</v>
+        <v>0.2504479651515548</v>
       </c>
       <c r="H175" t="n">
-        <v>0.1487151181272303</v>
+        <v>0.1573966892171604</v>
       </c>
       <c r="I175" t="n">
-        <v>0.2165865749120712</v>
+        <v>0.2117656618356705</v>
       </c>
       <c r="J175" t="n">
-        <v>0.4509951978921891</v>
+        <v>0.5140059918165208</v>
       </c>
       <c r="K175" t="n">
-        <v>0.5879831668734551</v>
+        <v>0.5834906020760536</v>
       </c>
       <c r="L175" t="n">
-        <v>0.7244351506233215</v>
+        <v>0.6052480340003967</v>
       </c>
       <c r="M175" t="n">
-        <v>91.07072126865387</v>
+        <v>92.66574710607529</v>
       </c>
     </row>
     <row r="176">
@@ -58105,31 +58105,31 @@
         <v>308</v>
       </c>
       <c r="E176" t="n">
-        <v>0.3921896284083267</v>
+        <v>0.4301550588631011</v>
       </c>
       <c r="F176" t="n">
-        <v>0.4416530281305313</v>
+        <v>0.4786081910133362</v>
       </c>
       <c r="G176" t="n">
-        <v>0.3921896284083267</v>
+        <v>0.4301550588631011</v>
       </c>
       <c r="H176" t="n">
-        <v>0.1639844781424242</v>
+        <v>0.2018605644982045</v>
       </c>
       <c r="I176" t="n">
-        <v>0.4416530281305313</v>
+        <v>0.4786081910133362</v>
       </c>
       <c r="J176" t="n">
-        <v>0.5897913664579392</v>
+        <v>0.6544035851955414</v>
       </c>
       <c r="K176" t="n">
-        <v>0.6370388889312745</v>
+        <v>0.7657716166973114</v>
       </c>
       <c r="L176" t="n">
-        <v>0.6780245304107666</v>
+        <v>0.7961772084236145</v>
       </c>
       <c r="M176" t="n">
-        <v>120.7944055497646</v>
+        <v>132.4877581298351</v>
       </c>
     </row>
     <row r="177">
@@ -58152,31 +58152,31 @@
         <v>168</v>
       </c>
       <c r="E177" t="n">
-        <v>0.6033360271581582</v>
+        <v>0.8428533089657625</v>
       </c>
       <c r="F177" t="n">
-        <v>0.5896310806274414</v>
+        <v>0.7597955763339996</v>
       </c>
       <c r="G177" t="n">
-        <v>0.6033360271581582</v>
+        <v>0.8428533089657625</v>
       </c>
       <c r="H177" t="n">
-        <v>0.1023339619113669</v>
+        <v>0.2057016658250896</v>
       </c>
       <c r="I177" t="n">
-        <v>0.5896310806274414</v>
+        <v>0.7597955763339996</v>
       </c>
       <c r="J177" t="n">
-        <v>0.7236069202423095</v>
+        <v>1.116035383939743</v>
       </c>
       <c r="K177" t="n">
-        <v>0.78253171145916</v>
+        <v>1.196222313046456</v>
       </c>
       <c r="L177" t="n">
-        <v>0.7962197959423065</v>
+        <v>1.224345296621323</v>
       </c>
       <c r="M177" t="n">
-        <v>101.3604525625706</v>
+        <v>141.5993559062481</v>
       </c>
     </row>
     <row r="178">
@@ -58199,31 +58199,31 @@
         <v>320</v>
       </c>
       <c r="E178" t="n">
-        <v>0.7337078384123743</v>
+        <v>1.261618656944484</v>
       </c>
       <c r="F178" t="n">
-        <v>0.7311970144510269</v>
+        <v>1.251566499471664</v>
       </c>
       <c r="G178" t="n">
-        <v>0.7337078384123743</v>
+        <v>1.261618656944484</v>
       </c>
       <c r="H178" t="n">
-        <v>0.06305493747401442</v>
+        <v>0.1015286364811923</v>
       </c>
       <c r="I178" t="n">
-        <v>0.7311970144510269</v>
+        <v>1.251566499471664</v>
       </c>
       <c r="J178" t="n">
-        <v>0.8159686207771302</v>
+        <v>1.404601776599884</v>
       </c>
       <c r="K178" t="n">
-        <v>0.8459305587410927</v>
+        <v>1.443557454645634</v>
       </c>
       <c r="L178" t="n">
-        <v>0.852442741394043</v>
+        <v>1.456828474998474</v>
       </c>
       <c r="M178" t="n">
-        <v>234.7865082919598</v>
+        <v>403.7179702222347</v>
       </c>
     </row>
     <row r="179">
@@ -58428,19 +58428,19 @@
         <v>1625</v>
       </c>
       <c r="C2" t="n">
-        <v>45.5487556111955</v>
+        <v>25.25752296682525</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1713476917911171</v>
+        <v>0.04399558183352042</v>
       </c>
       <c r="E2" t="n">
         <v>41</v>
       </c>
       <c r="F2" t="n">
-        <v>10.16707801742611</v>
+        <v>5.435784531517386</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0259984958363663</v>
+        <v>0.006294087758895841</v>
       </c>
     </row>
     <row r="3">
@@ -58453,19 +58453,19 @@
         <v>1636</v>
       </c>
       <c r="C3" t="n">
-        <v>38.55377087153876</v>
+        <v>32.53943112977357</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1134337532842444</v>
+        <v>0.07020457914712386</v>
       </c>
       <c r="E3" t="n">
         <v>44</v>
       </c>
       <c r="F3" t="n">
-        <v>12.85727452243145</v>
+        <v>9.369951612268158</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03583768075066488</v>
+        <v>0.01662291098093419</v>
       </c>
     </row>
     <row r="4">
@@ -58478,19 +58478,19 @@
         <v>1287</v>
       </c>
       <c r="C4" t="n">
-        <v>71.2868574424609</v>
+        <v>27.98965130541826</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7186605739578315</v>
+        <v>0.1047324908745271</v>
       </c>
       <c r="E4" t="n">
         <v>31</v>
       </c>
       <c r="F4" t="n">
-        <v>23.45780467907755</v>
+        <v>6.45097803394263</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2639651871575015</v>
+        <v>0.01622543139363702</v>
       </c>
     </row>
     <row r="5">
@@ -58503,19 +58503,19 @@
         <v>1621</v>
       </c>
       <c r="C5" t="n">
-        <v>52.85374749233759</v>
+        <v>34.21038399733682</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2162997091276416</v>
+        <v>0.09100174303322751</v>
       </c>
       <c r="E5" t="n">
         <v>44</v>
       </c>
       <c r="F5" t="n">
-        <v>11.42889083207523</v>
+        <v>5.349101716810127</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03245346053153715</v>
+        <v>0.007799584511911649</v>
       </c>
     </row>
     <row r="6">
@@ -58528,19 +58528,19 @@
         <v>1411</v>
       </c>
       <c r="C6" t="n">
-        <v>69.85707582278934</v>
+        <v>48.24562451634465</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5859912522741146</v>
+        <v>0.3259833336635287</v>
       </c>
       <c r="E6" t="n">
         <v>38</v>
       </c>
       <c r="F6" t="n">
-        <v>14.43067409491604</v>
+        <v>5.335705510884674</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1136091201394744</v>
+        <v>0.00990057643451229</v>
       </c>
     </row>
     <row r="7">
@@ -58553,19 +58553,19 @@
         <v>1157</v>
       </c>
       <c r="C7" t="n">
-        <v>40.80541508825746</v>
+        <v>21.62768350795552</v>
       </c>
       <c r="D7" t="n">
-        <v>0.276716877729271</v>
+        <v>0.1363901763627463</v>
       </c>
       <c r="E7" t="n">
         <v>22</v>
       </c>
       <c r="F7" t="n">
-        <v>9.201953282820373</v>
+        <v>3.892811162373816</v>
       </c>
       <c r="G7" t="n">
-        <v>0.04858797265931221</v>
+        <v>0.00853564341194145</v>
       </c>
     </row>
     <row r="8">
@@ -58578,19 +58578,19 @@
         <v>1027</v>
       </c>
       <c r="C8" t="n">
-        <v>32.54994022962165</v>
+        <v>16.54562201614923</v>
       </c>
       <c r="D8" t="n">
-        <v>0.158727015320855</v>
+        <v>0.05132637196471904</v>
       </c>
       <c r="E8" t="n">
         <v>17</v>
       </c>
       <c r="F8" t="n">
-        <v>10.78153587065731</v>
+        <v>2.719460133003583</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0560977042147708</v>
+        <v>0.004294990654328174</v>
       </c>
     </row>
     <row r="9">
@@ -58603,19 +58603,19 @@
         <v>1226</v>
       </c>
       <c r="C9" t="n">
-        <v>60.72313165892697</v>
+        <v>28.23941824070213</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5095737018629416</v>
+        <v>0.1499297739188104</v>
       </c>
       <c r="E9" t="n">
         <v>24</v>
       </c>
       <c r="F9" t="n">
-        <v>17.42888560658751</v>
+        <v>2.58284052936358</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1540297454948976</v>
+        <v>0.002709540910807316</v>
       </c>
     </row>
     <row r="10">
@@ -58628,19 +58628,19 @@
         <v>1295</v>
       </c>
       <c r="C10" t="n">
-        <v>40.32074875793444</v>
+        <v>20.90438196316629</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1979680672071711</v>
+        <v>0.04685195176043131</v>
       </c>
       <c r="E10" t="n">
         <v>31</v>
       </c>
       <c r="F10" t="n">
-        <v>13.3708099546639</v>
+        <v>5.539692426552276</v>
       </c>
       <c r="G10" t="n">
-        <v>0.07480377165580918</v>
+        <v>0.009214169754961036</v>
       </c>
     </row>
     <row r="11">
@@ -58653,19 +58653,19 @@
         <v>1132</v>
       </c>
       <c r="C11" t="n">
-        <v>23.79319552204374</v>
+        <v>17.18348699858024</v>
       </c>
       <c r="D11" t="n">
-        <v>0.09278527690757059</v>
+        <v>0.04824448591949564</v>
       </c>
       <c r="E11" t="n">
         <v>23</v>
       </c>
       <c r="F11" t="n">
-        <v>5.951479648177592</v>
+        <v>3.945979813608822</v>
       </c>
       <c r="G11" t="n">
-        <v>0.01816779184580341</v>
+        <v>0.007725014730385541</v>
       </c>
     </row>
   </sheetData>

--- a/Compute-Link-Attenuations/TenPatches/batch_analyze_output_multi/stats_multi.xlsx
+++ b/Compute-Link-Attenuations/TenPatches/batch_analyze_output_multi/stats_multi.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,6 +474,11 @@
           <t>E_all</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>E2_all</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -502,6 +507,9 @@
       <c r="H2" t="n">
         <v>0.005115147734703691</v>
       </c>
+      <c r="I2" t="n">
+        <v>0.0006222970616919406</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -530,6 +538,9 @@
       <c r="H3" t="n">
         <v>0.005961322652001728</v>
       </c>
+      <c r="I3" t="n">
+        <v>0.001076203680393967</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -558,6 +569,9 @@
       <c r="H4" t="n">
         <v>0.001057875626004603</v>
       </c>
+      <c r="I4" t="n">
+        <v>0.001674784254147365</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -586,6 +600,9 @@
       <c r="H5" t="n">
         <v>0.003664818332437939</v>
       </c>
+      <c r="I5" t="n">
+        <v>0.0007763014199406654</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -614,6 +631,9 @@
       <c r="H6" t="n">
         <v>-0.00302430417074996</v>
       </c>
+      <c r="I6" t="n">
+        <v>0.002747724766083882</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -642,6 +662,9 @@
       <c r="H7" t="n">
         <v>0.003125549233203863</v>
       </c>
+      <c r="I7" t="n">
+        <v>0.0008693580507599857</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -670,6 +693,9 @@
       <c r="H8" t="n">
         <v>0.002051478504188021</v>
       </c>
+      <c r="I8" t="n">
+        <v>0.0005760841273232297</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -698,6 +724,9 @@
       <c r="H9" t="n">
         <v>-0.001687862501400475</v>
       </c>
+      <c r="I9" t="n">
+        <v>0.001720425713696153</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -726,6 +755,9 @@
       <c r="H10" t="n">
         <v>0.003531064188996554</v>
       </c>
+      <c r="I10" t="n">
+        <v>0.0006373250762595202</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -753,6 +785,9 @@
       </c>
       <c r="H11" t="n">
         <v>0.003706254201615038</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.000693118752020537</v>
       </c>
     </row>
   </sheetData>
@@ -47496,7 +47531,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>wet (pred &gt;= threshold)</t>
+          <t>wet (gt &gt;= threshold)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -47543,7 +47578,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>wet (pred &gt;= threshold)</t>
+          <t>wet (gt &gt;= threshold)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -47590,7 +47625,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>wet (pred &gt;= threshold)</t>
+          <t>wet (gt &gt;= threshold)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -47637,7 +47672,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>wet (pred &gt;= threshold)</t>
+          <t>wet (gt &gt;= threshold)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -47684,7 +47719,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47728,6 +47763,11 @@
           <t>E_all</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>E2_all</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -47756,6 +47796,9 @@
       <c r="H2" t="n">
         <v>0.004737094557220646</v>
       </c>
+      <c r="I2" t="n">
+        <v>0.000531833297510217</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -47784,6 +47827,9 @@
       <c r="H3" t="n">
         <v>0.006027665110847955</v>
       </c>
+      <c r="I3" t="n">
+        <v>0.001095392134377851</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -47812,6 +47858,9 @@
       <c r="H4" t="n">
         <v>0.001194488329483568</v>
       </c>
+      <c r="I4" t="n">
+        <v>0.001346351402030888</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -47840,6 +47889,9 @@
       <c r="H5" t="n">
         <v>0.003783641048363989</v>
       </c>
+      <c r="I5" t="n">
+        <v>0.0008017132786392428</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -47868,6 +47920,9 @@
       <c r="H6" t="n">
         <v>-0.002914648603188149</v>
       </c>
+      <c r="I6" t="n">
+        <v>0.00188272455506917</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -47896,6 +47951,9 @@
       <c r="H7" t="n">
         <v>0.003097347417206426</v>
       </c>
+      <c r="I7" t="n">
+        <v>0.0008256550433253247</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -47924,6 +47982,9 @@
       <c r="H8" t="n">
         <v>0.002244445933802667</v>
       </c>
+      <c r="I8" t="n">
+        <v>0.0005665642979026886</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -47952,6 +48013,9 @@
       <c r="H9" t="n">
         <v>-0.001566201099833023</v>
       </c>
+      <c r="I9" t="n">
+        <v>0.001059448052006112</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -47980,6 +48044,9 @@
       <c r="H10" t="n">
         <v>0.003576921802845029</v>
       </c>
+      <c r="I10" t="n">
+        <v>0.0006630143512268025</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -48007,6 +48074,9 @@
       </c>
       <c r="H11" t="n">
         <v>0.003636988923439474</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.0006946981794490566</v>
       </c>
     </row>
   </sheetData>
@@ -48020,7 +48090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48064,6 +48134,11 @@
           <t>E_all</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>E2_all</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -48092,6 +48167,9 @@
       <c r="H2" t="n">
         <v>0.001364595220814024</v>
       </c>
+      <c r="I2" t="n">
+        <v>0.002252162526822577</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -48120,6 +48198,9 @@
       <c r="H3" t="n">
         <v>0.003365315744706829</v>
       </c>
+      <c r="I3" t="n">
+        <v>0.005134370931684691</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -48148,6 +48229,9 @@
       <c r="H4" t="n">
         <v>-0.0003464930755406259</v>
       </c>
+      <c r="I4" t="n">
+        <v>0.03714779125229746</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -48176,6 +48260,9 @@
       <c r="H5" t="n">
         <v>0.002668731219213252</v>
       </c>
+      <c r="I5" t="n">
+        <v>0.01183278426974612</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -48204,6 +48291,9 @@
       <c r="H6" t="n">
         <v>0.002372721791010654</v>
       </c>
+      <c r="I6" t="n">
+        <v>0.04597543451683309</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -48232,6 +48322,9 @@
       <c r="H7" t="n">
         <v>0.008117334010060042</v>
       </c>
+      <c r="I7" t="n">
+        <v>0.01527877507930473</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -48260,6 +48353,9 @@
       <c r="H8" t="n">
         <v>-0.004892922021564123</v>
       </c>
+      <c r="I8" t="n">
+        <v>0.02856143332693761</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -48288,6 +48384,9 @@
       <c r="H9" t="n">
         <v>-0.003203590019715465</v>
       </c>
+      <c r="I9" t="n">
+        <v>0.01694734780984011</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -48316,6 +48415,9 @@
       <c r="H10" t="n">
         <v>-0.003212918397939285</v>
       </c>
+      <c r="I10" t="n">
+        <v>0.00729838517625174</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -48343,6 +48445,9 @@
       </c>
       <c r="H11" t="n">
         <v>0.001844379130187991</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.007097127331009232</v>
       </c>
     </row>
   </sheetData>
@@ -48356,7 +48461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48400,6 +48505,11 @@
           <t>E_all</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>E2_all</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -48428,6 +48538,9 @@
       <c r="H2" t="n">
         <v>-2.860415774315879e-05</v>
       </c>
+      <c r="I2" t="n">
+        <v>5.701096970112061e-05</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -48456,6 +48569,9 @@
       <c r="H3" t="n">
         <v>-0.0005210501509056015</v>
       </c>
+      <c r="I3" t="n">
+        <v>0.0001984949020040664</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -48484,6 +48600,9 @@
       <c r="H4" t="n">
         <v>-0.0004791373814502451</v>
       </c>
+      <c r="I4" t="n">
+        <v>0.0008955136286526264</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -48512,6 +48631,9 @@
       <c r="H5" t="n">
         <v>-0.000386277440769455</v>
       </c>
+      <c r="I5" t="n">
+        <v>0.0003134358134263692</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -48540,6 +48662,9 @@
       <c r="H6" t="n">
         <v>-0.0005744450091487974</v>
       </c>
+      <c r="I6" t="n">
+        <v>0.002515720012241273</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -48568,6 +48693,9 @@
       <c r="H7" t="n">
         <v>-0.0008784611915105734</v>
       </c>
+      <c r="I7" t="n">
+        <v>0.0006735311823801542</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -48596,6 +48724,9 @@
       <c r="H8" t="n">
         <v>0.0006713293038393661</v>
       </c>
+      <c r="I8" t="n">
+        <v>0.001548307773713387</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -48624,6 +48755,9 @@
       <c r="H9" t="n">
         <v>-0.0003348858864490092</v>
       </c>
+      <c r="I9" t="n">
+        <v>0.0003060283956790368</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -48652,6 +48786,9 @@
       <c r="H10" t="n">
         <v>5.917579778501482e-05</v>
       </c>
+      <c r="I10" t="n">
+        <v>0.000272651428422457</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -48679,6 +48816,9 @@
       </c>
       <c r="H11" t="n">
         <v>-0.0004395068747252375</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.000236719240501938</v>
       </c>
     </row>
   </sheetData>
